--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B842591-F709-497E-BF98-E8726B83615F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -2845,7 +2845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2853,17 +2853,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3604,6 +3603,34 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -3637,6 +3664,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-A8FA-4C7B-A290-7F25A57497B3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3652,6 +3684,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-A8FA-4C7B-A290-7F25A57497B3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -4321,6 +4358,48 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -4354,6 +4433,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5CB6-464F-8CD9-E6AEBCB8C748}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -4369,6 +4453,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5CB6-464F-8CD9-E6AEBCB8C748}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -4384,6 +4473,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-5CB6-464F-8CD9-E6AEBCB8C748}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -6758,8 +6852,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>149222</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="RoomNo">
@@ -6782,7 +6876,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6836,8 +6930,8 @@
       <xdr:row>26</xdr:row>
       <xdr:rowOff>53972</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="PaymentStatus">
@@ -6860,7 +6954,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -10613,344 +10707,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D12B0F7-3CA9-41E1-BAEE-124641D0366F}" name="PivotTable5" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="A67:B71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="251">
-        <item x="70"/>
-        <item x="142"/>
-        <item x="214"/>
-        <item x="5"/>
-        <item x="76"/>
-        <item x="148"/>
-        <item x="220"/>
-        <item x="10"/>
-        <item x="82"/>
-        <item x="154"/>
-        <item x="226"/>
-        <item x="16"/>
-        <item x="88"/>
-        <item x="160"/>
-        <item x="232"/>
-        <item x="22"/>
-        <item x="94"/>
-        <item x="166"/>
-        <item x="238"/>
-        <item x="28"/>
-        <item x="100"/>
-        <item x="172"/>
-        <item x="244"/>
-        <item x="34"/>
-        <item x="106"/>
-        <item x="178"/>
-        <item x="40"/>
-        <item x="112"/>
-        <item x="184"/>
-        <item x="46"/>
-        <item x="118"/>
-        <item x="190"/>
-        <item x="52"/>
-        <item x="124"/>
-        <item x="196"/>
-        <item x="58"/>
-        <item x="130"/>
-        <item x="202"/>
-        <item x="64"/>
-        <item x="136"/>
-        <item x="208"/>
-        <item x="0"/>
-        <item x="71"/>
-        <item x="143"/>
-        <item x="215"/>
-        <item x="6"/>
-        <item x="77"/>
-        <item x="149"/>
-        <item x="221"/>
-        <item x="11"/>
-        <item x="83"/>
-        <item x="155"/>
-        <item x="227"/>
-        <item x="17"/>
-        <item x="89"/>
-        <item x="161"/>
-        <item x="233"/>
-        <item x="23"/>
-        <item x="95"/>
-        <item x="167"/>
-        <item x="239"/>
-        <item x="29"/>
-        <item x="101"/>
-        <item x="173"/>
-        <item x="245"/>
-        <item x="35"/>
-        <item x="107"/>
-        <item x="179"/>
-        <item x="41"/>
-        <item x="113"/>
-        <item x="185"/>
-        <item x="47"/>
-        <item x="119"/>
-        <item x="191"/>
-        <item x="53"/>
-        <item x="125"/>
-        <item x="197"/>
-        <item x="59"/>
-        <item x="131"/>
-        <item x="203"/>
-        <item x="65"/>
-        <item x="137"/>
-        <item x="209"/>
-        <item x="1"/>
-        <item x="72"/>
-        <item x="144"/>
-        <item x="216"/>
-        <item x="7"/>
-        <item x="78"/>
-        <item x="150"/>
-        <item x="222"/>
-        <item x="12"/>
-        <item x="84"/>
-        <item x="156"/>
-        <item x="228"/>
-        <item x="18"/>
-        <item x="90"/>
-        <item x="162"/>
-        <item x="234"/>
-        <item x="24"/>
-        <item x="96"/>
-        <item x="168"/>
-        <item x="240"/>
-        <item x="30"/>
-        <item x="102"/>
-        <item x="174"/>
-        <item x="246"/>
-        <item x="36"/>
-        <item x="108"/>
-        <item x="180"/>
-        <item x="42"/>
-        <item x="114"/>
-        <item x="186"/>
-        <item x="48"/>
-        <item x="120"/>
-        <item x="192"/>
-        <item x="54"/>
-        <item x="126"/>
-        <item x="198"/>
-        <item x="60"/>
-        <item x="132"/>
-        <item x="204"/>
-        <item x="66"/>
-        <item x="138"/>
-        <item x="210"/>
-        <item x="2"/>
-        <item x="73"/>
-        <item x="145"/>
-        <item x="217"/>
-        <item x="8"/>
-        <item x="79"/>
-        <item x="151"/>
-        <item x="223"/>
-        <item x="13"/>
-        <item x="85"/>
-        <item x="157"/>
-        <item x="229"/>
-        <item x="19"/>
-        <item x="91"/>
-        <item x="163"/>
-        <item x="235"/>
-        <item x="25"/>
-        <item x="97"/>
-        <item x="169"/>
-        <item x="241"/>
-        <item x="31"/>
-        <item x="103"/>
-        <item x="175"/>
-        <item x="247"/>
-        <item x="37"/>
-        <item x="109"/>
-        <item x="181"/>
-        <item x="43"/>
-        <item x="115"/>
-        <item x="187"/>
-        <item x="49"/>
-        <item x="121"/>
-        <item x="193"/>
-        <item x="55"/>
-        <item x="127"/>
-        <item x="199"/>
-        <item x="61"/>
-        <item x="133"/>
-        <item x="205"/>
-        <item x="67"/>
-        <item x="139"/>
-        <item x="211"/>
-        <item x="3"/>
-        <item x="74"/>
-        <item x="146"/>
-        <item x="218"/>
-        <item x="9"/>
-        <item x="80"/>
-        <item x="152"/>
-        <item x="224"/>
-        <item x="14"/>
-        <item x="86"/>
-        <item x="158"/>
-        <item x="230"/>
-        <item x="20"/>
-        <item x="92"/>
-        <item x="164"/>
-        <item x="236"/>
-        <item x="26"/>
-        <item x="98"/>
-        <item x="170"/>
-        <item x="242"/>
-        <item x="32"/>
-        <item x="104"/>
-        <item x="176"/>
-        <item x="248"/>
-        <item x="38"/>
-        <item x="110"/>
-        <item x="182"/>
-        <item x="44"/>
-        <item x="116"/>
-        <item x="188"/>
-        <item x="50"/>
-        <item x="122"/>
-        <item x="194"/>
-        <item x="56"/>
-        <item x="128"/>
-        <item x="200"/>
-        <item x="62"/>
-        <item x="134"/>
-        <item x="206"/>
-        <item x="68"/>
-        <item x="140"/>
-        <item x="212"/>
-        <item x="4"/>
-        <item x="75"/>
-        <item x="147"/>
-        <item x="219"/>
-        <item x="81"/>
-        <item x="153"/>
-        <item x="225"/>
-        <item x="15"/>
-        <item x="87"/>
-        <item x="159"/>
-        <item x="231"/>
-        <item x="21"/>
-        <item x="93"/>
-        <item x="165"/>
-        <item x="237"/>
-        <item x="27"/>
-        <item x="99"/>
-        <item x="171"/>
-        <item x="243"/>
-        <item x="33"/>
-        <item x="105"/>
-        <item x="177"/>
-        <item x="249"/>
-        <item x="39"/>
-        <item x="111"/>
-        <item x="183"/>
-        <item x="45"/>
-        <item x="117"/>
-        <item x="189"/>
-        <item x="51"/>
-        <item x="123"/>
-        <item x="195"/>
-        <item x="57"/>
-        <item x="129"/>
-        <item x="201"/>
-        <item x="63"/>
-        <item x="135"/>
-        <item x="207"/>
-        <item x="69"/>
-        <item x="141"/>
-        <item x="213"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="5" baseItem="1"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="8" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A62FA1C6-6B15-42CF-B8ED-FDCC0FCBC43C}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A62FA1C6-6B15-42CF-B8ED-FDCC0FCBC43C}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A43:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField dataField="1" showAll="0"/>
@@ -11288,8 +11045,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C59890A-608F-4988-B6CF-7001EF1794D9}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C59890A-608F-4988-B6CF-7001EF1794D9}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A14:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField dataField="1" showAll="0"/>
@@ -11869,8 +11626,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{325A8F64-29CD-470E-9D0F-650C9B1326CD}" name="PivotTable1" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{325A8F64-29CD-470E-9D0F-650C9B1326CD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -12217,6 +11974,343 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D12B0F7-3CA9-41E1-BAEE-124641D0366F}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A67:B71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="251">
+        <item x="70"/>
+        <item x="142"/>
+        <item x="214"/>
+        <item x="5"/>
+        <item x="76"/>
+        <item x="148"/>
+        <item x="220"/>
+        <item x="10"/>
+        <item x="82"/>
+        <item x="154"/>
+        <item x="226"/>
+        <item x="16"/>
+        <item x="88"/>
+        <item x="160"/>
+        <item x="232"/>
+        <item x="22"/>
+        <item x="94"/>
+        <item x="166"/>
+        <item x="238"/>
+        <item x="28"/>
+        <item x="100"/>
+        <item x="172"/>
+        <item x="244"/>
+        <item x="34"/>
+        <item x="106"/>
+        <item x="178"/>
+        <item x="40"/>
+        <item x="112"/>
+        <item x="184"/>
+        <item x="46"/>
+        <item x="118"/>
+        <item x="190"/>
+        <item x="52"/>
+        <item x="124"/>
+        <item x="196"/>
+        <item x="58"/>
+        <item x="130"/>
+        <item x="202"/>
+        <item x="64"/>
+        <item x="136"/>
+        <item x="208"/>
+        <item x="0"/>
+        <item x="71"/>
+        <item x="143"/>
+        <item x="215"/>
+        <item x="6"/>
+        <item x="77"/>
+        <item x="149"/>
+        <item x="221"/>
+        <item x="11"/>
+        <item x="83"/>
+        <item x="155"/>
+        <item x="227"/>
+        <item x="17"/>
+        <item x="89"/>
+        <item x="161"/>
+        <item x="233"/>
+        <item x="23"/>
+        <item x="95"/>
+        <item x="167"/>
+        <item x="239"/>
+        <item x="29"/>
+        <item x="101"/>
+        <item x="173"/>
+        <item x="245"/>
+        <item x="35"/>
+        <item x="107"/>
+        <item x="179"/>
+        <item x="41"/>
+        <item x="113"/>
+        <item x="185"/>
+        <item x="47"/>
+        <item x="119"/>
+        <item x="191"/>
+        <item x="53"/>
+        <item x="125"/>
+        <item x="197"/>
+        <item x="59"/>
+        <item x="131"/>
+        <item x="203"/>
+        <item x="65"/>
+        <item x="137"/>
+        <item x="209"/>
+        <item x="1"/>
+        <item x="72"/>
+        <item x="144"/>
+        <item x="216"/>
+        <item x="7"/>
+        <item x="78"/>
+        <item x="150"/>
+        <item x="222"/>
+        <item x="12"/>
+        <item x="84"/>
+        <item x="156"/>
+        <item x="228"/>
+        <item x="18"/>
+        <item x="90"/>
+        <item x="162"/>
+        <item x="234"/>
+        <item x="24"/>
+        <item x="96"/>
+        <item x="168"/>
+        <item x="240"/>
+        <item x="30"/>
+        <item x="102"/>
+        <item x="174"/>
+        <item x="246"/>
+        <item x="36"/>
+        <item x="108"/>
+        <item x="180"/>
+        <item x="42"/>
+        <item x="114"/>
+        <item x="186"/>
+        <item x="48"/>
+        <item x="120"/>
+        <item x="192"/>
+        <item x="54"/>
+        <item x="126"/>
+        <item x="198"/>
+        <item x="60"/>
+        <item x="132"/>
+        <item x="204"/>
+        <item x="66"/>
+        <item x="138"/>
+        <item x="210"/>
+        <item x="2"/>
+        <item x="73"/>
+        <item x="145"/>
+        <item x="217"/>
+        <item x="8"/>
+        <item x="79"/>
+        <item x="151"/>
+        <item x="223"/>
+        <item x="13"/>
+        <item x="85"/>
+        <item x="157"/>
+        <item x="229"/>
+        <item x="19"/>
+        <item x="91"/>
+        <item x="163"/>
+        <item x="235"/>
+        <item x="25"/>
+        <item x="97"/>
+        <item x="169"/>
+        <item x="241"/>
+        <item x="31"/>
+        <item x="103"/>
+        <item x="175"/>
+        <item x="247"/>
+        <item x="37"/>
+        <item x="109"/>
+        <item x="181"/>
+        <item x="43"/>
+        <item x="115"/>
+        <item x="187"/>
+        <item x="49"/>
+        <item x="121"/>
+        <item x="193"/>
+        <item x="55"/>
+        <item x="127"/>
+        <item x="199"/>
+        <item x="61"/>
+        <item x="133"/>
+        <item x="205"/>
+        <item x="67"/>
+        <item x="139"/>
+        <item x="211"/>
+        <item x="3"/>
+        <item x="74"/>
+        <item x="146"/>
+        <item x="218"/>
+        <item x="9"/>
+        <item x="80"/>
+        <item x="152"/>
+        <item x="224"/>
+        <item x="14"/>
+        <item x="86"/>
+        <item x="158"/>
+        <item x="230"/>
+        <item x="20"/>
+        <item x="92"/>
+        <item x="164"/>
+        <item x="236"/>
+        <item x="26"/>
+        <item x="98"/>
+        <item x="170"/>
+        <item x="242"/>
+        <item x="32"/>
+        <item x="104"/>
+        <item x="176"/>
+        <item x="248"/>
+        <item x="38"/>
+        <item x="110"/>
+        <item x="182"/>
+        <item x="44"/>
+        <item x="116"/>
+        <item x="188"/>
+        <item x="50"/>
+        <item x="122"/>
+        <item x="194"/>
+        <item x="56"/>
+        <item x="128"/>
+        <item x="200"/>
+        <item x="62"/>
+        <item x="134"/>
+        <item x="206"/>
+        <item x="68"/>
+        <item x="140"/>
+        <item x="212"/>
+        <item x="4"/>
+        <item x="75"/>
+        <item x="147"/>
+        <item x="219"/>
+        <item x="81"/>
+        <item x="153"/>
+        <item x="225"/>
+        <item x="15"/>
+        <item x="87"/>
+        <item x="159"/>
+        <item x="231"/>
+        <item x="21"/>
+        <item x="93"/>
+        <item x="165"/>
+        <item x="237"/>
+        <item x="27"/>
+        <item x="99"/>
+        <item x="171"/>
+        <item x="243"/>
+        <item x="33"/>
+        <item x="105"/>
+        <item x="177"/>
+        <item x="249"/>
+        <item x="39"/>
+        <item x="111"/>
+        <item x="183"/>
+        <item x="45"/>
+        <item x="117"/>
+        <item x="189"/>
+        <item x="51"/>
+        <item x="123"/>
+        <item x="195"/>
+        <item x="57"/>
+        <item x="129"/>
+        <item x="201"/>
+        <item x="63"/>
+        <item x="135"/>
+        <item x="207"/>
+        <item x="69"/>
+        <item x="141"/>
+        <item x="213"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="5" baseItem="1"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="8" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_RoomNo" xr10:uid="{FC762340-3809-4E26-9D63-7D14763AE321}" sourceName="RoomNo">
   <pivotTables>
@@ -12415,7 +12509,7 @@
       <c r="A4" s="4">
         <v>201</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>379769</v>
       </c>
     </row>
@@ -12423,7 +12517,7 @@
       <c r="A5" s="4">
         <v>202</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>332367</v>
       </c>
     </row>
@@ -12431,7 +12525,7 @@
       <c r="A6" s="4">
         <v>203</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>484569</v>
       </c>
     </row>
@@ -12439,7 +12533,7 @@
       <c r="A7" s="4">
         <v>204</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>566865</v>
       </c>
     </row>
@@ -12447,7 +12541,7 @@
       <c r="A8" s="4">
         <v>205</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>226497</v>
       </c>
     </row>
@@ -12455,7 +12549,7 @@
       <c r="A9" s="4">
         <v>206</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>845859</v>
       </c>
     </row>
@@ -12463,7 +12557,7 @@
       <c r="A10" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>2835926</v>
       </c>
     </row>
@@ -12479,7 +12573,7 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15">
         <v>162</v>
       </c>
     </row>
@@ -12487,7 +12581,7 @@
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16">
         <v>88</v>
       </c>
     </row>
@@ -12495,7 +12589,7 @@
       <c r="A17" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>250</v>
       </c>
     </row>
@@ -12511,7 +12605,7 @@
       <c r="A44" s="4">
         <v>201</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44">
         <v>43</v>
       </c>
     </row>
@@ -12519,7 +12613,7 @@
       <c r="A45" s="4">
         <v>202</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45">
         <v>41</v>
       </c>
     </row>
@@ -12527,7 +12621,7 @@
       <c r="A46" s="4">
         <v>203</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46">
         <v>42</v>
       </c>
     </row>
@@ -12535,7 +12629,7 @@
       <c r="A47" s="4">
         <v>204</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47">
         <v>41</v>
       </c>
     </row>
@@ -12543,7 +12637,7 @@
       <c r="A48" s="4">
         <v>205</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48">
         <v>42</v>
       </c>
     </row>
@@ -12551,7 +12645,7 @@
       <c r="A49" s="4">
         <v>206</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49">
         <v>41</v>
       </c>
     </row>
@@ -12559,7 +12653,7 @@
       <c r="A50" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50">
         <v>250</v>
       </c>
     </row>
@@ -12575,7 +12669,7 @@
       <c r="A68" s="4">
         <v>2</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B68">
         <v>171</v>
       </c>
     </row>
@@ -12583,7 +12677,7 @@
       <c r="A69" s="4">
         <v>3</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B69">
         <v>43</v>
       </c>
     </row>
@@ -12591,7 +12685,7 @@
       <c r="A70" s="4">
         <v>4</v>
       </c>
-      <c r="B70" s="5">
+      <c r="B70">
         <v>36</v>
       </c>
     </row>
@@ -12599,7 +12693,7 @@
       <c r="A71" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B71">
         <v>250</v>
       </c>
     </row>
@@ -19930,50 +20024,50 @@
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:19" ht="20" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>906</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
     </row>
     <row r="2" spans="1:19" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -19995,13 +20089,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="5" t="s">
         <v>908</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>909</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>910</v>
       </c>
     </row>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C1C6D97-D892-491B-9525-738D7D748EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CECC7F-B6D4-4B9A-8FCA-5AC4DBBB9282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
+    <sheet name="Monthly Revenue Trend" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="6" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="930">
   <si>
     <t>BookingID</t>
   </si>
@@ -2755,12 +2760,84 @@
   </si>
   <si>
     <t>Quarter</t>
+  </si>
+  <si>
+    <t>Sum of TotalAmount</t>
+  </si>
+  <si>
+    <t>Count of BookingID</t>
+  </si>
+  <si>
+    <t>Average of TotalAmount</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Average of Stay Duration</t>
+  </si>
+  <si>
+    <t>KPI 1 Total Revenue</t>
+  </si>
+  <si>
+    <t>KPI 2 Total Bookings</t>
+  </si>
+  <si>
+    <t>KPI 3 Average Booking Value</t>
+  </si>
+  <si>
+    <t>KPI 4 Paid Bookings</t>
+  </si>
+  <si>
+    <t>KPI 6 Average Stay</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2879,7 +2956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2895,11 +2972,68 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="33">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3333,32 +3467,4455 @@
 </styleSheet>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46188.716442129633" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="250" xr:uid="{ABC0FC96-CD6A-4AE4-9F1C-C79E4709B301}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="tblBookings"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="BookingID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="RoomNo" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="201" maxValue="206"/>
+    </cacheField>
+    <cacheField name="GuestName" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="CheckIn" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="CheckOut" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Guests" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="4"/>
+    </cacheField>
+    <cacheField name="Phone" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="9012345678" maxValue="9903456789"/>
+    </cacheField>
+    <cacheField name="TotalAmount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4398" maxValue="29995"/>
+    </cacheField>
+    <cacheField name="PaymentStatus" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Paid"/>
+        <s v="Pending"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Stay Duration" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="5"/>
+    </cacheField>
+    <cacheField name="Year" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2026" maxValue="2029"/>
+    </cacheField>
+    <cacheField name="Month" numFmtId="0">
+      <sharedItems count="12">
+        <s v="Jan"/>
+        <s v="Feb"/>
+        <s v="Mar"/>
+        <s v="Apr"/>
+        <s v="May"/>
+        <s v="Jun"/>
+        <s v="Jul"/>
+        <s v="Aug"/>
+        <s v="Sep"/>
+        <s v="Oct"/>
+        <s v="Nov"/>
+        <s v="Dec"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Month Number" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12"/>
+    </cacheField>
+    <cacheField name="Quarter" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="250">
+  <r>
+    <s v="BK0001"/>
+    <n v="201"/>
+    <s v="Rahul Sharma"/>
+    <s v="05-01-26"/>
+    <s v="08-01-26"/>
+    <n v="2"/>
+    <n v="9876543210"/>
+    <n v="8697"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0002"/>
+    <n v="203"/>
+    <s v="Priya Patel"/>
+    <s v="10-01-26"/>
+    <s v="13-01-26"/>
+    <n v="4"/>
+    <n v="9123456789"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0003"/>
+    <n v="205"/>
+    <s v="Amit Kumar"/>
+    <s v="15-01-26"/>
+    <s v="17-01-26"/>
+    <n v="2"/>
+    <n v="9345678901"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0004"/>
+    <n v="204"/>
+    <s v="Sneha Reddy"/>
+    <s v="20-01-26"/>
+    <s v="24-01-26"/>
+    <n v="2"/>
+    <n v="9456789012"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0005"/>
+    <n v="202"/>
+    <s v="Vikram Gupta"/>
+    <s v="25-01-26"/>
+    <s v="28-01-26"/>
+    <n v="2"/>
+    <n v="9567890123"/>
+    <n v="7497"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0006"/>
+    <n v="206"/>
+    <s v="Meera Nair"/>
+    <s v="01-02-26"/>
+    <s v="04-02-26"/>
+    <n v="3"/>
+    <n v="9678901234"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0007"/>
+    <n v="201"/>
+    <s v="Aditya Singh"/>
+    <s v="05-02-26"/>
+    <s v="07-02-26"/>
+    <n v="2"/>
+    <n v="9789012345"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0008"/>
+    <n v="203"/>
+    <s v="Kavya Rao"/>
+    <s v="10-02-26"/>
+    <s v="14-02-26"/>
+    <n v="4"/>
+    <n v="9890123456"/>
+    <n v="14796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0009"/>
+    <n v="205"/>
+    <s v="Rohan Mehta"/>
+    <s v="15-02-26"/>
+    <s v="18-02-26"/>
+    <n v="2"/>
+    <n v="9901234567"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0010"/>
+    <n v="204"/>
+    <s v="Divya Kapoor"/>
+    <s v="20-02-26"/>
+    <s v="22-02-26"/>
+    <n v="2"/>
+    <n v="9012345678"/>
+    <n v="8398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0011"/>
+    <n v="202"/>
+    <s v="Neha Jain"/>
+    <s v="01-03-26"/>
+    <s v="04-03-26"/>
+    <n v="2"/>
+    <n v="9123456701"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0012"/>
+    <n v="201"/>
+    <s v="Arjun Verma"/>
+    <s v="05-03-26"/>
+    <s v="09-03-26"/>
+    <n v="2"/>
+    <n v="9234567012"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0013"/>
+    <n v="206"/>
+    <s v="Nikhil Das"/>
+    <s v="10-03-26"/>
+    <s v="12-03-26"/>
+    <n v="2"/>
+    <n v="9345670123"/>
+    <n v="11998"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0014"/>
+    <n v="205"/>
+    <s v="Aisha Bhat"/>
+    <s v="15-03-26"/>
+    <s v="18-03-26"/>
+    <n v="2"/>
+    <n v="9456701234"/>
+    <n v="6597"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0015"/>
+    <n v="203"/>
+    <s v="Sanjay Yadav"/>
+    <s v="20-03-26"/>
+    <s v="23-03-26"/>
+    <n v="4"/>
+    <n v="9567012345"/>
+    <n v="11097"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0016"/>
+    <n v="204"/>
+    <s v="Pooja Iyer"/>
+    <s v="25-03-26"/>
+    <s v="29-03-26"/>
+    <n v="2"/>
+    <n v="9670123456"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0017"/>
+    <n v="201"/>
+    <s v="Ishita Rao"/>
+    <s v="01-04-26"/>
+    <s v="03-04-26"/>
+    <n v="2"/>
+    <n v="9781234567"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0018"/>
+    <n v="202"/>
+    <s v="Karthik Sharma"/>
+    <s v="05-04-26"/>
+    <s v="08-04-26"/>
+    <n v="2"/>
+    <n v="9892345678"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0019"/>
+    <n v="206"/>
+    <s v="Ananya Gupta"/>
+    <s v="10-04-26"/>
+    <s v="14-04-26"/>
+    <n v="3"/>
+    <n v="9903456789"/>
+    <n v="23996"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0020"/>
+    <n v="203"/>
+    <s v="Varun Kumar"/>
+    <s v="15-04-26"/>
+    <s v="18-04-26"/>
+    <n v="4"/>
+    <n v="9014567890"/>
+    <n v="11097"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0021"/>
+    <n v="205"/>
+    <s v="Meera Singh"/>
+    <s v="20-04-26"/>
+    <s v="22-04-26"/>
+    <n v="2"/>
+    <n v="9125678901"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0022"/>
+    <n v="204"/>
+    <s v="Rahul Jain"/>
+    <s v="25-04-26"/>
+    <s v="28-04-26"/>
+    <n v="2"/>
+    <n v="9236789012"/>
+    <n v="12597"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0023"/>
+    <n v="201"/>
+    <s v="Divya Patel"/>
+    <s v="01-05-26"/>
+    <s v="04-05-26"/>
+    <n v="2"/>
+    <n v="9347890123"/>
+    <n v="8697"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0024"/>
+    <n v="202"/>
+    <s v="Nikhil Sharma"/>
+    <s v="05-05-26"/>
+    <s v="07-05-26"/>
+    <n v="2"/>
+    <n v="9458901234"/>
+    <n v="4998"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0025"/>
+    <n v="206"/>
+    <s v="Sneha Kapoor"/>
+    <s v="10-05-26"/>
+    <s v="13-05-26"/>
+    <n v="3"/>
+    <n v="9569012345"/>
+    <n v="17997"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0026"/>
+    <n v="203"/>
+    <s v="Amit Verma"/>
+    <s v="15-05-26"/>
+    <s v="19-05-26"/>
+    <n v="4"/>
+    <n v="9670123987"/>
+    <n v="14796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0027"/>
+    <n v="205"/>
+    <s v="Priya Rao"/>
+    <s v="20-05-26"/>
+    <s v="23-05-26"/>
+    <n v="2"/>
+    <n v="9781234098"/>
+    <n v="6597"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0028"/>
+    <n v="201"/>
+    <s v="Rohan Gupta"/>
+    <s v="25-05-26"/>
+    <s v="27-05-26"/>
+    <n v="2"/>
+    <n v="9892345109"/>
+    <n v="5798"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0029"/>
+    <n v="204"/>
+    <s v="Ananya Nair"/>
+    <s v="01-06-26"/>
+    <s v="05-06-26"/>
+    <n v="2"/>
+    <n v="9903456210"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0030"/>
+    <n v="202"/>
+    <s v="Sanjay Das"/>
+    <s v="05-06-26"/>
+    <s v="08-06-26"/>
+    <n v="2"/>
+    <n v="9014567321"/>
+    <n v="7497"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0031"/>
+    <n v="203"/>
+    <s v="Kavya Mehta"/>
+    <s v="10-06-26"/>
+    <s v="12-06-26"/>
+    <n v="3"/>
+    <n v="9125678432"/>
+    <n v="7398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0032"/>
+    <n v="206"/>
+    <s v="Arjun Singh"/>
+    <s v="15-06-26"/>
+    <s v="20-06-26"/>
+    <n v="3"/>
+    <n v="9236789543"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2026"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0033"/>
+    <n v="205"/>
+    <s v="Neha Bhat"/>
+    <s v="20-06-26"/>
+    <s v="22-06-26"/>
+    <n v="2"/>
+    <n v="9347890654"/>
+    <n v="4398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0034"/>
+    <n v="201"/>
+    <s v="Vikram Iyer"/>
+    <s v="25-06-26"/>
+    <s v="28-06-26"/>
+    <n v="2"/>
+    <n v="9458901765"/>
+    <n v="8697"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0035"/>
+    <n v="204"/>
+    <s v="Pooja Sharma"/>
+    <s v="01-07-26"/>
+    <s v="03-07-26"/>
+    <n v="2"/>
+    <n v="9569012876"/>
+    <n v="8398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0036"/>
+    <n v="202"/>
+    <s v="Aisha Patel"/>
+    <s v="05-07-26"/>
+    <s v="08-07-26"/>
+    <n v="2"/>
+    <n v="9670123987"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0037"/>
+    <n v="203"/>
+    <s v="Karthik Rao"/>
+    <s v="10-07-26"/>
+    <s v="14-07-26"/>
+    <n v="4"/>
+    <n v="9781234098"/>
+    <n v="14796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0038"/>
+    <n v="206"/>
+    <s v="Divya Gupta"/>
+    <s v="15-07-26"/>
+    <s v="18-07-26"/>
+    <n v="3"/>
+    <n v="9892345109"/>
+    <n v="17997"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0039"/>
+    <n v="205"/>
+    <s v="Aditya Jain"/>
+    <s v="20-07-26"/>
+    <s v="23-07-26"/>
+    <n v="2"/>
+    <n v="9903456210"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0040"/>
+    <n v="201"/>
+    <s v="Meera Verma"/>
+    <s v="25-07-26"/>
+    <s v="27-07-26"/>
+    <n v="2"/>
+    <n v="9014567321"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0041"/>
+    <n v="204"/>
+    <s v="Rahul Nair"/>
+    <s v="01-08-26"/>
+    <s v="04-08-26"/>
+    <n v="2"/>
+    <n v="9125678432"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0042"/>
+    <n v="202"/>
+    <s v="Sneha Das"/>
+    <s v="05-08-26"/>
+    <s v="09-08-26"/>
+    <n v="2"/>
+    <n v="9236789543"/>
+    <n v="9996"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0043"/>
+    <n v="203"/>
+    <s v="Varun Sharma"/>
+    <s v="10-08-26"/>
+    <s v="13-08-26"/>
+    <n v="4"/>
+    <n v="9347890654"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0044"/>
+    <n v="206"/>
+    <s v="Priya Kapoor"/>
+    <s v="15-08-26"/>
+    <s v="17-08-26"/>
+    <n v="2"/>
+    <n v="9458901765"/>
+    <n v="11998"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0045"/>
+    <n v="205"/>
+    <s v="Nikhil Patel"/>
+    <s v="20-08-26"/>
+    <s v="22-08-26"/>
+    <n v="2"/>
+    <n v="9569012876"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0046"/>
+    <n v="201"/>
+    <s v="Amit Gupta"/>
+    <s v="25-08-26"/>
+    <s v="29-08-26"/>
+    <n v="2"/>
+    <n v="9670123987"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0047"/>
+    <n v="204"/>
+    <s v="Ishita Singh"/>
+    <s v="01-09-26"/>
+    <s v="05-09-26"/>
+    <n v="2"/>
+    <n v="9781234098"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0048"/>
+    <n v="202"/>
+    <s v="Rohan Kumar"/>
+    <s v="05-09-26"/>
+    <s v="08-09-26"/>
+    <n v="2"/>
+    <n v="9892345109"/>
+    <n v="7497"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0049"/>
+    <n v="203"/>
+    <s v="Ananya Mehta"/>
+    <s v="10-09-26"/>
+    <s v="12-09-26"/>
+    <n v="4"/>
+    <n v="9903456210"/>
+    <n v="7398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0050"/>
+    <n v="206"/>
+    <s v="Kavya Jain"/>
+    <s v="15-09-26"/>
+    <s v="19-09-26"/>
+    <n v="3"/>
+    <n v="9014567321"/>
+    <n v="23996"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0051"/>
+    <n v="205"/>
+    <s v="Arjun Rao"/>
+    <s v="20-09-26"/>
+    <s v="23-09-26"/>
+    <n v="2"/>
+    <n v="9123457811"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0052"/>
+    <n v="201"/>
+    <s v="Priya Sharma"/>
+    <s v="25-09-26"/>
+    <s v="28-09-26"/>
+    <n v="2"/>
+    <n v="9234568922"/>
+    <n v="8697"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0053"/>
+    <n v="204"/>
+    <s v="Vikram Patel"/>
+    <s v="01-10-26"/>
+    <s v="04-10-26"/>
+    <n v="2"/>
+    <n v="9345679033"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0054"/>
+    <n v="202"/>
+    <s v="Sneha Gupta"/>
+    <s v="05-10-26"/>
+    <s v="08-10-26"/>
+    <n v="2"/>
+    <n v="9456780144"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0055"/>
+    <n v="203"/>
+    <s v="Rohan Singh"/>
+    <s v="10-10-26"/>
+    <s v="14-10-26"/>
+    <n v="4"/>
+    <n v="9567891255"/>
+    <n v="14796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0056"/>
+    <n v="206"/>
+    <s v="Divya Nair"/>
+    <s v="15-10-26"/>
+    <s v="18-10-26"/>
+    <n v="3"/>
+    <n v="9678902366"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0057"/>
+    <n v="205"/>
+    <s v="Amit Mehta"/>
+    <s v="20-10-26"/>
+    <s v="22-10-26"/>
+    <n v="2"/>
+    <n v="9789013477"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0058"/>
+    <n v="201"/>
+    <s v="Kavya Jain"/>
+    <s v="25-10-26"/>
+    <s v="29-10-26"/>
+    <n v="2"/>
+    <n v="9890124588"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0059"/>
+    <n v="204"/>
+    <s v="Aditya Verma"/>
+    <s v="01-11-26"/>
+    <s v="03-11-26"/>
+    <n v="2"/>
+    <n v="9901235699"/>
+    <n v="8398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0060"/>
+    <n v="202"/>
+    <s v="Neha Kapoor"/>
+    <s v="05-11-26"/>
+    <s v="09-11-26"/>
+    <n v="2"/>
+    <n v="9012346700"/>
+    <n v="9996"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0061"/>
+    <n v="203"/>
+    <s v="Sanjay Kumar"/>
+    <s v="10-11-26"/>
+    <s v="13-11-26"/>
+    <n v="4"/>
+    <n v="9123457811"/>
+    <n v="11097"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0062"/>
+    <n v="206"/>
+    <s v="Ananya Rao"/>
+    <s v="15-11-26"/>
+    <s v="20-11-26"/>
+    <n v="3"/>
+    <n v="9234568922"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2026"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0063"/>
+    <n v="205"/>
+    <s v="Rahul Bhat"/>
+    <s v="20-11-26"/>
+    <s v="23-11-26"/>
+    <n v="2"/>
+    <n v="9345679033"/>
+    <n v="6597"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0064"/>
+    <n v="201"/>
+    <s v="Meera Patel"/>
+    <s v="25-11-26"/>
+    <s v="27-11-26"/>
+    <n v="2"/>
+    <n v="9456780144"/>
+    <n v="5798"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0065"/>
+    <n v="204"/>
+    <s v="Nikhil Sharma"/>
+    <s v="01-12-26"/>
+    <s v="05-12-26"/>
+    <n v="2"/>
+    <n v="9567891255"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0066"/>
+    <n v="202"/>
+    <s v="Pooja Gupta"/>
+    <s v="05-12-26"/>
+    <s v="08-12-26"/>
+    <n v="2"/>
+    <n v="9678902366"/>
+    <n v="7497"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0067"/>
+    <n v="203"/>
+    <s v="Karthik Das"/>
+    <s v="10-12-26"/>
+    <s v="12-12-26"/>
+    <n v="3"/>
+    <n v="9789013477"/>
+    <n v="7398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0068"/>
+    <n v="206"/>
+    <s v="Aisha Singh"/>
+    <s v="15-12-26"/>
+    <s v="18-12-26"/>
+    <n v="3"/>
+    <n v="9890124588"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2026"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0069"/>
+    <n v="205"/>
+    <s v="Varun Nair"/>
+    <s v="20-12-26"/>
+    <s v="22-12-26"/>
+    <n v="2"/>
+    <n v="9901235699"/>
+    <n v="4398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2026"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0070"/>
+    <n v="201"/>
+    <s v="Sneha Rao"/>
+    <s v="25-12-26"/>
+    <s v="29-12-26"/>
+    <n v="2"/>
+    <n v="9012346700"/>
+    <n v="11596"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2026"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0071"/>
+    <n v="204"/>
+    <s v="Amit Jain"/>
+    <s v="01-01-27"/>
+    <s v="04-01-27"/>
+    <n v="2"/>
+    <n v="9123457811"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0072"/>
+    <n v="202"/>
+    <s v="Divya Sharma"/>
+    <s v="05-01-27"/>
+    <s v="08-01-27"/>
+    <n v="2"/>
+    <n v="9234568922"/>
+    <n v="7497"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0073"/>
+    <n v="203"/>
+    <s v="Rohan Patel"/>
+    <s v="10-01-27"/>
+    <s v="13-01-27"/>
+    <n v="4"/>
+    <n v="9345679033"/>
+    <n v="11097"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0074"/>
+    <n v="206"/>
+    <s v="Priya Kapoor"/>
+    <s v="15-01-27"/>
+    <s v="17-01-27"/>
+    <n v="2"/>
+    <n v="9456780144"/>
+    <n v="11998"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0075"/>
+    <n v="205"/>
+    <s v="Aditya Gupta"/>
+    <s v="20-01-27"/>
+    <s v="23-01-27"/>
+    <n v="2"/>
+    <n v="9567891255"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0076"/>
+    <n v="201"/>
+    <s v="Kavya Verma"/>
+    <s v="25-01-27"/>
+    <s v="27-01-27"/>
+    <n v="2"/>
+    <n v="9678902366"/>
+    <n v="5798"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0077"/>
+    <n v="204"/>
+    <s v="Neha Singh"/>
+    <s v="01-02-27"/>
+    <s v="05-02-27"/>
+    <n v="2"/>
+    <n v="9789013477"/>
+    <n v="16796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0078"/>
+    <n v="202"/>
+    <s v="Sanjay Mehta"/>
+    <s v="05-02-27"/>
+    <s v="09-02-27"/>
+    <n v="2"/>
+    <n v="9890124588"/>
+    <n v="9996"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0079"/>
+    <n v="203"/>
+    <s v="Ananya Jain"/>
+    <s v="10-02-27"/>
+    <s v="14-02-27"/>
+    <n v="4"/>
+    <n v="9901235699"/>
+    <n v="14796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0080"/>
+    <n v="206"/>
+    <s v="Rahul Kumar"/>
+    <s v="15-02-27"/>
+    <s v="18-02-27"/>
+    <n v="3"/>
+    <n v="9012346700"/>
+    <n v="17997"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0081"/>
+    <n v="205"/>
+    <s v="Meera Das"/>
+    <s v="20-02-27"/>
+    <s v="22-02-27"/>
+    <n v="2"/>
+    <n v="9123457811"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0082"/>
+    <n v="201"/>
+    <s v="Nikhil Rao"/>
+    <s v="25-02-27"/>
+    <s v="28-02-27"/>
+    <n v="2"/>
+    <n v="9234568922"/>
+    <n v="8697"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0083"/>
+    <n v="204"/>
+    <s v="Pooja Patel"/>
+    <s v="01-03-27"/>
+    <s v="04-03-27"/>
+    <n v="2"/>
+    <n v="9345679033"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0084"/>
+    <n v="202"/>
+    <s v="Karthik Sharma"/>
+    <s v="05-03-27"/>
+    <s v="08-03-27"/>
+    <n v="2"/>
+    <n v="9456780144"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0085"/>
+    <n v="203"/>
+    <s v="Aisha Gupta"/>
+    <s v="10-03-27"/>
+    <s v="13-03-27"/>
+    <n v="4"/>
+    <n v="9567891255"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0086"/>
+    <n v="206"/>
+    <s v="Varun Singh"/>
+    <s v="15-03-27"/>
+    <s v="20-03-27"/>
+    <n v="3"/>
+    <n v="9678902366"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2027"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0087"/>
+    <n v="205"/>
+    <s v="Sneha Kapoor"/>
+    <s v="20-03-27"/>
+    <s v="22-03-27"/>
+    <n v="2"/>
+    <n v="9789013477"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0088"/>
+    <n v="201"/>
+    <s v="Amit Nair"/>
+    <s v="25-03-27"/>
+    <s v="29-03-27"/>
+    <n v="2"/>
+    <n v="9890124588"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0089"/>
+    <n v="204"/>
+    <s v="Divya Rao"/>
+    <s v="01-04-27"/>
+    <s v="03-04-27"/>
+    <n v="2"/>
+    <n v="9901235699"/>
+    <n v="8398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0090"/>
+    <n v="202"/>
+    <s v="Rohan Jain"/>
+    <s v="05-04-27"/>
+    <s v="08-04-27"/>
+    <n v="2"/>
+    <n v="9012346700"/>
+    <n v="7497"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0091"/>
+    <n v="203"/>
+    <s v="Priya Verma"/>
+    <s v="10-04-27"/>
+    <s v="14-04-27"/>
+    <n v="4"/>
+    <n v="9123457811"/>
+    <n v="14796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0092"/>
+    <n v="206"/>
+    <s v="Aditya Sharma"/>
+    <s v="15-04-27"/>
+    <s v="18-04-27"/>
+    <n v="3"/>
+    <n v="9234568922"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0093"/>
+    <n v="205"/>
+    <s v="Kavya Gupta"/>
+    <s v="20-04-27"/>
+    <s v="23-04-27"/>
+    <n v="2"/>
+    <n v="9345679033"/>
+    <n v="6597"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0094"/>
+    <n v="201"/>
+    <s v="Neha Patel"/>
+    <s v="25-04-27"/>
+    <s v="27-04-27"/>
+    <n v="2"/>
+    <n v="9456780144"/>
+    <n v="5798"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0095"/>
+    <n v="204"/>
+    <s v="Sanjay Singh"/>
+    <s v="01-05-27"/>
+    <s v="05-05-27"/>
+    <n v="2"/>
+    <n v="9567891255"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0096"/>
+    <n v="202"/>
+    <s v="Ananya Mehta"/>
+    <s v="05-05-27"/>
+    <s v="09-05-27"/>
+    <n v="2"/>
+    <n v="9678902366"/>
+    <n v="9996"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0097"/>
+    <n v="203"/>
+    <s v="Rahul Kapoor"/>
+    <s v="10-05-27"/>
+    <s v="12-05-27"/>
+    <n v="4"/>
+    <n v="9789013477"/>
+    <n v="7398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0098"/>
+    <n v="206"/>
+    <s v="Meera Kumar"/>
+    <s v="15-05-27"/>
+    <s v="18-05-27"/>
+    <n v="3"/>
+    <n v="9890124588"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0099"/>
+    <n v="205"/>
+    <s v="Nikhil Jain"/>
+    <s v="20-05-27"/>
+    <s v="22-05-27"/>
+    <n v="2"/>
+    <n v="9901235699"/>
+    <n v="4398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0100"/>
+    <n v="201"/>
+    <s v="Pooja Das"/>
+    <s v="25-05-27"/>
+    <s v="29-05-27"/>
+    <n v="2"/>
+    <n v="9012346700"/>
+    <n v="11596"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0101"/>
+    <n v="204"/>
+    <s v="Arjun Sharma"/>
+    <s v="01-06-27"/>
+    <s v="04-06-27"/>
+    <n v="2"/>
+    <n v="9123457001"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0102"/>
+    <n v="202"/>
+    <s v="Priya Gupta"/>
+    <s v="05-06-27"/>
+    <s v="08-06-27"/>
+    <n v="2"/>
+    <n v="9234568112"/>
+    <n v="7497"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0103"/>
+    <n v="203"/>
+    <s v="Rahul Patel"/>
+    <s v="10-06-27"/>
+    <s v="14-06-27"/>
+    <n v="4"/>
+    <n v="9345679223"/>
+    <n v="14796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0104"/>
+    <n v="206"/>
+    <s v="Sneha Singh"/>
+    <s v="15-06-27"/>
+    <s v="18-06-27"/>
+    <n v="3"/>
+    <n v="9456780334"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0105"/>
+    <n v="205"/>
+    <s v="Amit Rao"/>
+    <s v="20-06-27"/>
+    <s v="22-06-27"/>
+    <n v="2"/>
+    <n v="9567891445"/>
+    <n v="4398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0106"/>
+    <n v="201"/>
+    <s v="Kavya Jain"/>
+    <s v="25-06-27"/>
+    <s v="29-06-27"/>
+    <n v="2"/>
+    <n v="9678902556"/>
+    <n v="11596"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0107"/>
+    <n v="204"/>
+    <s v="Nikhil Kumar"/>
+    <s v="01-07-27"/>
+    <s v="03-07-27"/>
+    <n v="2"/>
+    <n v="9789013667"/>
+    <n v="8398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0108"/>
+    <n v="202"/>
+    <s v="Meera Sharma"/>
+    <s v="05-07-27"/>
+    <s v="09-07-27"/>
+    <n v="2"/>
+    <n v="9890124778"/>
+    <n v="9996"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0109"/>
+    <n v="203"/>
+    <s v="Aditya Gupta"/>
+    <s v="10-07-27"/>
+    <s v="13-07-27"/>
+    <n v="4"/>
+    <n v="9901235889"/>
+    <n v="11097"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0110"/>
+    <n v="206"/>
+    <s v="Divya Patel"/>
+    <s v="15-07-27"/>
+    <s v="20-07-27"/>
+    <n v="3"/>
+    <n v="9012346990"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2027"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0111"/>
+    <n v="205"/>
+    <s v="Rohan Kapoor"/>
+    <s v="20-07-27"/>
+    <s v="23-07-27"/>
+    <n v="2"/>
+    <n v="9123457001"/>
+    <n v="6597"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0112"/>
+    <n v="201"/>
+    <s v="Ananya Verma"/>
+    <s v="25-07-27"/>
+    <s v="27-07-27"/>
+    <n v="2"/>
+    <n v="9234568112"/>
+    <n v="5798"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0113"/>
+    <n v="204"/>
+    <s v="Sanjay Nair"/>
+    <s v="01-08-27"/>
+    <s v="05-08-27"/>
+    <n v="2"/>
+    <n v="9345679223"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0114"/>
+    <n v="202"/>
+    <s v="Pooja Rao"/>
+    <s v="05-08-27"/>
+    <s v="08-08-27"/>
+    <n v="2"/>
+    <n v="9456780334"/>
+    <n v="7497"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0115"/>
+    <n v="203"/>
+    <s v="Karthik Singh"/>
+    <s v="10-08-27"/>
+    <s v="12-08-27"/>
+    <n v="3"/>
+    <n v="9567891445"/>
+    <n v="7398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0116"/>
+    <n v="206"/>
+    <s v="Aisha Mehta"/>
+    <s v="15-08-27"/>
+    <s v="18-08-27"/>
+    <n v="3"/>
+    <n v="9678902556"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0117"/>
+    <n v="205"/>
+    <s v="Varun Jain"/>
+    <s v="20-08-27"/>
+    <s v="22-08-27"/>
+    <n v="2"/>
+    <n v="9789013667"/>
+    <n v="4398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0118"/>
+    <n v="201"/>
+    <s v="Sneha Das"/>
+    <s v="25-08-27"/>
+    <s v="29-08-27"/>
+    <n v="2"/>
+    <n v="9890124778"/>
+    <n v="11596"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0119"/>
+    <n v="204"/>
+    <s v="Amit Sharma"/>
+    <s v="01-09-27"/>
+    <s v="04-09-27"/>
+    <n v="2"/>
+    <n v="9901235889"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0120"/>
+    <n v="202"/>
+    <s v="Divya Gupta"/>
+    <s v="05-09-27"/>
+    <s v="08-09-27"/>
+    <n v="2"/>
+    <n v="9012346990"/>
+    <n v="7497"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0121"/>
+    <n v="203"/>
+    <s v="Rohan Patel"/>
+    <s v="10-09-27"/>
+    <s v="13-09-27"/>
+    <n v="4"/>
+    <n v="9123457001"/>
+    <n v="11097"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0122"/>
+    <n v="206"/>
+    <s v="Ananya Kapoor"/>
+    <s v="15-09-27"/>
+    <s v="17-09-27"/>
+    <n v="2"/>
+    <n v="9234568112"/>
+    <n v="11998"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0123"/>
+    <n v="205"/>
+    <s v="Sanjay Verma"/>
+    <s v="20-09-27"/>
+    <s v="23-09-27"/>
+    <n v="2"/>
+    <n v="9345679223"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0124"/>
+    <n v="201"/>
+    <s v="Pooja Nair"/>
+    <s v="25-09-27"/>
+    <s v="27-09-27"/>
+    <n v="2"/>
+    <n v="9456780334"/>
+    <n v="5798"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0125"/>
+    <n v="204"/>
+    <s v="Karthik Rao"/>
+    <s v="01-10-27"/>
+    <s v="05-10-27"/>
+    <n v="2"/>
+    <n v="9567891445"/>
+    <n v="16796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0126"/>
+    <n v="202"/>
+    <s v="Aisha Singh"/>
+    <s v="05-10-27"/>
+    <s v="09-10-27"/>
+    <n v="2"/>
+    <n v="9678902556"/>
+    <n v="9996"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0127"/>
+    <n v="203"/>
+    <s v="Varun Mehta"/>
+    <s v="10-10-27"/>
+    <s v="14-10-27"/>
+    <n v="4"/>
+    <n v="9789013667"/>
+    <n v="14796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0128"/>
+    <n v="206"/>
+    <s v="Sneha Jain"/>
+    <s v="15-10-27"/>
+    <s v="18-10-27"/>
+    <n v="3"/>
+    <n v="9890124778"/>
+    <n v="17997"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0129"/>
+    <n v="205"/>
+    <s v="Amit Das"/>
+    <s v="20-10-27"/>
+    <s v="22-10-27"/>
+    <n v="2"/>
+    <n v="9901235889"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0130"/>
+    <n v="201"/>
+    <s v="Divya Sharma"/>
+    <s v="25-10-27"/>
+    <s v="29-10-27"/>
+    <n v="2"/>
+    <n v="9012346990"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0131"/>
+    <n v="204"/>
+    <s v="Rohan Gupta"/>
+    <s v="01-11-27"/>
+    <s v="03-11-27"/>
+    <n v="2"/>
+    <n v="9123457001"/>
+    <n v="8398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0132"/>
+    <n v="202"/>
+    <s v="Ananya Patel"/>
+    <s v="05-11-27"/>
+    <s v="08-11-27"/>
+    <n v="2"/>
+    <n v="9234568112"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0133"/>
+    <n v="203"/>
+    <s v="Sanjay Kapoor"/>
+    <s v="10-11-27"/>
+    <s v="14-11-27"/>
+    <n v="4"/>
+    <n v="9345679223"/>
+    <n v="14796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0134"/>
+    <n v="206"/>
+    <s v="Pooja Verma"/>
+    <s v="15-11-27"/>
+    <s v="20-11-27"/>
+    <n v="3"/>
+    <n v="9456780334"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2027"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0135"/>
+    <n v="205"/>
+    <s v="Karthik Nair"/>
+    <s v="20-11-27"/>
+    <s v="23-11-27"/>
+    <n v="2"/>
+    <n v="9567891445"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0136"/>
+    <n v="201"/>
+    <s v="Aisha Rao"/>
+    <s v="25-11-27"/>
+    <s v="27-11-27"/>
+    <n v="2"/>
+    <n v="9678902556"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0137"/>
+    <n v="204"/>
+    <s v="Varun Singh"/>
+    <s v="01-12-27"/>
+    <s v="05-12-27"/>
+    <n v="2"/>
+    <n v="9789013667"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0138"/>
+    <n v="202"/>
+    <s v="Sneha Mehta"/>
+    <s v="05-12-27"/>
+    <s v="08-12-27"/>
+    <n v="2"/>
+    <n v="9890124778"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0139"/>
+    <n v="203"/>
+    <s v="Amit Jain"/>
+    <s v="10-12-27"/>
+    <s v="13-12-27"/>
+    <n v="4"/>
+    <n v="9901235889"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0140"/>
+    <n v="206"/>
+    <s v="Divya Das"/>
+    <s v="15-12-27"/>
+    <s v="18-12-27"/>
+    <n v="3"/>
+    <n v="9012346990"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2027"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0141"/>
+    <n v="205"/>
+    <s v="Rohan Sharma"/>
+    <s v="20-12-27"/>
+    <s v="22-12-27"/>
+    <n v="2"/>
+    <n v="9123457001"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2027"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0142"/>
+    <n v="201"/>
+    <s v="Ananya Gupta"/>
+    <s v="25-12-27"/>
+    <s v="29-12-27"/>
+    <n v="2"/>
+    <n v="9234568112"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2027"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0143"/>
+    <n v="204"/>
+    <s v="Sanjay Patel"/>
+    <s v="01-01-28"/>
+    <s v="04-01-28"/>
+    <n v="2"/>
+    <n v="9345679223"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0144"/>
+    <n v="202"/>
+    <s v="Pooja Kapoor"/>
+    <s v="05-01-28"/>
+    <s v="09-01-28"/>
+    <n v="2"/>
+    <n v="9456780334"/>
+    <n v="9996"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0145"/>
+    <n v="203"/>
+    <s v="Karthik Verma"/>
+    <s v="10-01-28"/>
+    <s v="12-01-28"/>
+    <n v="3"/>
+    <n v="9567891445"/>
+    <n v="7398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0146"/>
+    <n v="206"/>
+    <s v="Aisha Nair"/>
+    <s v="15-01-28"/>
+    <s v="18-01-28"/>
+    <n v="3"/>
+    <n v="9678902556"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0147"/>
+    <n v="205"/>
+    <s v="Varun Rao"/>
+    <s v="20-01-28"/>
+    <s v="23-01-28"/>
+    <n v="2"/>
+    <n v="9789013667"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0148"/>
+    <n v="201"/>
+    <s v="Sneha Singh"/>
+    <s v="25-01-28"/>
+    <s v="27-01-28"/>
+    <n v="2"/>
+    <n v="9890124778"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0149"/>
+    <n v="204"/>
+    <s v="Amit Mehta"/>
+    <s v="01-02-28"/>
+    <s v="05-02-28"/>
+    <n v="2"/>
+    <n v="9901235889"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0150"/>
+    <n v="202"/>
+    <s v="Divya Jain"/>
+    <s v="05-02-28"/>
+    <s v="08-02-28"/>
+    <n v="2"/>
+    <n v="9012346990"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0151"/>
+    <n v="203"/>
+    <s v="Rahul Nair"/>
+    <s v="10-02-28"/>
+    <s v="13-02-28"/>
+    <n v="4"/>
+    <n v="9123457101"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0152"/>
+    <n v="206"/>
+    <s v="Meera Sharma"/>
+    <s v="15-02-28"/>
+    <s v="18-02-28"/>
+    <n v="3"/>
+    <n v="9234568212"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0153"/>
+    <n v="205"/>
+    <s v="Nikhil Gupta"/>
+    <s v="20-02-28"/>
+    <s v="22-02-28"/>
+    <n v="2"/>
+    <n v="9345679323"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0154"/>
+    <n v="201"/>
+    <s v="Pooja Patel"/>
+    <s v="25-02-28"/>
+    <s v="29-02-28"/>
+    <n v="2"/>
+    <n v="9456780434"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0155"/>
+    <n v="204"/>
+    <s v="Karthik Kapoor"/>
+    <s v="01-03-28"/>
+    <s v="04-03-28"/>
+    <n v="2"/>
+    <n v="9567891545"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0156"/>
+    <n v="202"/>
+    <s v="Aisha Verma"/>
+    <s v="05-03-28"/>
+    <s v="08-03-28"/>
+    <n v="2"/>
+    <n v="9678902656"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0157"/>
+    <n v="203"/>
+    <s v="Varun Jain"/>
+    <s v="10-03-28"/>
+    <s v="14-03-28"/>
+    <n v="4"/>
+    <n v="9789013767"/>
+    <n v="14796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0158"/>
+    <n v="206"/>
+    <s v="Sneha Das"/>
+    <s v="15-03-28"/>
+    <s v="20-03-28"/>
+    <n v="3"/>
+    <n v="9890124878"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2028"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0159"/>
+    <n v="205"/>
+    <s v="Amit Sharma"/>
+    <s v="20-03-28"/>
+    <s v="23-03-28"/>
+    <n v="2"/>
+    <n v="9901235989"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0160"/>
+    <n v="201"/>
+    <s v="Divya Gupta"/>
+    <s v="25-03-28"/>
+    <s v="27-03-28"/>
+    <n v="2"/>
+    <n v="9012346090"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0161"/>
+    <n v="204"/>
+    <s v="Rohan Patel"/>
+    <s v="01-04-28"/>
+    <s v="05-04-28"/>
+    <n v="2"/>
+    <n v="9123457101"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0162"/>
+    <n v="202"/>
+    <s v="Ananya Singh"/>
+    <s v="05-04-28"/>
+    <s v="09-04-28"/>
+    <n v="2"/>
+    <n v="9234568212"/>
+    <n v="9996"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0163"/>
+    <n v="203"/>
+    <s v="Sanjay Mehta"/>
+    <s v="10-04-28"/>
+    <s v="13-04-28"/>
+    <n v="4"/>
+    <n v="9345679323"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0164"/>
+    <n v="206"/>
+    <s v="Priya Rao"/>
+    <s v="15-04-28"/>
+    <s v="18-04-28"/>
+    <n v="3"/>
+    <n v="9456780434"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0165"/>
+    <n v="205"/>
+    <s v="Aditya Kumar"/>
+    <s v="20-04-28"/>
+    <s v="22-04-28"/>
+    <n v="2"/>
+    <n v="9567891545"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0166"/>
+    <n v="201"/>
+    <s v="Kavya Nair"/>
+    <s v="25-04-28"/>
+    <s v="29-04-28"/>
+    <n v="2"/>
+    <n v="9678902656"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0167"/>
+    <n v="204"/>
+    <s v="Neha Sharma"/>
+    <s v="01-05-28"/>
+    <s v="04-05-28"/>
+    <n v="2"/>
+    <n v="9789013767"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0168"/>
+    <n v="202"/>
+    <s v="Rahul Gupta"/>
+    <s v="05-05-28"/>
+    <s v="08-05-28"/>
+    <n v="2"/>
+    <n v="9890124878"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0169"/>
+    <n v="203"/>
+    <s v="Meera Patel"/>
+    <s v="10-05-28"/>
+    <s v="12-05-28"/>
+    <n v="3"/>
+    <n v="9901235989"/>
+    <n v="7398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0170"/>
+    <n v="206"/>
+    <s v="Nikhil Kapoor"/>
+    <s v="15-05-28"/>
+    <s v="18-05-28"/>
+    <n v="3"/>
+    <n v="9012346090"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0171"/>
+    <n v="205"/>
+    <s v="Pooja Verma"/>
+    <s v="20-05-28"/>
+    <s v="23-05-28"/>
+    <n v="2"/>
+    <n v="9123457101"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0172"/>
+    <n v="201"/>
+    <s v="Karthik Jain"/>
+    <s v="25-05-28"/>
+    <s v="27-05-28"/>
+    <n v="2"/>
+    <n v="9234568212"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0173"/>
+    <n v="204"/>
+    <s v="Aisha Das"/>
+    <s v="01-06-28"/>
+    <s v="05-06-28"/>
+    <n v="2"/>
+    <n v="9345679323"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0174"/>
+    <n v="202"/>
+    <s v="Varun Sharma"/>
+    <s v="05-06-28"/>
+    <s v="08-06-28"/>
+    <n v="2"/>
+    <n v="9456780434"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0175"/>
+    <n v="203"/>
+    <s v="Sneha Gupta"/>
+    <s v="10-06-28"/>
+    <s v="13-06-28"/>
+    <n v="4"/>
+    <n v="9567891545"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0176"/>
+    <n v="206"/>
+    <s v="Amit Patel"/>
+    <s v="15-06-28"/>
+    <s v="20-06-28"/>
+    <n v="3"/>
+    <n v="9678902656"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2028"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0177"/>
+    <n v="205"/>
+    <s v="Divya Singh"/>
+    <s v="20-06-28"/>
+    <s v="22-06-28"/>
+    <n v="2"/>
+    <n v="9789013767"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0178"/>
+    <n v="201"/>
+    <s v="Rohan Mehta"/>
+    <s v="25-06-28"/>
+    <s v="29-06-28"/>
+    <n v="2"/>
+    <n v="9890124878"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0179"/>
+    <n v="204"/>
+    <s v="Ananya Rao"/>
+    <s v="01-07-28"/>
+    <s v="03-07-28"/>
+    <n v="2"/>
+    <n v="9901235989"/>
+    <n v="8398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0180"/>
+    <n v="202"/>
+    <s v="Sanjay Kumar"/>
+    <s v="05-07-28"/>
+    <s v="08-07-28"/>
+    <n v="2"/>
+    <n v="9012346090"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0181"/>
+    <n v="203"/>
+    <s v="Priya Nair"/>
+    <s v="10-07-28"/>
+    <s v="14-07-28"/>
+    <n v="4"/>
+    <n v="9123457101"/>
+    <n v="14796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0182"/>
+    <n v="206"/>
+    <s v="Aditya Sharma"/>
+    <s v="15-07-28"/>
+    <s v="18-07-28"/>
+    <n v="3"/>
+    <n v="9234568212"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0183"/>
+    <n v="205"/>
+    <s v="Kavya Gupta"/>
+    <s v="20-07-28"/>
+    <s v="23-07-28"/>
+    <n v="2"/>
+    <n v="9345679323"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0184"/>
+    <n v="201"/>
+    <s v="Neha Patel"/>
+    <s v="25-07-28"/>
+    <s v="27-07-28"/>
+    <n v="2"/>
+    <n v="9456780434"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="6"/>
+    <n v="7"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0185"/>
+    <n v="204"/>
+    <s v="Rahul Singh"/>
+    <s v="01-08-28"/>
+    <s v="05-08-28"/>
+    <n v="2"/>
+    <n v="9567891545"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0186"/>
+    <n v="202"/>
+    <s v="Meera Mehta"/>
+    <s v="05-08-28"/>
+    <s v="09-08-28"/>
+    <n v="2"/>
+    <n v="9678902656"/>
+    <n v="9996"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0187"/>
+    <n v="203"/>
+    <s v="Nikhil Rao"/>
+    <s v="10-08-28"/>
+    <s v="12-08-28"/>
+    <n v="4"/>
+    <n v="9789013767"/>
+    <n v="7398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0188"/>
+    <n v="206"/>
+    <s v="Pooja Kumar"/>
+    <s v="15-08-28"/>
+    <s v="18-08-28"/>
+    <n v="3"/>
+    <n v="9890124878"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0189"/>
+    <n v="205"/>
+    <s v="Karthik Nair"/>
+    <s v="20-08-28"/>
+    <s v="22-08-28"/>
+    <n v="2"/>
+    <n v="9901235989"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0190"/>
+    <n v="201"/>
+    <s v="Aisha Sharma"/>
+    <s v="25-08-28"/>
+    <s v="29-08-28"/>
+    <n v="2"/>
+    <n v="9012346090"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="7"/>
+    <n v="8"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0191"/>
+    <n v="204"/>
+    <s v="Varun Gupta"/>
+    <s v="01-09-28"/>
+    <s v="04-09-28"/>
+    <n v="2"/>
+    <n v="9123457101"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0192"/>
+    <n v="202"/>
+    <s v="Sneha Patel"/>
+    <s v="05-09-28"/>
+    <s v="08-09-28"/>
+    <n v="2"/>
+    <n v="9234568212"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0193"/>
+    <n v="203"/>
+    <s v="Amit Singh"/>
+    <s v="10-09-28"/>
+    <s v="13-09-28"/>
+    <n v="4"/>
+    <n v="9345679323"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0194"/>
+    <n v="206"/>
+    <s v="Divya Mehta"/>
+    <s v="15-09-28"/>
+    <s v="18-09-28"/>
+    <n v="3"/>
+    <n v="9456780434"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0195"/>
+    <n v="205"/>
+    <s v="Rohan Rao"/>
+    <s v="20-09-28"/>
+    <s v="22-09-28"/>
+    <n v="2"/>
+    <n v="9567891545"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0196"/>
+    <n v="201"/>
+    <s v="Ananya Kumar"/>
+    <s v="25-09-28"/>
+    <s v="29-09-28"/>
+    <n v="2"/>
+    <n v="9678902656"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="8"/>
+    <n v="9"/>
+    <s v="Q3"/>
+  </r>
+  <r>
+    <s v="BK0197"/>
+    <n v="204"/>
+    <s v="Sanjay Nair"/>
+    <s v="01-10-28"/>
+    <s v="05-10-28"/>
+    <n v="2"/>
+    <n v="9789013767"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0198"/>
+    <n v="202"/>
+    <s v="Priya Sharma"/>
+    <s v="05-10-28"/>
+    <s v="08-10-28"/>
+    <n v="2"/>
+    <n v="9890124878"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0199"/>
+    <n v="203"/>
+    <s v="Aditya Gupta"/>
+    <s v="10-10-28"/>
+    <s v="14-10-28"/>
+    <n v="4"/>
+    <n v="9901235989"/>
+    <n v="14796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0200"/>
+    <n v="206"/>
+    <s v="Kavya Patel"/>
+    <s v="15-10-28"/>
+    <s v="18-10-28"/>
+    <n v="3"/>
+    <n v="9012346090"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0201"/>
+    <n v="205"/>
+    <s v="Neha Kapoor"/>
+    <s v="20-10-28"/>
+    <s v="23-10-28"/>
+    <n v="2"/>
+    <n v="9123457201"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0202"/>
+    <n v="201"/>
+    <s v="Rahul Sharma"/>
+    <s v="25-10-28"/>
+    <s v="27-10-28"/>
+    <n v="2"/>
+    <n v="9234568312"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="9"/>
+    <n v="10"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0203"/>
+    <n v="204"/>
+    <s v="Meera Gupta"/>
+    <s v="01-11-28"/>
+    <s v="05-11-28"/>
+    <n v="2"/>
+    <n v="9345679423"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0204"/>
+    <n v="202"/>
+    <s v="Nikhil Patel"/>
+    <s v="05-11-28"/>
+    <s v="08-11-28"/>
+    <n v="2"/>
+    <n v="9456780534"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0205"/>
+    <n v="203"/>
+    <s v="Pooja Singh"/>
+    <s v="10-11-28"/>
+    <s v="13-11-28"/>
+    <n v="4"/>
+    <n v="9567891645"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0206"/>
+    <n v="206"/>
+    <s v="Karthik Mehta"/>
+    <s v="15-11-28"/>
+    <s v="20-11-28"/>
+    <n v="3"/>
+    <n v="9678902756"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2028"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0207"/>
+    <n v="205"/>
+    <s v="Aisha Rao"/>
+    <s v="20-11-28"/>
+    <s v="22-11-28"/>
+    <n v="2"/>
+    <n v="9789013867"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0208"/>
+    <n v="201"/>
+    <s v="Varun Kumar"/>
+    <s v="25-11-28"/>
+    <s v="29-11-28"/>
+    <n v="2"/>
+    <n v="9890124978"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="10"/>
+    <n v="11"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0209"/>
+    <n v="204"/>
+    <s v="Sneha Nair"/>
+    <s v="01-12-28"/>
+    <s v="04-12-28"/>
+    <n v="2"/>
+    <n v="9901236089"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0210"/>
+    <n v="202"/>
+    <s v="Amit Sharma"/>
+    <s v="05-12-28"/>
+    <s v="08-12-28"/>
+    <n v="2"/>
+    <n v="9012347190"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0211"/>
+    <n v="203"/>
+    <s v="Divya Gupta"/>
+    <s v="10-12-28"/>
+    <s v="14-12-28"/>
+    <n v="4"/>
+    <n v="9123457201"/>
+    <n v="14796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2028"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0212"/>
+    <n v="206"/>
+    <s v="Rohan Patel"/>
+    <s v="15-12-28"/>
+    <s v="18-12-28"/>
+    <n v="3"/>
+    <n v="9234568312"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0213"/>
+    <n v="205"/>
+    <s v="Ananya Singh"/>
+    <s v="20-12-28"/>
+    <s v="23-12-28"/>
+    <n v="2"/>
+    <n v="9345679423"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2028"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0214"/>
+    <n v="201"/>
+    <s v="Sanjay Mehta"/>
+    <s v="25-12-28"/>
+    <s v="27-12-28"/>
+    <n v="2"/>
+    <n v="9456780534"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2028"/>
+    <x v="11"/>
+    <n v="12"/>
+    <s v="Q4"/>
+  </r>
+  <r>
+    <s v="BK0215"/>
+    <n v="204"/>
+    <s v="Priya Rao"/>
+    <s v="01-01-29"/>
+    <s v="05-01-29"/>
+    <n v="2"/>
+    <n v="9567891645"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0216"/>
+    <n v="202"/>
+    <s v="Aditya Kumar"/>
+    <s v="05-01-29"/>
+    <s v="09-01-29"/>
+    <n v="2"/>
+    <n v="9678902756"/>
+    <n v="9996"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0217"/>
+    <n v="203"/>
+    <s v="Kavya Nair"/>
+    <s v="10-01-29"/>
+    <s v="12-01-29"/>
+    <n v="3"/>
+    <n v="9789013867"/>
+    <n v="7398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2029"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0218"/>
+    <n v="206"/>
+    <s v="Neha Sharma"/>
+    <s v="15-01-29"/>
+    <s v="18-01-29"/>
+    <n v="3"/>
+    <n v="9890124978"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0219"/>
+    <n v="205"/>
+    <s v="Rahul Gupta"/>
+    <s v="20-01-29"/>
+    <s v="22-01-29"/>
+    <n v="2"/>
+    <n v="9901236089"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2029"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0220"/>
+    <n v="201"/>
+    <s v="Meera Patel"/>
+    <s v="25-01-29"/>
+    <s v="29-01-29"/>
+    <n v="2"/>
+    <n v="9012347190"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0221"/>
+    <n v="204"/>
+    <s v="Nikhil Singh"/>
+    <s v="01-02-29"/>
+    <s v="04-02-29"/>
+    <n v="2"/>
+    <n v="9123457201"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0222"/>
+    <n v="202"/>
+    <s v="Pooja Mehta"/>
+    <s v="05-02-29"/>
+    <s v="08-02-29"/>
+    <n v="2"/>
+    <n v="9234568312"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0223"/>
+    <n v="203"/>
+    <s v="Karthik Rao"/>
+    <s v="10-02-29"/>
+    <s v="13-02-29"/>
+    <n v="4"/>
+    <n v="9345679423"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0224"/>
+    <n v="206"/>
+    <s v="Aisha Kumar"/>
+    <s v="15-02-29"/>
+    <s v="20-02-29"/>
+    <n v="3"/>
+    <n v="9456780534"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2029"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0225"/>
+    <n v="205"/>
+    <s v="Varun Nair"/>
+    <s v="20-02-29"/>
+    <s v="22-02-29"/>
+    <n v="2"/>
+    <n v="9567891645"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2029"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0226"/>
+    <n v="201"/>
+    <s v="Sneha Sharma"/>
+    <s v="25-02-29"/>
+    <s v="01-03-29"/>
+    <n v="2"/>
+    <n v="9678902756"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0227"/>
+    <n v="204"/>
+    <s v="Amit Gupta"/>
+    <s v="01-03-29"/>
+    <s v="05-03-29"/>
+    <n v="2"/>
+    <n v="9789013867"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0228"/>
+    <n v="202"/>
+    <s v="Divya Patel"/>
+    <s v="05-03-29"/>
+    <s v="08-03-29"/>
+    <n v="2"/>
+    <n v="9890124978"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0229"/>
+    <n v="203"/>
+    <s v="Rohan Singh"/>
+    <s v="10-03-29"/>
+    <s v="14-03-29"/>
+    <n v="4"/>
+    <n v="9901236089"/>
+    <n v="14796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0230"/>
+    <n v="206"/>
+    <s v="Ananya Mehta"/>
+    <s v="15-03-29"/>
+    <s v="18-03-29"/>
+    <n v="3"/>
+    <n v="9012347190"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0231"/>
+    <n v="205"/>
+    <s v="Sanjay Rao"/>
+    <s v="20-03-29"/>
+    <s v="23-03-29"/>
+    <n v="2"/>
+    <n v="9123457201"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0232"/>
+    <n v="201"/>
+    <s v="Priya Kumar"/>
+    <s v="25-03-29"/>
+    <s v="27-03-29"/>
+    <n v="2"/>
+    <n v="9234568312"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2029"/>
+    <x v="2"/>
+    <n v="3"/>
+    <s v="Q1"/>
+  </r>
+  <r>
+    <s v="BK0233"/>
+    <n v="204"/>
+    <s v="Aditya Nair"/>
+    <s v="01-04-29"/>
+    <s v="04-04-29"/>
+    <n v="2"/>
+    <n v="9345679423"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0234"/>
+    <n v="202"/>
+    <s v="Kavya Sharma"/>
+    <s v="05-04-29"/>
+    <s v="09-04-29"/>
+    <n v="2"/>
+    <n v="9456780534"/>
+    <n v="9996"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0235"/>
+    <n v="203"/>
+    <s v="Neha Gupta"/>
+    <s v="10-04-29"/>
+    <s v="12-04-29"/>
+    <n v="4"/>
+    <n v="9567891645"/>
+    <n v="7398"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2029"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0236"/>
+    <n v="206"/>
+    <s v="Rahul Patel"/>
+    <s v="15-04-29"/>
+    <s v="18-04-29"/>
+    <n v="3"/>
+    <n v="9678902756"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0237"/>
+    <n v="205"/>
+    <s v="Meera Singh"/>
+    <s v="20-04-29"/>
+    <s v="22-04-29"/>
+    <n v="2"/>
+    <n v="9789013867"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2029"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0238"/>
+    <n v="201"/>
+    <s v="Nikhil Mehta"/>
+    <s v="25-04-29"/>
+    <s v="29-04-29"/>
+    <n v="2"/>
+    <n v="9890124978"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="3"/>
+    <n v="4"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0239"/>
+    <n v="204"/>
+    <s v="Pooja Rao"/>
+    <s v="01-05-29"/>
+    <s v="05-05-29"/>
+    <n v="2"/>
+    <n v="9901236089"/>
+    <n v="16796"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0240"/>
+    <n v="202"/>
+    <s v="Karthik Kumar"/>
+    <s v="05-05-29"/>
+    <s v="08-05-29"/>
+    <n v="2"/>
+    <n v="9012347190"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0241"/>
+    <n v="203"/>
+    <s v="Aisha Nair"/>
+    <s v="10-05-29"/>
+    <s v="13-05-29"/>
+    <n v="4"/>
+    <n v="9123457201"/>
+    <n v="11097"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0242"/>
+    <n v="206"/>
+    <s v="Varun Sharma"/>
+    <s v="15-05-29"/>
+    <s v="20-05-29"/>
+    <n v="3"/>
+    <n v="9234568312"/>
+    <n v="29995"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="2029"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0243"/>
+    <n v="205"/>
+    <s v="Sneha Gupta"/>
+    <s v="20-05-29"/>
+    <s v="22-05-29"/>
+    <n v="2"/>
+    <n v="9345679423"/>
+    <n v="4398"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2029"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0244"/>
+    <n v="201"/>
+    <s v="Amit Patel"/>
+    <s v="25-05-29"/>
+    <s v="29-05-29"/>
+    <n v="2"/>
+    <n v="9456780534"/>
+    <n v="11596"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="4"/>
+    <n v="5"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0245"/>
+    <n v="204"/>
+    <s v="Divya Singh"/>
+    <s v="01-06-29"/>
+    <s v="04-06-29"/>
+    <n v="2"/>
+    <n v="9567891645"/>
+    <n v="12597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0246"/>
+    <n v="202"/>
+    <s v="Rohan Mehta"/>
+    <s v="05-06-29"/>
+    <s v="08-06-29"/>
+    <n v="2"/>
+    <n v="9678902756"/>
+    <n v="7497"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0247"/>
+    <n v="203"/>
+    <s v="Ananya Rao"/>
+    <s v="10-06-29"/>
+    <s v="14-06-29"/>
+    <n v="4"/>
+    <n v="9789013867"/>
+    <n v="14796"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="2029"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0248"/>
+    <n v="206"/>
+    <s v="Sanjay Kumar"/>
+    <s v="15-06-29"/>
+    <s v="18-06-29"/>
+    <n v="3"/>
+    <n v="9890124978"/>
+    <n v="17997"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0249"/>
+    <n v="205"/>
+    <s v="Priya Nair"/>
+    <s v="20-06-29"/>
+    <s v="23-06-29"/>
+    <n v="2"/>
+    <n v="9901236089"/>
+    <n v="6597"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="2029"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+  <r>
+    <s v="BK0250"/>
+    <n v="201"/>
+    <s v="Aditya Sharma"/>
+    <s v="25-06-29"/>
+    <s v="27-06-29"/>
+    <n v="2"/>
+    <n v="9012347190"/>
+    <n v="5798"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2029"/>
+    <x v="5"/>
+    <n v="6"/>
+    <s v="Q2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="5">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A15:A16" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="12">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="16">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="5" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="22" tableBorderDxfId="32">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="21">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="3">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="20">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="2">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="19">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="1">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="18">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="0">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="17">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3662,6 +8219,243 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED407872-522D-47C6-B7A0-4E6C0D2A76DE}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16">
+        <v>2835926</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" s="16">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" s="16">
+        <v>11343.704</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B21" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="15">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="15">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B24" s="15">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="15">
+        <v>3.0960000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{845A94EE-9C2D-4ED1-9459-BE9FCC0CB032}">
+  <dimension ref="A3:B16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>918</v>
+      </c>
+      <c r="B4" s="15">
+        <v>232633</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>919</v>
+      </c>
+      <c r="B5" s="15">
+        <v>272827</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>920</v>
+      </c>
+      <c r="B6" s="15">
+        <v>289522</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>921</v>
+      </c>
+      <c r="B7" s="15">
+        <v>262328</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>922</v>
+      </c>
+      <c r="B8" s="15">
+        <v>266327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>923</v>
+      </c>
+      <c r="B9" s="15">
+        <v>290323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="B10" s="15">
+        <v>194047</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="B11" s="15">
+        <v>195545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>926</v>
+      </c>
+      <c r="B12" s="15">
+        <v>191747</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>927</v>
+      </c>
+      <c r="B13" s="15">
+        <v>213941</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="18" t="s">
+        <v>928</v>
+      </c>
+      <c r="B14" s="15">
+        <v>226341</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="18" t="s">
+        <v>929</v>
+      </c>
+      <c r="B15" s="15">
+        <v>200345</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B16" s="15">
+        <v>2835926</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDD515C-FF03-47FA-A66B-60F1EAC984C4}">
   <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CECC7F-B6D4-4B9A-8FCA-5AC4DBBB9282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93727ABA-3361-400D-9F58-A931E425F06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="1" activeTab="1" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
     <sheet name="Monthly Revenue Trend" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Payment Status Chart" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId4"/>
+    <pivotCache cacheId="7" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="930">
   <si>
     <t>BookingID</t>
   </si>
@@ -3467,6 +3468,1060 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Monthly Revenue Trend!PivotTable6</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Monthly Revenue Trend</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Monthly Revenue Trend'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Monthly Revenue Trend'!$A$4:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monthly Revenue Trend'!$B$4:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>232633</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>272827</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>289522</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>262328</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>266327</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>290323</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>194047</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>195545</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>191747</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>213941</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>226341</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>200345</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1ECC-464E-804C-600AFC926066}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1350862143"/>
+        <c:axId val="1350858303"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1350862143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350858303"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1350858303"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350862143"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21519496-6861-1EA1-7BBD-5158CC49B5F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46188.716442129633" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="250" xr:uid="{ABC0FC96-CD6A-4AE4-9F1C-C79E4709B301}">
   <cacheSource type="worksheet">
@@ -7546,7 +8601,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -7597,7 +8652,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -7659,7 +8714,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A15:A16" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -7704,7 +8759,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -7749,7 +8804,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -7794,7 +8849,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -7877,6 +8932,74 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -8452,10 +9575,57 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43145B0-5EAA-4625-86B1-2B343EA48E35}">
+  <dimension ref="A3:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="15">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="15">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B6" s="15">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDD515C-FF03-47FA-A66B-60F1EAC984C4}">
   <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93727ABA-3361-400D-9F58-A931E425F06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B95262-340A-4E22-AD27-6AB33F72F97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="1" activeTab="1" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="1" activeTab="2" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -3938,7 +3938,429 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Payment Status Chart!PivotTable7</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Paid vs Pending</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Payment Status Chart'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Payment Status Chart'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Paid</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pending</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Payment Status Chart'!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-02BF-429E-BD24-DA10A5BC4D36}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4481,6 +4903,525 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -4502,6 +5443,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21519496-6861-1EA1-7BBD-5158CC49B5F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF225213-5D12-EE43-4967-E33C5EE55AF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8957,7 +9939,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -9001,6 +9983,17 @@
   <dataFields count="1">
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -9622,6 +10615,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B95262-340A-4E22-AD27-6AB33F72F97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32695C68-4BA0-40B9-A587-CEB8A1243EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="1" activeTab="2" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="3" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
     <sheet name="Monthly Revenue Trend" sheetId="4" r:id="rId2"/>
     <sheet name="Payment Status Chart" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Room-wise Revenue" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId5"/>
+    <pivotCache cacheId="9" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="930">
   <si>
     <t>BookingID</t>
   </si>
@@ -4320,6 +4321,413 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Room-wise Revenue!PivotTable8</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Revenue by Room</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Room-wise Revenue'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Room-wise Revenue'!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>206</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Room-wise Revenue'!$B$4:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>379769</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>332367</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>484569</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>566865</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>226497</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>845859</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-10DA-4D94-B4EF-36AE8450AE6D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1350909663"/>
+        <c:axId val="1350911103"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1350909663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350911103"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1350911103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350909663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4361,6 +4769,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5422,6 +5870,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -5504,6 +6455,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>336550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6DDF0AC-89E4-A40E-994E-C489836DD34A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46188.716442129633" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="250" xr:uid="{ABC0FC96-CD6A-4AE4-9F1C-C79E4709B301}">
   <cacheSource type="worksheet">
@@ -5514,7 +6506,14 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="RoomNo" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="201" maxValue="206"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="201" maxValue="206" count="6">
+        <n v="201"/>
+        <n v="203"/>
+        <n v="205"/>
+        <n v="204"/>
+        <n v="202"/>
+        <n v="206"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="GuestName" numFmtId="0">
       <sharedItems/>
@@ -5581,7 +6580,7 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="250">
   <r>
     <s v="BK0001"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Rahul Sharma"/>
     <s v="05-01-26"/>
     <s v="08-01-26"/>
@@ -5597,7 +6596,7 @@
   </r>
   <r>
     <s v="BK0002"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Priya Patel"/>
     <s v="10-01-26"/>
     <s v="13-01-26"/>
@@ -5613,7 +6612,7 @@
   </r>
   <r>
     <s v="BK0003"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Amit Kumar"/>
     <s v="15-01-26"/>
     <s v="17-01-26"/>
@@ -5629,7 +6628,7 @@
   </r>
   <r>
     <s v="BK0004"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Sneha Reddy"/>
     <s v="20-01-26"/>
     <s v="24-01-26"/>
@@ -5645,7 +6644,7 @@
   </r>
   <r>
     <s v="BK0005"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Vikram Gupta"/>
     <s v="25-01-26"/>
     <s v="28-01-26"/>
@@ -5661,7 +6660,7 @@
   </r>
   <r>
     <s v="BK0006"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Meera Nair"/>
     <s v="01-02-26"/>
     <s v="04-02-26"/>
@@ -5677,7 +6676,7 @@
   </r>
   <r>
     <s v="BK0007"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Aditya Singh"/>
     <s v="05-02-26"/>
     <s v="07-02-26"/>
@@ -5693,7 +6692,7 @@
   </r>
   <r>
     <s v="BK0008"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Kavya Rao"/>
     <s v="10-02-26"/>
     <s v="14-02-26"/>
@@ -5709,7 +6708,7 @@
   </r>
   <r>
     <s v="BK0009"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Rohan Mehta"/>
     <s v="15-02-26"/>
     <s v="18-02-26"/>
@@ -5725,7 +6724,7 @@
   </r>
   <r>
     <s v="BK0010"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Divya Kapoor"/>
     <s v="20-02-26"/>
     <s v="22-02-26"/>
@@ -5741,7 +6740,7 @@
   </r>
   <r>
     <s v="BK0011"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Neha Jain"/>
     <s v="01-03-26"/>
     <s v="04-03-26"/>
@@ -5757,7 +6756,7 @@
   </r>
   <r>
     <s v="BK0012"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Arjun Verma"/>
     <s v="05-03-26"/>
     <s v="09-03-26"/>
@@ -5773,7 +6772,7 @@
   </r>
   <r>
     <s v="BK0013"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Nikhil Das"/>
     <s v="10-03-26"/>
     <s v="12-03-26"/>
@@ -5789,7 +6788,7 @@
   </r>
   <r>
     <s v="BK0014"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Aisha Bhat"/>
     <s v="15-03-26"/>
     <s v="18-03-26"/>
@@ -5805,7 +6804,7 @@
   </r>
   <r>
     <s v="BK0015"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Sanjay Yadav"/>
     <s v="20-03-26"/>
     <s v="23-03-26"/>
@@ -5821,7 +6820,7 @@
   </r>
   <r>
     <s v="BK0016"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Pooja Iyer"/>
     <s v="25-03-26"/>
     <s v="29-03-26"/>
@@ -5837,7 +6836,7 @@
   </r>
   <r>
     <s v="BK0017"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Ishita Rao"/>
     <s v="01-04-26"/>
     <s v="03-04-26"/>
@@ -5853,7 +6852,7 @@
   </r>
   <r>
     <s v="BK0018"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Karthik Sharma"/>
     <s v="05-04-26"/>
     <s v="08-04-26"/>
@@ -5869,7 +6868,7 @@
   </r>
   <r>
     <s v="BK0019"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Ananya Gupta"/>
     <s v="10-04-26"/>
     <s v="14-04-26"/>
@@ -5885,7 +6884,7 @@
   </r>
   <r>
     <s v="BK0020"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Varun Kumar"/>
     <s v="15-04-26"/>
     <s v="18-04-26"/>
@@ -5901,7 +6900,7 @@
   </r>
   <r>
     <s v="BK0021"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Meera Singh"/>
     <s v="20-04-26"/>
     <s v="22-04-26"/>
@@ -5917,7 +6916,7 @@
   </r>
   <r>
     <s v="BK0022"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Rahul Jain"/>
     <s v="25-04-26"/>
     <s v="28-04-26"/>
@@ -5933,7 +6932,7 @@
   </r>
   <r>
     <s v="BK0023"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Divya Patel"/>
     <s v="01-05-26"/>
     <s v="04-05-26"/>
@@ -5949,7 +6948,7 @@
   </r>
   <r>
     <s v="BK0024"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Nikhil Sharma"/>
     <s v="05-05-26"/>
     <s v="07-05-26"/>
@@ -5965,7 +6964,7 @@
   </r>
   <r>
     <s v="BK0025"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Sneha Kapoor"/>
     <s v="10-05-26"/>
     <s v="13-05-26"/>
@@ -5981,7 +6980,7 @@
   </r>
   <r>
     <s v="BK0026"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Amit Verma"/>
     <s v="15-05-26"/>
     <s v="19-05-26"/>
@@ -5997,7 +6996,7 @@
   </r>
   <r>
     <s v="BK0027"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Priya Rao"/>
     <s v="20-05-26"/>
     <s v="23-05-26"/>
@@ -6013,7 +7012,7 @@
   </r>
   <r>
     <s v="BK0028"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Rohan Gupta"/>
     <s v="25-05-26"/>
     <s v="27-05-26"/>
@@ -6029,7 +7028,7 @@
   </r>
   <r>
     <s v="BK0029"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Ananya Nair"/>
     <s v="01-06-26"/>
     <s v="05-06-26"/>
@@ -6045,7 +7044,7 @@
   </r>
   <r>
     <s v="BK0030"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Sanjay Das"/>
     <s v="05-06-26"/>
     <s v="08-06-26"/>
@@ -6061,7 +7060,7 @@
   </r>
   <r>
     <s v="BK0031"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Kavya Mehta"/>
     <s v="10-06-26"/>
     <s v="12-06-26"/>
@@ -6077,7 +7076,7 @@
   </r>
   <r>
     <s v="BK0032"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Arjun Singh"/>
     <s v="15-06-26"/>
     <s v="20-06-26"/>
@@ -6093,7 +7092,7 @@
   </r>
   <r>
     <s v="BK0033"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Neha Bhat"/>
     <s v="20-06-26"/>
     <s v="22-06-26"/>
@@ -6109,7 +7108,7 @@
   </r>
   <r>
     <s v="BK0034"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Vikram Iyer"/>
     <s v="25-06-26"/>
     <s v="28-06-26"/>
@@ -6125,7 +7124,7 @@
   </r>
   <r>
     <s v="BK0035"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Pooja Sharma"/>
     <s v="01-07-26"/>
     <s v="03-07-26"/>
@@ -6141,7 +7140,7 @@
   </r>
   <r>
     <s v="BK0036"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Aisha Patel"/>
     <s v="05-07-26"/>
     <s v="08-07-26"/>
@@ -6157,7 +7156,7 @@
   </r>
   <r>
     <s v="BK0037"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Karthik Rao"/>
     <s v="10-07-26"/>
     <s v="14-07-26"/>
@@ -6173,7 +7172,7 @@
   </r>
   <r>
     <s v="BK0038"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Divya Gupta"/>
     <s v="15-07-26"/>
     <s v="18-07-26"/>
@@ -6189,7 +7188,7 @@
   </r>
   <r>
     <s v="BK0039"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Aditya Jain"/>
     <s v="20-07-26"/>
     <s v="23-07-26"/>
@@ -6205,7 +7204,7 @@
   </r>
   <r>
     <s v="BK0040"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Meera Verma"/>
     <s v="25-07-26"/>
     <s v="27-07-26"/>
@@ -6221,7 +7220,7 @@
   </r>
   <r>
     <s v="BK0041"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Rahul Nair"/>
     <s v="01-08-26"/>
     <s v="04-08-26"/>
@@ -6237,7 +7236,7 @@
   </r>
   <r>
     <s v="BK0042"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Sneha Das"/>
     <s v="05-08-26"/>
     <s v="09-08-26"/>
@@ -6253,7 +7252,7 @@
   </r>
   <r>
     <s v="BK0043"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Varun Sharma"/>
     <s v="10-08-26"/>
     <s v="13-08-26"/>
@@ -6269,7 +7268,7 @@
   </r>
   <r>
     <s v="BK0044"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Priya Kapoor"/>
     <s v="15-08-26"/>
     <s v="17-08-26"/>
@@ -6285,7 +7284,7 @@
   </r>
   <r>
     <s v="BK0045"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Nikhil Patel"/>
     <s v="20-08-26"/>
     <s v="22-08-26"/>
@@ -6301,7 +7300,7 @@
   </r>
   <r>
     <s v="BK0046"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Amit Gupta"/>
     <s v="25-08-26"/>
     <s v="29-08-26"/>
@@ -6317,7 +7316,7 @@
   </r>
   <r>
     <s v="BK0047"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Ishita Singh"/>
     <s v="01-09-26"/>
     <s v="05-09-26"/>
@@ -6333,7 +7332,7 @@
   </r>
   <r>
     <s v="BK0048"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Rohan Kumar"/>
     <s v="05-09-26"/>
     <s v="08-09-26"/>
@@ -6349,7 +7348,7 @@
   </r>
   <r>
     <s v="BK0049"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Ananya Mehta"/>
     <s v="10-09-26"/>
     <s v="12-09-26"/>
@@ -6365,7 +7364,7 @@
   </r>
   <r>
     <s v="BK0050"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Kavya Jain"/>
     <s v="15-09-26"/>
     <s v="19-09-26"/>
@@ -6381,7 +7380,7 @@
   </r>
   <r>
     <s v="BK0051"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Arjun Rao"/>
     <s v="20-09-26"/>
     <s v="23-09-26"/>
@@ -6397,7 +7396,7 @@
   </r>
   <r>
     <s v="BK0052"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Priya Sharma"/>
     <s v="25-09-26"/>
     <s v="28-09-26"/>
@@ -6413,7 +7412,7 @@
   </r>
   <r>
     <s v="BK0053"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Vikram Patel"/>
     <s v="01-10-26"/>
     <s v="04-10-26"/>
@@ -6429,7 +7428,7 @@
   </r>
   <r>
     <s v="BK0054"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Sneha Gupta"/>
     <s v="05-10-26"/>
     <s v="08-10-26"/>
@@ -6445,7 +7444,7 @@
   </r>
   <r>
     <s v="BK0055"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Rohan Singh"/>
     <s v="10-10-26"/>
     <s v="14-10-26"/>
@@ -6461,7 +7460,7 @@
   </r>
   <r>
     <s v="BK0056"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Divya Nair"/>
     <s v="15-10-26"/>
     <s v="18-10-26"/>
@@ -6477,7 +7476,7 @@
   </r>
   <r>
     <s v="BK0057"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Amit Mehta"/>
     <s v="20-10-26"/>
     <s v="22-10-26"/>
@@ -6493,7 +7492,7 @@
   </r>
   <r>
     <s v="BK0058"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Kavya Jain"/>
     <s v="25-10-26"/>
     <s v="29-10-26"/>
@@ -6509,7 +7508,7 @@
   </r>
   <r>
     <s v="BK0059"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Aditya Verma"/>
     <s v="01-11-26"/>
     <s v="03-11-26"/>
@@ -6525,7 +7524,7 @@
   </r>
   <r>
     <s v="BK0060"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Neha Kapoor"/>
     <s v="05-11-26"/>
     <s v="09-11-26"/>
@@ -6541,7 +7540,7 @@
   </r>
   <r>
     <s v="BK0061"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Sanjay Kumar"/>
     <s v="10-11-26"/>
     <s v="13-11-26"/>
@@ -6557,7 +7556,7 @@
   </r>
   <r>
     <s v="BK0062"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Ananya Rao"/>
     <s v="15-11-26"/>
     <s v="20-11-26"/>
@@ -6573,7 +7572,7 @@
   </r>
   <r>
     <s v="BK0063"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Rahul Bhat"/>
     <s v="20-11-26"/>
     <s v="23-11-26"/>
@@ -6589,7 +7588,7 @@
   </r>
   <r>
     <s v="BK0064"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Meera Patel"/>
     <s v="25-11-26"/>
     <s v="27-11-26"/>
@@ -6605,7 +7604,7 @@
   </r>
   <r>
     <s v="BK0065"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Nikhil Sharma"/>
     <s v="01-12-26"/>
     <s v="05-12-26"/>
@@ -6621,7 +7620,7 @@
   </r>
   <r>
     <s v="BK0066"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Pooja Gupta"/>
     <s v="05-12-26"/>
     <s v="08-12-26"/>
@@ -6637,7 +7636,7 @@
   </r>
   <r>
     <s v="BK0067"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Karthik Das"/>
     <s v="10-12-26"/>
     <s v="12-12-26"/>
@@ -6653,7 +7652,7 @@
   </r>
   <r>
     <s v="BK0068"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Aisha Singh"/>
     <s v="15-12-26"/>
     <s v="18-12-26"/>
@@ -6669,7 +7668,7 @@
   </r>
   <r>
     <s v="BK0069"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Varun Nair"/>
     <s v="20-12-26"/>
     <s v="22-12-26"/>
@@ -6685,7 +7684,7 @@
   </r>
   <r>
     <s v="BK0070"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Sneha Rao"/>
     <s v="25-12-26"/>
     <s v="29-12-26"/>
@@ -6701,7 +7700,7 @@
   </r>
   <r>
     <s v="BK0071"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Amit Jain"/>
     <s v="01-01-27"/>
     <s v="04-01-27"/>
@@ -6717,7 +7716,7 @@
   </r>
   <r>
     <s v="BK0072"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Divya Sharma"/>
     <s v="05-01-27"/>
     <s v="08-01-27"/>
@@ -6733,7 +7732,7 @@
   </r>
   <r>
     <s v="BK0073"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Rohan Patel"/>
     <s v="10-01-27"/>
     <s v="13-01-27"/>
@@ -6749,7 +7748,7 @@
   </r>
   <r>
     <s v="BK0074"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Priya Kapoor"/>
     <s v="15-01-27"/>
     <s v="17-01-27"/>
@@ -6765,7 +7764,7 @@
   </r>
   <r>
     <s v="BK0075"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Aditya Gupta"/>
     <s v="20-01-27"/>
     <s v="23-01-27"/>
@@ -6781,7 +7780,7 @@
   </r>
   <r>
     <s v="BK0076"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Kavya Verma"/>
     <s v="25-01-27"/>
     <s v="27-01-27"/>
@@ -6797,7 +7796,7 @@
   </r>
   <r>
     <s v="BK0077"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Neha Singh"/>
     <s v="01-02-27"/>
     <s v="05-02-27"/>
@@ -6813,7 +7812,7 @@
   </r>
   <r>
     <s v="BK0078"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Sanjay Mehta"/>
     <s v="05-02-27"/>
     <s v="09-02-27"/>
@@ -6829,7 +7828,7 @@
   </r>
   <r>
     <s v="BK0079"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Ananya Jain"/>
     <s v="10-02-27"/>
     <s v="14-02-27"/>
@@ -6845,7 +7844,7 @@
   </r>
   <r>
     <s v="BK0080"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Rahul Kumar"/>
     <s v="15-02-27"/>
     <s v="18-02-27"/>
@@ -6861,7 +7860,7 @@
   </r>
   <r>
     <s v="BK0081"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Meera Das"/>
     <s v="20-02-27"/>
     <s v="22-02-27"/>
@@ -6877,7 +7876,7 @@
   </r>
   <r>
     <s v="BK0082"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Nikhil Rao"/>
     <s v="25-02-27"/>
     <s v="28-02-27"/>
@@ -6893,7 +7892,7 @@
   </r>
   <r>
     <s v="BK0083"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Pooja Patel"/>
     <s v="01-03-27"/>
     <s v="04-03-27"/>
@@ -6909,7 +7908,7 @@
   </r>
   <r>
     <s v="BK0084"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Karthik Sharma"/>
     <s v="05-03-27"/>
     <s v="08-03-27"/>
@@ -6925,7 +7924,7 @@
   </r>
   <r>
     <s v="BK0085"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Aisha Gupta"/>
     <s v="10-03-27"/>
     <s v="13-03-27"/>
@@ -6941,7 +7940,7 @@
   </r>
   <r>
     <s v="BK0086"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Varun Singh"/>
     <s v="15-03-27"/>
     <s v="20-03-27"/>
@@ -6957,7 +7956,7 @@
   </r>
   <r>
     <s v="BK0087"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Sneha Kapoor"/>
     <s v="20-03-27"/>
     <s v="22-03-27"/>
@@ -6973,7 +7972,7 @@
   </r>
   <r>
     <s v="BK0088"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Amit Nair"/>
     <s v="25-03-27"/>
     <s v="29-03-27"/>
@@ -6989,7 +7988,7 @@
   </r>
   <r>
     <s v="BK0089"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Divya Rao"/>
     <s v="01-04-27"/>
     <s v="03-04-27"/>
@@ -7005,7 +8004,7 @@
   </r>
   <r>
     <s v="BK0090"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Rohan Jain"/>
     <s v="05-04-27"/>
     <s v="08-04-27"/>
@@ -7021,7 +8020,7 @@
   </r>
   <r>
     <s v="BK0091"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Priya Verma"/>
     <s v="10-04-27"/>
     <s v="14-04-27"/>
@@ -7037,7 +8036,7 @@
   </r>
   <r>
     <s v="BK0092"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Aditya Sharma"/>
     <s v="15-04-27"/>
     <s v="18-04-27"/>
@@ -7053,7 +8052,7 @@
   </r>
   <r>
     <s v="BK0093"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Kavya Gupta"/>
     <s v="20-04-27"/>
     <s v="23-04-27"/>
@@ -7069,7 +8068,7 @@
   </r>
   <r>
     <s v="BK0094"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Neha Patel"/>
     <s v="25-04-27"/>
     <s v="27-04-27"/>
@@ -7085,7 +8084,7 @@
   </r>
   <r>
     <s v="BK0095"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Sanjay Singh"/>
     <s v="01-05-27"/>
     <s v="05-05-27"/>
@@ -7101,7 +8100,7 @@
   </r>
   <r>
     <s v="BK0096"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Ananya Mehta"/>
     <s v="05-05-27"/>
     <s v="09-05-27"/>
@@ -7117,7 +8116,7 @@
   </r>
   <r>
     <s v="BK0097"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Rahul Kapoor"/>
     <s v="10-05-27"/>
     <s v="12-05-27"/>
@@ -7133,7 +8132,7 @@
   </r>
   <r>
     <s v="BK0098"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Meera Kumar"/>
     <s v="15-05-27"/>
     <s v="18-05-27"/>
@@ -7149,7 +8148,7 @@
   </r>
   <r>
     <s v="BK0099"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Nikhil Jain"/>
     <s v="20-05-27"/>
     <s v="22-05-27"/>
@@ -7165,7 +8164,7 @@
   </r>
   <r>
     <s v="BK0100"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Pooja Das"/>
     <s v="25-05-27"/>
     <s v="29-05-27"/>
@@ -7181,7 +8180,7 @@
   </r>
   <r>
     <s v="BK0101"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Arjun Sharma"/>
     <s v="01-06-27"/>
     <s v="04-06-27"/>
@@ -7197,7 +8196,7 @@
   </r>
   <r>
     <s v="BK0102"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Priya Gupta"/>
     <s v="05-06-27"/>
     <s v="08-06-27"/>
@@ -7213,7 +8212,7 @@
   </r>
   <r>
     <s v="BK0103"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Rahul Patel"/>
     <s v="10-06-27"/>
     <s v="14-06-27"/>
@@ -7229,7 +8228,7 @@
   </r>
   <r>
     <s v="BK0104"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Sneha Singh"/>
     <s v="15-06-27"/>
     <s v="18-06-27"/>
@@ -7245,7 +8244,7 @@
   </r>
   <r>
     <s v="BK0105"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Amit Rao"/>
     <s v="20-06-27"/>
     <s v="22-06-27"/>
@@ -7261,7 +8260,7 @@
   </r>
   <r>
     <s v="BK0106"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Kavya Jain"/>
     <s v="25-06-27"/>
     <s v="29-06-27"/>
@@ -7277,7 +8276,7 @@
   </r>
   <r>
     <s v="BK0107"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Nikhil Kumar"/>
     <s v="01-07-27"/>
     <s v="03-07-27"/>
@@ -7293,7 +8292,7 @@
   </r>
   <r>
     <s v="BK0108"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Meera Sharma"/>
     <s v="05-07-27"/>
     <s v="09-07-27"/>
@@ -7309,7 +8308,7 @@
   </r>
   <r>
     <s v="BK0109"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Aditya Gupta"/>
     <s v="10-07-27"/>
     <s v="13-07-27"/>
@@ -7325,7 +8324,7 @@
   </r>
   <r>
     <s v="BK0110"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Divya Patel"/>
     <s v="15-07-27"/>
     <s v="20-07-27"/>
@@ -7341,7 +8340,7 @@
   </r>
   <r>
     <s v="BK0111"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Rohan Kapoor"/>
     <s v="20-07-27"/>
     <s v="23-07-27"/>
@@ -7357,7 +8356,7 @@
   </r>
   <r>
     <s v="BK0112"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Ananya Verma"/>
     <s v="25-07-27"/>
     <s v="27-07-27"/>
@@ -7373,7 +8372,7 @@
   </r>
   <r>
     <s v="BK0113"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Sanjay Nair"/>
     <s v="01-08-27"/>
     <s v="05-08-27"/>
@@ -7389,7 +8388,7 @@
   </r>
   <r>
     <s v="BK0114"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Pooja Rao"/>
     <s v="05-08-27"/>
     <s v="08-08-27"/>
@@ -7405,7 +8404,7 @@
   </r>
   <r>
     <s v="BK0115"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Karthik Singh"/>
     <s v="10-08-27"/>
     <s v="12-08-27"/>
@@ -7421,7 +8420,7 @@
   </r>
   <r>
     <s v="BK0116"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Aisha Mehta"/>
     <s v="15-08-27"/>
     <s v="18-08-27"/>
@@ -7437,7 +8436,7 @@
   </r>
   <r>
     <s v="BK0117"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Varun Jain"/>
     <s v="20-08-27"/>
     <s v="22-08-27"/>
@@ -7453,7 +8452,7 @@
   </r>
   <r>
     <s v="BK0118"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Sneha Das"/>
     <s v="25-08-27"/>
     <s v="29-08-27"/>
@@ -7469,7 +8468,7 @@
   </r>
   <r>
     <s v="BK0119"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Amit Sharma"/>
     <s v="01-09-27"/>
     <s v="04-09-27"/>
@@ -7485,7 +8484,7 @@
   </r>
   <r>
     <s v="BK0120"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Divya Gupta"/>
     <s v="05-09-27"/>
     <s v="08-09-27"/>
@@ -7501,7 +8500,7 @@
   </r>
   <r>
     <s v="BK0121"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Rohan Patel"/>
     <s v="10-09-27"/>
     <s v="13-09-27"/>
@@ -7517,7 +8516,7 @@
   </r>
   <r>
     <s v="BK0122"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Ananya Kapoor"/>
     <s v="15-09-27"/>
     <s v="17-09-27"/>
@@ -7533,7 +8532,7 @@
   </r>
   <r>
     <s v="BK0123"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Sanjay Verma"/>
     <s v="20-09-27"/>
     <s v="23-09-27"/>
@@ -7549,7 +8548,7 @@
   </r>
   <r>
     <s v="BK0124"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Pooja Nair"/>
     <s v="25-09-27"/>
     <s v="27-09-27"/>
@@ -7565,7 +8564,7 @@
   </r>
   <r>
     <s v="BK0125"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Karthik Rao"/>
     <s v="01-10-27"/>
     <s v="05-10-27"/>
@@ -7581,7 +8580,7 @@
   </r>
   <r>
     <s v="BK0126"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Aisha Singh"/>
     <s v="05-10-27"/>
     <s v="09-10-27"/>
@@ -7597,7 +8596,7 @@
   </r>
   <r>
     <s v="BK0127"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Varun Mehta"/>
     <s v="10-10-27"/>
     <s v="14-10-27"/>
@@ -7613,7 +8612,7 @@
   </r>
   <r>
     <s v="BK0128"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Sneha Jain"/>
     <s v="15-10-27"/>
     <s v="18-10-27"/>
@@ -7629,7 +8628,7 @@
   </r>
   <r>
     <s v="BK0129"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Amit Das"/>
     <s v="20-10-27"/>
     <s v="22-10-27"/>
@@ -7645,7 +8644,7 @@
   </r>
   <r>
     <s v="BK0130"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Divya Sharma"/>
     <s v="25-10-27"/>
     <s v="29-10-27"/>
@@ -7661,7 +8660,7 @@
   </r>
   <r>
     <s v="BK0131"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Rohan Gupta"/>
     <s v="01-11-27"/>
     <s v="03-11-27"/>
@@ -7677,7 +8676,7 @@
   </r>
   <r>
     <s v="BK0132"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Ananya Patel"/>
     <s v="05-11-27"/>
     <s v="08-11-27"/>
@@ -7693,7 +8692,7 @@
   </r>
   <r>
     <s v="BK0133"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Sanjay Kapoor"/>
     <s v="10-11-27"/>
     <s v="14-11-27"/>
@@ -7709,7 +8708,7 @@
   </r>
   <r>
     <s v="BK0134"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Pooja Verma"/>
     <s v="15-11-27"/>
     <s v="20-11-27"/>
@@ -7725,7 +8724,7 @@
   </r>
   <r>
     <s v="BK0135"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Karthik Nair"/>
     <s v="20-11-27"/>
     <s v="23-11-27"/>
@@ -7741,7 +8740,7 @@
   </r>
   <r>
     <s v="BK0136"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Aisha Rao"/>
     <s v="25-11-27"/>
     <s v="27-11-27"/>
@@ -7757,7 +8756,7 @@
   </r>
   <r>
     <s v="BK0137"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Varun Singh"/>
     <s v="01-12-27"/>
     <s v="05-12-27"/>
@@ -7773,7 +8772,7 @@
   </r>
   <r>
     <s v="BK0138"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Sneha Mehta"/>
     <s v="05-12-27"/>
     <s v="08-12-27"/>
@@ -7789,7 +8788,7 @@
   </r>
   <r>
     <s v="BK0139"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Amit Jain"/>
     <s v="10-12-27"/>
     <s v="13-12-27"/>
@@ -7805,7 +8804,7 @@
   </r>
   <r>
     <s v="BK0140"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Divya Das"/>
     <s v="15-12-27"/>
     <s v="18-12-27"/>
@@ -7821,7 +8820,7 @@
   </r>
   <r>
     <s v="BK0141"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Rohan Sharma"/>
     <s v="20-12-27"/>
     <s v="22-12-27"/>
@@ -7837,7 +8836,7 @@
   </r>
   <r>
     <s v="BK0142"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Ananya Gupta"/>
     <s v="25-12-27"/>
     <s v="29-12-27"/>
@@ -7853,7 +8852,7 @@
   </r>
   <r>
     <s v="BK0143"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Sanjay Patel"/>
     <s v="01-01-28"/>
     <s v="04-01-28"/>
@@ -7869,7 +8868,7 @@
   </r>
   <r>
     <s v="BK0144"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Pooja Kapoor"/>
     <s v="05-01-28"/>
     <s v="09-01-28"/>
@@ -7885,7 +8884,7 @@
   </r>
   <r>
     <s v="BK0145"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Karthik Verma"/>
     <s v="10-01-28"/>
     <s v="12-01-28"/>
@@ -7901,7 +8900,7 @@
   </r>
   <r>
     <s v="BK0146"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Aisha Nair"/>
     <s v="15-01-28"/>
     <s v="18-01-28"/>
@@ -7917,7 +8916,7 @@
   </r>
   <r>
     <s v="BK0147"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Varun Rao"/>
     <s v="20-01-28"/>
     <s v="23-01-28"/>
@@ -7933,7 +8932,7 @@
   </r>
   <r>
     <s v="BK0148"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Sneha Singh"/>
     <s v="25-01-28"/>
     <s v="27-01-28"/>
@@ -7949,7 +8948,7 @@
   </r>
   <r>
     <s v="BK0149"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Amit Mehta"/>
     <s v="01-02-28"/>
     <s v="05-02-28"/>
@@ -7965,7 +8964,7 @@
   </r>
   <r>
     <s v="BK0150"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Divya Jain"/>
     <s v="05-02-28"/>
     <s v="08-02-28"/>
@@ -7981,7 +8980,7 @@
   </r>
   <r>
     <s v="BK0151"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Rahul Nair"/>
     <s v="10-02-28"/>
     <s v="13-02-28"/>
@@ -7997,7 +8996,7 @@
   </r>
   <r>
     <s v="BK0152"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Meera Sharma"/>
     <s v="15-02-28"/>
     <s v="18-02-28"/>
@@ -8013,7 +9012,7 @@
   </r>
   <r>
     <s v="BK0153"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Nikhil Gupta"/>
     <s v="20-02-28"/>
     <s v="22-02-28"/>
@@ -8029,7 +9028,7 @@
   </r>
   <r>
     <s v="BK0154"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Pooja Patel"/>
     <s v="25-02-28"/>
     <s v="29-02-28"/>
@@ -8045,7 +9044,7 @@
   </r>
   <r>
     <s v="BK0155"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Karthik Kapoor"/>
     <s v="01-03-28"/>
     <s v="04-03-28"/>
@@ -8061,7 +9060,7 @@
   </r>
   <r>
     <s v="BK0156"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Aisha Verma"/>
     <s v="05-03-28"/>
     <s v="08-03-28"/>
@@ -8077,7 +9076,7 @@
   </r>
   <r>
     <s v="BK0157"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Varun Jain"/>
     <s v="10-03-28"/>
     <s v="14-03-28"/>
@@ -8093,7 +9092,7 @@
   </r>
   <r>
     <s v="BK0158"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Sneha Das"/>
     <s v="15-03-28"/>
     <s v="20-03-28"/>
@@ -8109,7 +9108,7 @@
   </r>
   <r>
     <s v="BK0159"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Amit Sharma"/>
     <s v="20-03-28"/>
     <s v="23-03-28"/>
@@ -8125,7 +9124,7 @@
   </r>
   <r>
     <s v="BK0160"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Divya Gupta"/>
     <s v="25-03-28"/>
     <s v="27-03-28"/>
@@ -8141,7 +9140,7 @@
   </r>
   <r>
     <s v="BK0161"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Rohan Patel"/>
     <s v="01-04-28"/>
     <s v="05-04-28"/>
@@ -8157,7 +9156,7 @@
   </r>
   <r>
     <s v="BK0162"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Ananya Singh"/>
     <s v="05-04-28"/>
     <s v="09-04-28"/>
@@ -8173,7 +9172,7 @@
   </r>
   <r>
     <s v="BK0163"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Sanjay Mehta"/>
     <s v="10-04-28"/>
     <s v="13-04-28"/>
@@ -8189,7 +9188,7 @@
   </r>
   <r>
     <s v="BK0164"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Priya Rao"/>
     <s v="15-04-28"/>
     <s v="18-04-28"/>
@@ -8205,7 +9204,7 @@
   </r>
   <r>
     <s v="BK0165"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Aditya Kumar"/>
     <s v="20-04-28"/>
     <s v="22-04-28"/>
@@ -8221,7 +9220,7 @@
   </r>
   <r>
     <s v="BK0166"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Kavya Nair"/>
     <s v="25-04-28"/>
     <s v="29-04-28"/>
@@ -8237,7 +9236,7 @@
   </r>
   <r>
     <s v="BK0167"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Neha Sharma"/>
     <s v="01-05-28"/>
     <s v="04-05-28"/>
@@ -8253,7 +9252,7 @@
   </r>
   <r>
     <s v="BK0168"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Rahul Gupta"/>
     <s v="05-05-28"/>
     <s v="08-05-28"/>
@@ -8269,7 +9268,7 @@
   </r>
   <r>
     <s v="BK0169"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Meera Patel"/>
     <s v="10-05-28"/>
     <s v="12-05-28"/>
@@ -8285,7 +9284,7 @@
   </r>
   <r>
     <s v="BK0170"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Nikhil Kapoor"/>
     <s v="15-05-28"/>
     <s v="18-05-28"/>
@@ -8301,7 +9300,7 @@
   </r>
   <r>
     <s v="BK0171"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Pooja Verma"/>
     <s v="20-05-28"/>
     <s v="23-05-28"/>
@@ -8317,7 +9316,7 @@
   </r>
   <r>
     <s v="BK0172"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Karthik Jain"/>
     <s v="25-05-28"/>
     <s v="27-05-28"/>
@@ -8333,7 +9332,7 @@
   </r>
   <r>
     <s v="BK0173"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Aisha Das"/>
     <s v="01-06-28"/>
     <s v="05-06-28"/>
@@ -8349,7 +9348,7 @@
   </r>
   <r>
     <s v="BK0174"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Varun Sharma"/>
     <s v="05-06-28"/>
     <s v="08-06-28"/>
@@ -8365,7 +9364,7 @@
   </r>
   <r>
     <s v="BK0175"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Sneha Gupta"/>
     <s v="10-06-28"/>
     <s v="13-06-28"/>
@@ -8381,7 +9380,7 @@
   </r>
   <r>
     <s v="BK0176"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Amit Patel"/>
     <s v="15-06-28"/>
     <s v="20-06-28"/>
@@ -8397,7 +9396,7 @@
   </r>
   <r>
     <s v="BK0177"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Divya Singh"/>
     <s v="20-06-28"/>
     <s v="22-06-28"/>
@@ -8413,7 +9412,7 @@
   </r>
   <r>
     <s v="BK0178"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Rohan Mehta"/>
     <s v="25-06-28"/>
     <s v="29-06-28"/>
@@ -8429,7 +9428,7 @@
   </r>
   <r>
     <s v="BK0179"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Ananya Rao"/>
     <s v="01-07-28"/>
     <s v="03-07-28"/>
@@ -8445,7 +9444,7 @@
   </r>
   <r>
     <s v="BK0180"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Sanjay Kumar"/>
     <s v="05-07-28"/>
     <s v="08-07-28"/>
@@ -8461,7 +9460,7 @@
   </r>
   <r>
     <s v="BK0181"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Priya Nair"/>
     <s v="10-07-28"/>
     <s v="14-07-28"/>
@@ -8477,7 +9476,7 @@
   </r>
   <r>
     <s v="BK0182"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Aditya Sharma"/>
     <s v="15-07-28"/>
     <s v="18-07-28"/>
@@ -8493,7 +9492,7 @@
   </r>
   <r>
     <s v="BK0183"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Kavya Gupta"/>
     <s v="20-07-28"/>
     <s v="23-07-28"/>
@@ -8509,7 +9508,7 @@
   </r>
   <r>
     <s v="BK0184"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Neha Patel"/>
     <s v="25-07-28"/>
     <s v="27-07-28"/>
@@ -8525,7 +9524,7 @@
   </r>
   <r>
     <s v="BK0185"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Rahul Singh"/>
     <s v="01-08-28"/>
     <s v="05-08-28"/>
@@ -8541,7 +9540,7 @@
   </r>
   <r>
     <s v="BK0186"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Meera Mehta"/>
     <s v="05-08-28"/>
     <s v="09-08-28"/>
@@ -8557,7 +9556,7 @@
   </r>
   <r>
     <s v="BK0187"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Nikhil Rao"/>
     <s v="10-08-28"/>
     <s v="12-08-28"/>
@@ -8573,7 +9572,7 @@
   </r>
   <r>
     <s v="BK0188"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Pooja Kumar"/>
     <s v="15-08-28"/>
     <s v="18-08-28"/>
@@ -8589,7 +9588,7 @@
   </r>
   <r>
     <s v="BK0189"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Karthik Nair"/>
     <s v="20-08-28"/>
     <s v="22-08-28"/>
@@ -8605,7 +9604,7 @@
   </r>
   <r>
     <s v="BK0190"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Aisha Sharma"/>
     <s v="25-08-28"/>
     <s v="29-08-28"/>
@@ -8621,7 +9620,7 @@
   </r>
   <r>
     <s v="BK0191"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Varun Gupta"/>
     <s v="01-09-28"/>
     <s v="04-09-28"/>
@@ -8637,7 +9636,7 @@
   </r>
   <r>
     <s v="BK0192"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Sneha Patel"/>
     <s v="05-09-28"/>
     <s v="08-09-28"/>
@@ -8653,7 +9652,7 @@
   </r>
   <r>
     <s v="BK0193"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Amit Singh"/>
     <s v="10-09-28"/>
     <s v="13-09-28"/>
@@ -8669,7 +9668,7 @@
   </r>
   <r>
     <s v="BK0194"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Divya Mehta"/>
     <s v="15-09-28"/>
     <s v="18-09-28"/>
@@ -8685,7 +9684,7 @@
   </r>
   <r>
     <s v="BK0195"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Rohan Rao"/>
     <s v="20-09-28"/>
     <s v="22-09-28"/>
@@ -8701,7 +9700,7 @@
   </r>
   <r>
     <s v="BK0196"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Ananya Kumar"/>
     <s v="25-09-28"/>
     <s v="29-09-28"/>
@@ -8717,7 +9716,7 @@
   </r>
   <r>
     <s v="BK0197"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Sanjay Nair"/>
     <s v="01-10-28"/>
     <s v="05-10-28"/>
@@ -8733,7 +9732,7 @@
   </r>
   <r>
     <s v="BK0198"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Priya Sharma"/>
     <s v="05-10-28"/>
     <s v="08-10-28"/>
@@ -8749,7 +9748,7 @@
   </r>
   <r>
     <s v="BK0199"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Aditya Gupta"/>
     <s v="10-10-28"/>
     <s v="14-10-28"/>
@@ -8765,7 +9764,7 @@
   </r>
   <r>
     <s v="BK0200"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Kavya Patel"/>
     <s v="15-10-28"/>
     <s v="18-10-28"/>
@@ -8781,7 +9780,7 @@
   </r>
   <r>
     <s v="BK0201"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Neha Kapoor"/>
     <s v="20-10-28"/>
     <s v="23-10-28"/>
@@ -8797,7 +9796,7 @@
   </r>
   <r>
     <s v="BK0202"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Rahul Sharma"/>
     <s v="25-10-28"/>
     <s v="27-10-28"/>
@@ -8813,7 +9812,7 @@
   </r>
   <r>
     <s v="BK0203"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Meera Gupta"/>
     <s v="01-11-28"/>
     <s v="05-11-28"/>
@@ -8829,7 +9828,7 @@
   </r>
   <r>
     <s v="BK0204"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Nikhil Patel"/>
     <s v="05-11-28"/>
     <s v="08-11-28"/>
@@ -8845,7 +9844,7 @@
   </r>
   <r>
     <s v="BK0205"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Pooja Singh"/>
     <s v="10-11-28"/>
     <s v="13-11-28"/>
@@ -8861,7 +9860,7 @@
   </r>
   <r>
     <s v="BK0206"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Karthik Mehta"/>
     <s v="15-11-28"/>
     <s v="20-11-28"/>
@@ -8877,7 +9876,7 @@
   </r>
   <r>
     <s v="BK0207"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Aisha Rao"/>
     <s v="20-11-28"/>
     <s v="22-11-28"/>
@@ -8893,7 +9892,7 @@
   </r>
   <r>
     <s v="BK0208"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Varun Kumar"/>
     <s v="25-11-28"/>
     <s v="29-11-28"/>
@@ -8909,7 +9908,7 @@
   </r>
   <r>
     <s v="BK0209"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Sneha Nair"/>
     <s v="01-12-28"/>
     <s v="04-12-28"/>
@@ -8925,7 +9924,7 @@
   </r>
   <r>
     <s v="BK0210"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Amit Sharma"/>
     <s v="05-12-28"/>
     <s v="08-12-28"/>
@@ -8941,7 +9940,7 @@
   </r>
   <r>
     <s v="BK0211"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Divya Gupta"/>
     <s v="10-12-28"/>
     <s v="14-12-28"/>
@@ -8957,7 +9956,7 @@
   </r>
   <r>
     <s v="BK0212"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Rohan Patel"/>
     <s v="15-12-28"/>
     <s v="18-12-28"/>
@@ -8973,7 +9972,7 @@
   </r>
   <r>
     <s v="BK0213"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Ananya Singh"/>
     <s v="20-12-28"/>
     <s v="23-12-28"/>
@@ -8989,7 +9988,7 @@
   </r>
   <r>
     <s v="BK0214"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Sanjay Mehta"/>
     <s v="25-12-28"/>
     <s v="27-12-28"/>
@@ -9005,7 +10004,7 @@
   </r>
   <r>
     <s v="BK0215"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Priya Rao"/>
     <s v="01-01-29"/>
     <s v="05-01-29"/>
@@ -9021,7 +10020,7 @@
   </r>
   <r>
     <s v="BK0216"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Aditya Kumar"/>
     <s v="05-01-29"/>
     <s v="09-01-29"/>
@@ -9037,7 +10036,7 @@
   </r>
   <r>
     <s v="BK0217"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Kavya Nair"/>
     <s v="10-01-29"/>
     <s v="12-01-29"/>
@@ -9053,7 +10052,7 @@
   </r>
   <r>
     <s v="BK0218"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Neha Sharma"/>
     <s v="15-01-29"/>
     <s v="18-01-29"/>
@@ -9069,7 +10068,7 @@
   </r>
   <r>
     <s v="BK0219"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Rahul Gupta"/>
     <s v="20-01-29"/>
     <s v="22-01-29"/>
@@ -9085,7 +10084,7 @@
   </r>
   <r>
     <s v="BK0220"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Meera Patel"/>
     <s v="25-01-29"/>
     <s v="29-01-29"/>
@@ -9101,7 +10100,7 @@
   </r>
   <r>
     <s v="BK0221"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Nikhil Singh"/>
     <s v="01-02-29"/>
     <s v="04-02-29"/>
@@ -9117,7 +10116,7 @@
   </r>
   <r>
     <s v="BK0222"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Pooja Mehta"/>
     <s v="05-02-29"/>
     <s v="08-02-29"/>
@@ -9133,7 +10132,7 @@
   </r>
   <r>
     <s v="BK0223"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Karthik Rao"/>
     <s v="10-02-29"/>
     <s v="13-02-29"/>
@@ -9149,7 +10148,7 @@
   </r>
   <r>
     <s v="BK0224"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Aisha Kumar"/>
     <s v="15-02-29"/>
     <s v="20-02-29"/>
@@ -9165,7 +10164,7 @@
   </r>
   <r>
     <s v="BK0225"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Varun Nair"/>
     <s v="20-02-29"/>
     <s v="22-02-29"/>
@@ -9181,7 +10180,7 @@
   </r>
   <r>
     <s v="BK0226"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Sneha Sharma"/>
     <s v="25-02-29"/>
     <s v="01-03-29"/>
@@ -9197,7 +10196,7 @@
   </r>
   <r>
     <s v="BK0227"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Amit Gupta"/>
     <s v="01-03-29"/>
     <s v="05-03-29"/>
@@ -9213,7 +10212,7 @@
   </r>
   <r>
     <s v="BK0228"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Divya Patel"/>
     <s v="05-03-29"/>
     <s v="08-03-29"/>
@@ -9229,7 +10228,7 @@
   </r>
   <r>
     <s v="BK0229"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Rohan Singh"/>
     <s v="10-03-29"/>
     <s v="14-03-29"/>
@@ -9245,7 +10244,7 @@
   </r>
   <r>
     <s v="BK0230"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Ananya Mehta"/>
     <s v="15-03-29"/>
     <s v="18-03-29"/>
@@ -9261,7 +10260,7 @@
   </r>
   <r>
     <s v="BK0231"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Sanjay Rao"/>
     <s v="20-03-29"/>
     <s v="23-03-29"/>
@@ -9277,7 +10276,7 @@
   </r>
   <r>
     <s v="BK0232"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Priya Kumar"/>
     <s v="25-03-29"/>
     <s v="27-03-29"/>
@@ -9293,7 +10292,7 @@
   </r>
   <r>
     <s v="BK0233"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Aditya Nair"/>
     <s v="01-04-29"/>
     <s v="04-04-29"/>
@@ -9309,7 +10308,7 @@
   </r>
   <r>
     <s v="BK0234"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Kavya Sharma"/>
     <s v="05-04-29"/>
     <s v="09-04-29"/>
@@ -9325,7 +10324,7 @@
   </r>
   <r>
     <s v="BK0235"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Neha Gupta"/>
     <s v="10-04-29"/>
     <s v="12-04-29"/>
@@ -9341,7 +10340,7 @@
   </r>
   <r>
     <s v="BK0236"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Rahul Patel"/>
     <s v="15-04-29"/>
     <s v="18-04-29"/>
@@ -9357,7 +10356,7 @@
   </r>
   <r>
     <s v="BK0237"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Meera Singh"/>
     <s v="20-04-29"/>
     <s v="22-04-29"/>
@@ -9373,7 +10372,7 @@
   </r>
   <r>
     <s v="BK0238"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Nikhil Mehta"/>
     <s v="25-04-29"/>
     <s v="29-04-29"/>
@@ -9389,7 +10388,7 @@
   </r>
   <r>
     <s v="BK0239"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Pooja Rao"/>
     <s v="01-05-29"/>
     <s v="05-05-29"/>
@@ -9405,7 +10404,7 @@
   </r>
   <r>
     <s v="BK0240"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Karthik Kumar"/>
     <s v="05-05-29"/>
     <s v="08-05-29"/>
@@ -9421,7 +10420,7 @@
   </r>
   <r>
     <s v="BK0241"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Aisha Nair"/>
     <s v="10-05-29"/>
     <s v="13-05-29"/>
@@ -9437,7 +10436,7 @@
   </r>
   <r>
     <s v="BK0242"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Varun Sharma"/>
     <s v="15-05-29"/>
     <s v="20-05-29"/>
@@ -9453,7 +10452,7 @@
   </r>
   <r>
     <s v="BK0243"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Sneha Gupta"/>
     <s v="20-05-29"/>
     <s v="22-05-29"/>
@@ -9469,7 +10468,7 @@
   </r>
   <r>
     <s v="BK0244"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Amit Patel"/>
     <s v="25-05-29"/>
     <s v="29-05-29"/>
@@ -9485,7 +10484,7 @@
   </r>
   <r>
     <s v="BK0245"/>
-    <n v="204"/>
+    <x v="3"/>
     <s v="Divya Singh"/>
     <s v="01-06-29"/>
     <s v="04-06-29"/>
@@ -9501,7 +10500,7 @@
   </r>
   <r>
     <s v="BK0246"/>
-    <n v="202"/>
+    <x v="4"/>
     <s v="Rohan Mehta"/>
     <s v="05-06-29"/>
     <s v="08-06-29"/>
@@ -9517,7 +10516,7 @@
   </r>
   <r>
     <s v="BK0247"/>
-    <n v="203"/>
+    <x v="1"/>
     <s v="Ananya Rao"/>
     <s v="10-06-29"/>
     <s v="14-06-29"/>
@@ -9533,7 +10532,7 @@
   </r>
   <r>
     <s v="BK0248"/>
-    <n v="206"/>
+    <x v="5"/>
     <s v="Sanjay Kumar"/>
     <s v="15-06-29"/>
     <s v="18-06-29"/>
@@ -9549,7 +10548,7 @@
   </r>
   <r>
     <s v="BK0249"/>
-    <n v="205"/>
+    <x v="2"/>
     <s v="Priya Nair"/>
     <s v="20-06-29"/>
     <s v="23-06-29"/>
@@ -9565,7 +10564,7 @@
   </r>
   <r>
     <s v="BK0250"/>
-    <n v="201"/>
+    <x v="0"/>
     <s v="Aditya Sharma"/>
     <s v="25-06-29"/>
     <s v="27-06-29"/>
@@ -9583,7 +10582,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -9634,7 +10633,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -9696,7 +10695,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A15:A16" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -9741,7 +10740,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -9786,7 +10785,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -9831,7 +10830,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -9939,7 +10938,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -9982,6 +10981,90 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">
@@ -10620,6 +11703,85 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E86FBE-A6BE-4C10-8B1A-63ED78EBA71C}">
+  <dimension ref="A3:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18">
+        <v>201</v>
+      </c>
+      <c r="B4" s="15">
+        <v>379769</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18">
+        <v>202</v>
+      </c>
+      <c r="B5" s="15">
+        <v>332367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18">
+        <v>203</v>
+      </c>
+      <c r="B6" s="15">
+        <v>484569</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18">
+        <v>204</v>
+      </c>
+      <c r="B7" s="15">
+        <v>566865</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="18">
+        <v>205</v>
+      </c>
+      <c r="B8" s="15">
+        <v>226497</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="18">
+        <v>206</v>
+      </c>
+      <c r="B9" s="15">
+        <v>845859</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B10" s="15">
+        <v>2835926</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDD515C-FF03-47FA-A66B-60F1EAC984C4}">
   <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32695C68-4BA0-40B9-A587-CEB8A1243EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593C75AC-E963-44DF-9EF5-8C237A6B00AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="3" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="3" activeTab="4" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
     <sheet name="Monthly Revenue Trend" sheetId="4" r:id="rId2"/>
     <sheet name="Payment Status Chart" sheetId="5" r:id="rId3"/>
     <sheet name="Room-wise Revenue" sheetId="6" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Room-wise Bookings" sheetId="7" r:id="rId5"/>
+    <sheet name="Data" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId6"/>
+    <pivotCache cacheId="10" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="930">
   <si>
     <t>BookingID</t>
   </si>
@@ -2984,48 +2985,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="21">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -4728,6 +4693,412 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Room-wise Bookings!PivotTable9</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Bookings per Room</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Room-wise Bookings'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Room-wise Bookings'!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>206</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Room-wise Bookings'!$B$4:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>41</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6AA2-46FB-8C11-E42B4B823033}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1289281775"/>
+        <c:axId val="1289291855"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1289281775"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1289291855"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1289291855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1289281775"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4809,6 +5180,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6373,6 +6784,511 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -6496,6 +7412,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66E3AFFF-1C0D-2C3F-70AB-253A914F14B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46188.716442129633" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="250" xr:uid="{ABC0FC96-CD6A-4AE4-9F1C-C79E4709B301}">
   <cacheSource type="worksheet">
@@ -10582,7 +11539,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -10616,7 +11573,7 @@
     <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -10633,7 +11590,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -10678,7 +11635,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -10695,7 +11652,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A15:A16" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -10723,7 +11680,7 @@
     <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="12">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -10740,7 +11697,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -10768,7 +11725,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="15">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -10785,7 +11742,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -10813,7 +11770,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="16">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -10830,7 +11787,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -10938,7 +11895,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -11006,7 +11963,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -11089,32 +12046,116 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F432DA-19F0-4D22-A63C-E6256DB1F83D}" name="PivotTable9" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="22" tableBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="10" tableBorderDxfId="20">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="9">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="20">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="8">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="19">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="7">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="18">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="6">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="17">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="5">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11782,6 +12823,85 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4501FBA7-B240-4BCD-BB90-9ED916FDB84F}">
+  <dimension ref="A3:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18">
+        <v>201</v>
+      </c>
+      <c r="B4" s="15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18">
+        <v>202</v>
+      </c>
+      <c r="B5" s="15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18">
+        <v>203</v>
+      </c>
+      <c r="B6" s="15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18">
+        <v>204</v>
+      </c>
+      <c r="B7" s="15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="18">
+        <v>205</v>
+      </c>
+      <c r="B8" s="15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="18">
+        <v>206</v>
+      </c>
+      <c r="B9" s="15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B10" s="15">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDD515C-FF03-47FA-A66B-60F1EAC984C4}">
   <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593C75AC-E963-44DF-9EF5-8C237A6B00AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20670CC0-A132-42D7-92F6-6019475211F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="3" activeTab="4" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="4" activeTab="6" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -18,11 +18,12 @@
     <sheet name="Payment Status Chart" sheetId="5" r:id="rId3"/>
     <sheet name="Room-wise Revenue" sheetId="6" r:id="rId4"/>
     <sheet name="Room-wise Bookings" sheetId="7" r:id="rId5"/>
-    <sheet name="Data" sheetId="1" r:id="rId6"/>
+    <sheet name="Guest Capacity Analysis" sheetId="9" r:id="rId6"/>
+    <sheet name="Data" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId7"/>
+    <pivotCache cacheId="12" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="930">
   <si>
     <t>BookingID</t>
   </si>
@@ -5099,6 +5100,396 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Guest Capacity Analysis!PivotTable10</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Guest Capacity</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Guest Capacity Analysis'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Guest Capacity Analysis'!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Guest Capacity Analysis'!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3F88-4E10-8D0E-F5F61056B968}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1350863103"/>
+        <c:axId val="1350868383"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1350863103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350868383"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1350868383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350863103"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -5220,6 +5611,46 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7289,6 +7720,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -7453,6 +8387,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0F896E7-BA4B-41DE-7F0D-8FD9EE46B9E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46188.716442129633" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="250" xr:uid="{ABC0FC96-CD6A-4AE4-9F1C-C79E4709B301}">
   <cacheSource type="worksheet">
@@ -7482,7 +8457,11 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Guests" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="4"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="4" count="3">
+        <n v="2"/>
+        <n v="4"/>
+        <n v="3"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Phone" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="9012345678" maxValue="9903456789"/>
@@ -7541,7 +8520,7 @@
     <s v="Rahul Sharma"/>
     <s v="05-01-26"/>
     <s v="08-01-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9876543210"/>
     <n v="8697"/>
     <x v="0"/>
@@ -7557,7 +8536,7 @@
     <s v="Priya Patel"/>
     <s v="10-01-26"/>
     <s v="13-01-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9123456789"/>
     <n v="11097"/>
     <x v="1"/>
@@ -7573,7 +8552,7 @@
     <s v="Amit Kumar"/>
     <s v="15-01-26"/>
     <s v="17-01-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345678901"/>
     <n v="4398"/>
     <x v="0"/>
@@ -7589,7 +8568,7 @@
     <s v="Sneha Reddy"/>
     <s v="20-01-26"/>
     <s v="24-01-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456789012"/>
     <n v="16796"/>
     <x v="0"/>
@@ -7605,7 +8584,7 @@
     <s v="Vikram Gupta"/>
     <s v="25-01-26"/>
     <s v="28-01-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567890123"/>
     <n v="7497"/>
     <x v="1"/>
@@ -7621,7 +8600,7 @@
     <s v="Meera Nair"/>
     <s v="01-02-26"/>
     <s v="04-02-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9678901234"/>
     <n v="17997"/>
     <x v="0"/>
@@ -7637,7 +8616,7 @@
     <s v="Aditya Singh"/>
     <s v="05-02-26"/>
     <s v="07-02-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789012345"/>
     <n v="5798"/>
     <x v="1"/>
@@ -7653,7 +8632,7 @@
     <s v="Kavya Rao"/>
     <s v="10-02-26"/>
     <s v="14-02-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9890123456"/>
     <n v="14796"/>
     <x v="0"/>
@@ -7669,7 +8648,7 @@
     <s v="Rohan Mehta"/>
     <s v="15-02-26"/>
     <s v="18-02-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901234567"/>
     <n v="6597"/>
     <x v="0"/>
@@ -7685,7 +8664,7 @@
     <s v="Divya Kapoor"/>
     <s v="20-02-26"/>
     <s v="22-02-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012345678"/>
     <n v="8398"/>
     <x v="1"/>
@@ -7701,7 +8680,7 @@
     <s v="Neha Jain"/>
     <s v="01-03-26"/>
     <s v="04-03-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123456701"/>
     <n v="7497"/>
     <x v="0"/>
@@ -7717,7 +8696,7 @@
     <s v="Arjun Verma"/>
     <s v="05-03-26"/>
     <s v="09-03-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234567012"/>
     <n v="11596"/>
     <x v="1"/>
@@ -7733,7 +8712,7 @@
     <s v="Nikhil Das"/>
     <s v="10-03-26"/>
     <s v="12-03-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345670123"/>
     <n v="11998"/>
     <x v="0"/>
@@ -7749,7 +8728,7 @@
     <s v="Aisha Bhat"/>
     <s v="15-03-26"/>
     <s v="18-03-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456701234"/>
     <n v="6597"/>
     <x v="1"/>
@@ -7765,7 +8744,7 @@
     <s v="Sanjay Yadav"/>
     <s v="20-03-26"/>
     <s v="23-03-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9567012345"/>
     <n v="11097"/>
     <x v="0"/>
@@ -7781,7 +8760,7 @@
     <s v="Pooja Iyer"/>
     <s v="25-03-26"/>
     <s v="29-03-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9670123456"/>
     <n v="16796"/>
     <x v="0"/>
@@ -7797,7 +8776,7 @@
     <s v="Ishita Rao"/>
     <s v="01-04-26"/>
     <s v="03-04-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9781234567"/>
     <n v="5798"/>
     <x v="1"/>
@@ -7813,7 +8792,7 @@
     <s v="Karthik Sharma"/>
     <s v="05-04-26"/>
     <s v="08-04-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9892345678"/>
     <n v="7497"/>
     <x v="0"/>
@@ -7829,7 +8808,7 @@
     <s v="Ananya Gupta"/>
     <s v="10-04-26"/>
     <s v="14-04-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9903456789"/>
     <n v="23996"/>
     <x v="1"/>
@@ -7845,7 +8824,7 @@
     <s v="Varun Kumar"/>
     <s v="15-04-26"/>
     <s v="18-04-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9014567890"/>
     <n v="11097"/>
     <x v="0"/>
@@ -7861,7 +8840,7 @@
     <s v="Meera Singh"/>
     <s v="20-04-26"/>
     <s v="22-04-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9125678901"/>
     <n v="4398"/>
     <x v="0"/>
@@ -7877,7 +8856,7 @@
     <s v="Rahul Jain"/>
     <s v="25-04-26"/>
     <s v="28-04-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9236789012"/>
     <n v="12597"/>
     <x v="1"/>
@@ -7893,7 +8872,7 @@
     <s v="Divya Patel"/>
     <s v="01-05-26"/>
     <s v="04-05-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9347890123"/>
     <n v="8697"/>
     <x v="0"/>
@@ -7909,7 +8888,7 @@
     <s v="Nikhil Sharma"/>
     <s v="05-05-26"/>
     <s v="07-05-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9458901234"/>
     <n v="4998"/>
     <x v="0"/>
@@ -7925,7 +8904,7 @@
     <s v="Sneha Kapoor"/>
     <s v="10-05-26"/>
     <s v="13-05-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9569012345"/>
     <n v="17997"/>
     <x v="1"/>
@@ -7941,7 +8920,7 @@
     <s v="Amit Verma"/>
     <s v="15-05-26"/>
     <s v="19-05-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9670123987"/>
     <n v="14796"/>
     <x v="0"/>
@@ -7957,7 +8936,7 @@
     <s v="Priya Rao"/>
     <s v="20-05-26"/>
     <s v="23-05-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9781234098"/>
     <n v="6597"/>
     <x v="1"/>
@@ -7973,7 +8952,7 @@
     <s v="Rohan Gupta"/>
     <s v="25-05-26"/>
     <s v="27-05-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9892345109"/>
     <n v="5798"/>
     <x v="0"/>
@@ -7989,7 +8968,7 @@
     <s v="Ananya Nair"/>
     <s v="01-06-26"/>
     <s v="05-06-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9903456210"/>
     <n v="16796"/>
     <x v="0"/>
@@ -8005,7 +8984,7 @@
     <s v="Sanjay Das"/>
     <s v="05-06-26"/>
     <s v="08-06-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9014567321"/>
     <n v="7497"/>
     <x v="1"/>
@@ -8021,7 +9000,7 @@
     <s v="Kavya Mehta"/>
     <s v="10-06-26"/>
     <s v="12-06-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9125678432"/>
     <n v="7398"/>
     <x v="0"/>
@@ -8037,7 +9016,7 @@
     <s v="Arjun Singh"/>
     <s v="15-06-26"/>
     <s v="20-06-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9236789543"/>
     <n v="29995"/>
     <x v="0"/>
@@ -8053,7 +9032,7 @@
     <s v="Neha Bhat"/>
     <s v="20-06-26"/>
     <s v="22-06-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9347890654"/>
     <n v="4398"/>
     <x v="1"/>
@@ -8069,7 +9048,7 @@
     <s v="Vikram Iyer"/>
     <s v="25-06-26"/>
     <s v="28-06-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9458901765"/>
     <n v="8697"/>
     <x v="0"/>
@@ -8085,7 +9064,7 @@
     <s v="Pooja Sharma"/>
     <s v="01-07-26"/>
     <s v="03-07-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9569012876"/>
     <n v="8398"/>
     <x v="1"/>
@@ -8101,7 +9080,7 @@
     <s v="Aisha Patel"/>
     <s v="05-07-26"/>
     <s v="08-07-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9670123987"/>
     <n v="7497"/>
     <x v="0"/>
@@ -8117,7 +9096,7 @@
     <s v="Karthik Rao"/>
     <s v="10-07-26"/>
     <s v="14-07-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9781234098"/>
     <n v="14796"/>
     <x v="0"/>
@@ -8133,7 +9112,7 @@
     <s v="Divya Gupta"/>
     <s v="15-07-26"/>
     <s v="18-07-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9892345109"/>
     <n v="17997"/>
     <x v="1"/>
@@ -8149,7 +9128,7 @@
     <s v="Aditya Jain"/>
     <s v="20-07-26"/>
     <s v="23-07-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9903456210"/>
     <n v="6597"/>
     <x v="0"/>
@@ -8165,7 +9144,7 @@
     <s v="Meera Verma"/>
     <s v="25-07-26"/>
     <s v="27-07-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9014567321"/>
     <n v="5798"/>
     <x v="1"/>
@@ -8181,7 +9160,7 @@
     <s v="Rahul Nair"/>
     <s v="01-08-26"/>
     <s v="04-08-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9125678432"/>
     <n v="12597"/>
     <x v="0"/>
@@ -8197,7 +9176,7 @@
     <s v="Sneha Das"/>
     <s v="05-08-26"/>
     <s v="09-08-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9236789543"/>
     <n v="9996"/>
     <x v="0"/>
@@ -8213,7 +9192,7 @@
     <s v="Varun Sharma"/>
     <s v="10-08-26"/>
     <s v="13-08-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9347890654"/>
     <n v="11097"/>
     <x v="1"/>
@@ -8229,7 +9208,7 @@
     <s v="Priya Kapoor"/>
     <s v="15-08-26"/>
     <s v="17-08-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9458901765"/>
     <n v="11998"/>
     <x v="0"/>
@@ -8245,7 +9224,7 @@
     <s v="Nikhil Patel"/>
     <s v="20-08-26"/>
     <s v="22-08-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9569012876"/>
     <n v="4398"/>
     <x v="0"/>
@@ -8261,7 +9240,7 @@
     <s v="Amit Gupta"/>
     <s v="25-08-26"/>
     <s v="29-08-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9670123987"/>
     <n v="11596"/>
     <x v="1"/>
@@ -8277,7 +9256,7 @@
     <s v="Ishita Singh"/>
     <s v="01-09-26"/>
     <s v="05-09-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9781234098"/>
     <n v="16796"/>
     <x v="0"/>
@@ -8293,7 +9272,7 @@
     <s v="Rohan Kumar"/>
     <s v="05-09-26"/>
     <s v="08-09-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9892345109"/>
     <n v="7497"/>
     <x v="1"/>
@@ -8309,7 +9288,7 @@
     <s v="Ananya Mehta"/>
     <s v="10-09-26"/>
     <s v="12-09-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9903456210"/>
     <n v="7398"/>
     <x v="0"/>
@@ -8325,7 +9304,7 @@
     <s v="Kavya Jain"/>
     <s v="15-09-26"/>
     <s v="19-09-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9014567321"/>
     <n v="23996"/>
     <x v="0"/>
@@ -8341,7 +9320,7 @@
     <s v="Arjun Rao"/>
     <s v="20-09-26"/>
     <s v="23-09-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457811"/>
     <n v="6597"/>
     <x v="0"/>
@@ -8357,7 +9336,7 @@
     <s v="Priya Sharma"/>
     <s v="25-09-26"/>
     <s v="28-09-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568922"/>
     <n v="8697"/>
     <x v="1"/>
@@ -8373,7 +9352,7 @@
     <s v="Vikram Patel"/>
     <s v="01-10-26"/>
     <s v="04-10-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679033"/>
     <n v="12597"/>
     <x v="0"/>
@@ -8389,7 +9368,7 @@
     <s v="Sneha Gupta"/>
     <s v="05-10-26"/>
     <s v="08-10-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780144"/>
     <n v="7497"/>
     <x v="0"/>
@@ -8405,7 +9384,7 @@
     <s v="Rohan Singh"/>
     <s v="10-10-26"/>
     <s v="14-10-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9567891255"/>
     <n v="14796"/>
     <x v="1"/>
@@ -8421,7 +9400,7 @@
     <s v="Divya Nair"/>
     <s v="15-10-26"/>
     <s v="18-10-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9678902366"/>
     <n v="17997"/>
     <x v="0"/>
@@ -8437,7 +9416,7 @@
     <s v="Amit Mehta"/>
     <s v="20-10-26"/>
     <s v="22-10-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013477"/>
     <n v="4398"/>
     <x v="0"/>
@@ -8453,7 +9432,7 @@
     <s v="Kavya Jain"/>
     <s v="25-10-26"/>
     <s v="29-10-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124588"/>
     <n v="11596"/>
     <x v="1"/>
@@ -8469,7 +9448,7 @@
     <s v="Aditya Verma"/>
     <s v="01-11-26"/>
     <s v="03-11-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235699"/>
     <n v="8398"/>
     <x v="0"/>
@@ -8485,7 +9464,7 @@
     <s v="Neha Kapoor"/>
     <s v="05-11-26"/>
     <s v="09-11-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346700"/>
     <n v="9996"/>
     <x v="1"/>
@@ -8501,7 +9480,7 @@
     <s v="Sanjay Kumar"/>
     <s v="10-11-26"/>
     <s v="13-11-26"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9123457811"/>
     <n v="11097"/>
     <x v="0"/>
@@ -8517,7 +9496,7 @@
     <s v="Ananya Rao"/>
     <s v="15-11-26"/>
     <s v="20-11-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9234568922"/>
     <n v="29995"/>
     <x v="0"/>
@@ -8533,7 +9512,7 @@
     <s v="Rahul Bhat"/>
     <s v="20-11-26"/>
     <s v="23-11-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679033"/>
     <n v="6597"/>
     <x v="1"/>
@@ -8549,7 +9528,7 @@
     <s v="Meera Patel"/>
     <s v="25-11-26"/>
     <s v="27-11-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780144"/>
     <n v="5798"/>
     <x v="0"/>
@@ -8565,7 +9544,7 @@
     <s v="Nikhil Sharma"/>
     <s v="01-12-26"/>
     <s v="05-12-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891255"/>
     <n v="16796"/>
     <x v="0"/>
@@ -8581,7 +9560,7 @@
     <s v="Pooja Gupta"/>
     <s v="05-12-26"/>
     <s v="08-12-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902366"/>
     <n v="7497"/>
     <x v="1"/>
@@ -8597,7 +9576,7 @@
     <s v="Karthik Das"/>
     <s v="10-12-26"/>
     <s v="12-12-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9789013477"/>
     <n v="7398"/>
     <x v="0"/>
@@ -8613,7 +9592,7 @@
     <s v="Aisha Singh"/>
     <s v="15-12-26"/>
     <s v="18-12-26"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9890124588"/>
     <n v="17997"/>
     <x v="0"/>
@@ -8629,7 +9608,7 @@
     <s v="Varun Nair"/>
     <s v="20-12-26"/>
     <s v="22-12-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235699"/>
     <n v="4398"/>
     <x v="1"/>
@@ -8645,7 +9624,7 @@
     <s v="Sneha Rao"/>
     <s v="25-12-26"/>
     <s v="29-12-26"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346700"/>
     <n v="11596"/>
     <x v="0"/>
@@ -8661,7 +9640,7 @@
     <s v="Amit Jain"/>
     <s v="01-01-27"/>
     <s v="04-01-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457811"/>
     <n v="12597"/>
     <x v="0"/>
@@ -8677,7 +9656,7 @@
     <s v="Divya Sharma"/>
     <s v="05-01-27"/>
     <s v="08-01-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568922"/>
     <n v="7497"/>
     <x v="1"/>
@@ -8693,7 +9672,7 @@
     <s v="Rohan Patel"/>
     <s v="10-01-27"/>
     <s v="13-01-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9345679033"/>
     <n v="11097"/>
     <x v="0"/>
@@ -8709,7 +9688,7 @@
     <s v="Priya Kapoor"/>
     <s v="15-01-27"/>
     <s v="17-01-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780144"/>
     <n v="11998"/>
     <x v="1"/>
@@ -8725,7 +9704,7 @@
     <s v="Aditya Gupta"/>
     <s v="20-01-27"/>
     <s v="23-01-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891255"/>
     <n v="6597"/>
     <x v="0"/>
@@ -8741,7 +9720,7 @@
     <s v="Kavya Verma"/>
     <s v="25-01-27"/>
     <s v="27-01-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902366"/>
     <n v="5798"/>
     <x v="0"/>
@@ -8757,7 +9736,7 @@
     <s v="Neha Singh"/>
     <s v="01-02-27"/>
     <s v="05-02-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013477"/>
     <n v="16796"/>
     <x v="1"/>
@@ -8773,7 +9752,7 @@
     <s v="Sanjay Mehta"/>
     <s v="05-02-27"/>
     <s v="09-02-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124588"/>
     <n v="9996"/>
     <x v="0"/>
@@ -8789,7 +9768,7 @@
     <s v="Ananya Jain"/>
     <s v="10-02-27"/>
     <s v="14-02-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9901235699"/>
     <n v="14796"/>
     <x v="0"/>
@@ -8805,7 +9784,7 @@
     <s v="Rahul Kumar"/>
     <s v="15-02-27"/>
     <s v="18-02-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9012346700"/>
     <n v="17997"/>
     <x v="1"/>
@@ -8821,7 +9800,7 @@
     <s v="Meera Das"/>
     <s v="20-02-27"/>
     <s v="22-02-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457811"/>
     <n v="4398"/>
     <x v="0"/>
@@ -8837,7 +9816,7 @@
     <s v="Nikhil Rao"/>
     <s v="25-02-27"/>
     <s v="28-02-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568922"/>
     <n v="8697"/>
     <x v="1"/>
@@ -8853,7 +9832,7 @@
     <s v="Pooja Patel"/>
     <s v="01-03-27"/>
     <s v="04-03-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679033"/>
     <n v="12597"/>
     <x v="0"/>
@@ -8869,7 +9848,7 @@
     <s v="Karthik Sharma"/>
     <s v="05-03-27"/>
     <s v="08-03-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780144"/>
     <n v="7497"/>
     <x v="0"/>
@@ -8885,7 +9864,7 @@
     <s v="Aisha Gupta"/>
     <s v="10-03-27"/>
     <s v="13-03-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9567891255"/>
     <n v="11097"/>
     <x v="1"/>
@@ -8901,7 +9880,7 @@
     <s v="Varun Singh"/>
     <s v="15-03-27"/>
     <s v="20-03-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9678902366"/>
     <n v="29995"/>
     <x v="0"/>
@@ -8917,7 +9896,7 @@
     <s v="Sneha Kapoor"/>
     <s v="20-03-27"/>
     <s v="22-03-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013477"/>
     <n v="4398"/>
     <x v="0"/>
@@ -8933,7 +9912,7 @@
     <s v="Amit Nair"/>
     <s v="25-03-27"/>
     <s v="29-03-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124588"/>
     <n v="11596"/>
     <x v="1"/>
@@ -8949,7 +9928,7 @@
     <s v="Divya Rao"/>
     <s v="01-04-27"/>
     <s v="03-04-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235699"/>
     <n v="8398"/>
     <x v="0"/>
@@ -8965,7 +9944,7 @@
     <s v="Rohan Jain"/>
     <s v="05-04-27"/>
     <s v="08-04-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346700"/>
     <n v="7497"/>
     <x v="1"/>
@@ -8981,7 +9960,7 @@
     <s v="Priya Verma"/>
     <s v="10-04-27"/>
     <s v="14-04-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9123457811"/>
     <n v="14796"/>
     <x v="0"/>
@@ -8997,7 +9976,7 @@
     <s v="Aditya Sharma"/>
     <s v="15-04-27"/>
     <s v="18-04-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9234568922"/>
     <n v="17997"/>
     <x v="0"/>
@@ -9013,7 +9992,7 @@
     <s v="Kavya Gupta"/>
     <s v="20-04-27"/>
     <s v="23-04-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679033"/>
     <n v="6597"/>
     <x v="1"/>
@@ -9029,7 +10008,7 @@
     <s v="Neha Patel"/>
     <s v="25-04-27"/>
     <s v="27-04-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780144"/>
     <n v="5798"/>
     <x v="0"/>
@@ -9045,7 +10024,7 @@
     <s v="Sanjay Singh"/>
     <s v="01-05-27"/>
     <s v="05-05-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891255"/>
     <n v="16796"/>
     <x v="0"/>
@@ -9061,7 +10040,7 @@
     <s v="Ananya Mehta"/>
     <s v="05-05-27"/>
     <s v="09-05-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902366"/>
     <n v="9996"/>
     <x v="1"/>
@@ -9077,7 +10056,7 @@
     <s v="Rahul Kapoor"/>
     <s v="10-05-27"/>
     <s v="12-05-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9789013477"/>
     <n v="7398"/>
     <x v="0"/>
@@ -9093,7 +10072,7 @@
     <s v="Meera Kumar"/>
     <s v="15-05-27"/>
     <s v="18-05-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9890124588"/>
     <n v="17997"/>
     <x v="0"/>
@@ -9109,7 +10088,7 @@
     <s v="Nikhil Jain"/>
     <s v="20-05-27"/>
     <s v="22-05-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235699"/>
     <n v="4398"/>
     <x v="1"/>
@@ -9125,7 +10104,7 @@
     <s v="Pooja Das"/>
     <s v="25-05-27"/>
     <s v="29-05-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346700"/>
     <n v="11596"/>
     <x v="0"/>
@@ -9141,7 +10120,7 @@
     <s v="Arjun Sharma"/>
     <s v="01-06-27"/>
     <s v="04-06-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457001"/>
     <n v="12597"/>
     <x v="0"/>
@@ -9157,7 +10136,7 @@
     <s v="Priya Gupta"/>
     <s v="05-06-27"/>
     <s v="08-06-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568112"/>
     <n v="7497"/>
     <x v="1"/>
@@ -9173,7 +10152,7 @@
     <s v="Rahul Patel"/>
     <s v="10-06-27"/>
     <s v="14-06-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9345679223"/>
     <n v="14796"/>
     <x v="0"/>
@@ -9189,7 +10168,7 @@
     <s v="Sneha Singh"/>
     <s v="15-06-27"/>
     <s v="18-06-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9456780334"/>
     <n v="17997"/>
     <x v="0"/>
@@ -9205,7 +10184,7 @@
     <s v="Amit Rao"/>
     <s v="20-06-27"/>
     <s v="22-06-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891445"/>
     <n v="4398"/>
     <x v="1"/>
@@ -9221,7 +10200,7 @@
     <s v="Kavya Jain"/>
     <s v="25-06-27"/>
     <s v="29-06-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902556"/>
     <n v="11596"/>
     <x v="0"/>
@@ -9237,7 +10216,7 @@
     <s v="Nikhil Kumar"/>
     <s v="01-07-27"/>
     <s v="03-07-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013667"/>
     <n v="8398"/>
     <x v="0"/>
@@ -9253,7 +10232,7 @@
     <s v="Meera Sharma"/>
     <s v="05-07-27"/>
     <s v="09-07-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124778"/>
     <n v="9996"/>
     <x v="1"/>
@@ -9269,7 +10248,7 @@
     <s v="Aditya Gupta"/>
     <s v="10-07-27"/>
     <s v="13-07-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9901235889"/>
     <n v="11097"/>
     <x v="0"/>
@@ -9285,7 +10264,7 @@
     <s v="Divya Patel"/>
     <s v="15-07-27"/>
     <s v="20-07-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9012346990"/>
     <n v="29995"/>
     <x v="0"/>
@@ -9301,7 +10280,7 @@
     <s v="Rohan Kapoor"/>
     <s v="20-07-27"/>
     <s v="23-07-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457001"/>
     <n v="6597"/>
     <x v="1"/>
@@ -9317,7 +10296,7 @@
     <s v="Ananya Verma"/>
     <s v="25-07-27"/>
     <s v="27-07-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568112"/>
     <n v="5798"/>
     <x v="0"/>
@@ -9333,7 +10312,7 @@
     <s v="Sanjay Nair"/>
     <s v="01-08-27"/>
     <s v="05-08-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679223"/>
     <n v="16796"/>
     <x v="0"/>
@@ -9349,7 +10328,7 @@
     <s v="Pooja Rao"/>
     <s v="05-08-27"/>
     <s v="08-08-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780334"/>
     <n v="7497"/>
     <x v="1"/>
@@ -9365,7 +10344,7 @@
     <s v="Karthik Singh"/>
     <s v="10-08-27"/>
     <s v="12-08-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9567891445"/>
     <n v="7398"/>
     <x v="0"/>
@@ -9381,7 +10360,7 @@
     <s v="Aisha Mehta"/>
     <s v="15-08-27"/>
     <s v="18-08-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9678902556"/>
     <n v="17997"/>
     <x v="0"/>
@@ -9397,7 +10376,7 @@
     <s v="Varun Jain"/>
     <s v="20-08-27"/>
     <s v="22-08-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013667"/>
     <n v="4398"/>
     <x v="1"/>
@@ -9413,7 +10392,7 @@
     <s v="Sneha Das"/>
     <s v="25-08-27"/>
     <s v="29-08-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124778"/>
     <n v="11596"/>
     <x v="0"/>
@@ -9429,7 +10408,7 @@
     <s v="Amit Sharma"/>
     <s v="01-09-27"/>
     <s v="04-09-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235889"/>
     <n v="12597"/>
     <x v="0"/>
@@ -9445,7 +10424,7 @@
     <s v="Divya Gupta"/>
     <s v="05-09-27"/>
     <s v="08-09-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346990"/>
     <n v="7497"/>
     <x v="1"/>
@@ -9461,7 +10440,7 @@
     <s v="Rohan Patel"/>
     <s v="10-09-27"/>
     <s v="13-09-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9123457001"/>
     <n v="11097"/>
     <x v="0"/>
@@ -9477,7 +10456,7 @@
     <s v="Ananya Kapoor"/>
     <s v="15-09-27"/>
     <s v="17-09-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568112"/>
     <n v="11998"/>
     <x v="1"/>
@@ -9493,7 +10472,7 @@
     <s v="Sanjay Verma"/>
     <s v="20-09-27"/>
     <s v="23-09-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679223"/>
     <n v="6597"/>
     <x v="0"/>
@@ -9509,7 +10488,7 @@
     <s v="Pooja Nair"/>
     <s v="25-09-27"/>
     <s v="27-09-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780334"/>
     <n v="5798"/>
     <x v="0"/>
@@ -9525,7 +10504,7 @@
     <s v="Karthik Rao"/>
     <s v="01-10-27"/>
     <s v="05-10-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891445"/>
     <n v="16796"/>
     <x v="1"/>
@@ -9541,7 +10520,7 @@
     <s v="Aisha Singh"/>
     <s v="05-10-27"/>
     <s v="09-10-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902556"/>
     <n v="9996"/>
     <x v="0"/>
@@ -9557,7 +10536,7 @@
     <s v="Varun Mehta"/>
     <s v="10-10-27"/>
     <s v="14-10-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9789013667"/>
     <n v="14796"/>
     <x v="0"/>
@@ -9573,7 +10552,7 @@
     <s v="Sneha Jain"/>
     <s v="15-10-27"/>
     <s v="18-10-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9890124778"/>
     <n v="17997"/>
     <x v="1"/>
@@ -9589,7 +10568,7 @@
     <s v="Amit Das"/>
     <s v="20-10-27"/>
     <s v="22-10-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235889"/>
     <n v="4398"/>
     <x v="0"/>
@@ -9605,7 +10584,7 @@
     <s v="Divya Sharma"/>
     <s v="25-10-27"/>
     <s v="29-10-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346990"/>
     <n v="11596"/>
     <x v="1"/>
@@ -9621,7 +10600,7 @@
     <s v="Rohan Gupta"/>
     <s v="01-11-27"/>
     <s v="03-11-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457001"/>
     <n v="8398"/>
     <x v="0"/>
@@ -9637,7 +10616,7 @@
     <s v="Ananya Patel"/>
     <s v="05-11-27"/>
     <s v="08-11-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568112"/>
     <n v="7497"/>
     <x v="0"/>
@@ -9653,7 +10632,7 @@
     <s v="Sanjay Kapoor"/>
     <s v="10-11-27"/>
     <s v="14-11-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9345679223"/>
     <n v="14796"/>
     <x v="1"/>
@@ -9669,7 +10648,7 @@
     <s v="Pooja Verma"/>
     <s v="15-11-27"/>
     <s v="20-11-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9456780334"/>
     <n v="29995"/>
     <x v="0"/>
@@ -9685,7 +10664,7 @@
     <s v="Karthik Nair"/>
     <s v="20-11-27"/>
     <s v="23-11-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891445"/>
     <n v="6597"/>
     <x v="0"/>
@@ -9701,7 +10680,7 @@
     <s v="Aisha Rao"/>
     <s v="25-11-27"/>
     <s v="27-11-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902556"/>
     <n v="5798"/>
     <x v="1"/>
@@ -9717,7 +10696,7 @@
     <s v="Varun Singh"/>
     <s v="01-12-27"/>
     <s v="05-12-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013667"/>
     <n v="16796"/>
     <x v="0"/>
@@ -9733,7 +10712,7 @@
     <s v="Sneha Mehta"/>
     <s v="05-12-27"/>
     <s v="08-12-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124778"/>
     <n v="7497"/>
     <x v="0"/>
@@ -9749,7 +10728,7 @@
     <s v="Amit Jain"/>
     <s v="10-12-27"/>
     <s v="13-12-27"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9901235889"/>
     <n v="11097"/>
     <x v="1"/>
@@ -9765,7 +10744,7 @@
     <s v="Divya Das"/>
     <s v="15-12-27"/>
     <s v="18-12-27"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9012346990"/>
     <n v="17997"/>
     <x v="0"/>
@@ -9781,7 +10760,7 @@
     <s v="Rohan Sharma"/>
     <s v="20-12-27"/>
     <s v="22-12-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457001"/>
     <n v="4398"/>
     <x v="0"/>
@@ -9797,7 +10776,7 @@
     <s v="Ananya Gupta"/>
     <s v="25-12-27"/>
     <s v="29-12-27"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568112"/>
     <n v="11596"/>
     <x v="1"/>
@@ -9813,7 +10792,7 @@
     <s v="Sanjay Patel"/>
     <s v="01-01-28"/>
     <s v="04-01-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679223"/>
     <n v="12597"/>
     <x v="0"/>
@@ -9829,7 +10808,7 @@
     <s v="Pooja Kapoor"/>
     <s v="05-01-28"/>
     <s v="09-01-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780334"/>
     <n v="9996"/>
     <x v="0"/>
@@ -9845,7 +10824,7 @@
     <s v="Karthik Verma"/>
     <s v="10-01-28"/>
     <s v="12-01-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9567891445"/>
     <n v="7398"/>
     <x v="1"/>
@@ -9861,7 +10840,7 @@
     <s v="Aisha Nair"/>
     <s v="15-01-28"/>
     <s v="18-01-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9678902556"/>
     <n v="17997"/>
     <x v="0"/>
@@ -9877,7 +10856,7 @@
     <s v="Varun Rao"/>
     <s v="20-01-28"/>
     <s v="23-01-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013667"/>
     <n v="6597"/>
     <x v="0"/>
@@ -9893,7 +10872,7 @@
     <s v="Sneha Singh"/>
     <s v="25-01-28"/>
     <s v="27-01-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124778"/>
     <n v="5798"/>
     <x v="1"/>
@@ -9909,7 +10888,7 @@
     <s v="Amit Mehta"/>
     <s v="01-02-28"/>
     <s v="05-02-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235889"/>
     <n v="16796"/>
     <x v="0"/>
@@ -9925,7 +10904,7 @@
     <s v="Divya Jain"/>
     <s v="05-02-28"/>
     <s v="08-02-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346990"/>
     <n v="7497"/>
     <x v="0"/>
@@ -9941,7 +10920,7 @@
     <s v="Rahul Nair"/>
     <s v="10-02-28"/>
     <s v="13-02-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9123457101"/>
     <n v="11097"/>
     <x v="1"/>
@@ -9957,7 +10936,7 @@
     <s v="Meera Sharma"/>
     <s v="15-02-28"/>
     <s v="18-02-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9234568212"/>
     <n v="17997"/>
     <x v="0"/>
@@ -9973,7 +10952,7 @@
     <s v="Nikhil Gupta"/>
     <s v="20-02-28"/>
     <s v="22-02-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679323"/>
     <n v="4398"/>
     <x v="0"/>
@@ -9989,7 +10968,7 @@
     <s v="Pooja Patel"/>
     <s v="25-02-28"/>
     <s v="29-02-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780434"/>
     <n v="11596"/>
     <x v="1"/>
@@ -10005,7 +10984,7 @@
     <s v="Karthik Kapoor"/>
     <s v="01-03-28"/>
     <s v="04-03-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891545"/>
     <n v="12597"/>
     <x v="0"/>
@@ -10021,7 +11000,7 @@
     <s v="Aisha Verma"/>
     <s v="05-03-28"/>
     <s v="08-03-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902656"/>
     <n v="7497"/>
     <x v="0"/>
@@ -10037,7 +11016,7 @@
     <s v="Varun Jain"/>
     <s v="10-03-28"/>
     <s v="14-03-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9789013767"/>
     <n v="14796"/>
     <x v="1"/>
@@ -10053,7 +11032,7 @@
     <s v="Sneha Das"/>
     <s v="15-03-28"/>
     <s v="20-03-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9890124878"/>
     <n v="29995"/>
     <x v="0"/>
@@ -10069,7 +11048,7 @@
     <s v="Amit Sharma"/>
     <s v="20-03-28"/>
     <s v="23-03-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235989"/>
     <n v="6597"/>
     <x v="0"/>
@@ -10085,7 +11064,7 @@
     <s v="Divya Gupta"/>
     <s v="25-03-28"/>
     <s v="27-03-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346090"/>
     <n v="5798"/>
     <x v="1"/>
@@ -10101,7 +11080,7 @@
     <s v="Rohan Patel"/>
     <s v="01-04-28"/>
     <s v="05-04-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457101"/>
     <n v="16796"/>
     <x v="0"/>
@@ -10117,7 +11096,7 @@
     <s v="Ananya Singh"/>
     <s v="05-04-28"/>
     <s v="09-04-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568212"/>
     <n v="9996"/>
     <x v="0"/>
@@ -10133,7 +11112,7 @@
     <s v="Sanjay Mehta"/>
     <s v="10-04-28"/>
     <s v="13-04-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9345679323"/>
     <n v="11097"/>
     <x v="1"/>
@@ -10149,7 +11128,7 @@
     <s v="Priya Rao"/>
     <s v="15-04-28"/>
     <s v="18-04-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9456780434"/>
     <n v="17997"/>
     <x v="0"/>
@@ -10165,7 +11144,7 @@
     <s v="Aditya Kumar"/>
     <s v="20-04-28"/>
     <s v="22-04-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891545"/>
     <n v="4398"/>
     <x v="0"/>
@@ -10181,7 +11160,7 @@
     <s v="Kavya Nair"/>
     <s v="25-04-28"/>
     <s v="29-04-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902656"/>
     <n v="11596"/>
     <x v="1"/>
@@ -10197,7 +11176,7 @@
     <s v="Neha Sharma"/>
     <s v="01-05-28"/>
     <s v="04-05-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013767"/>
     <n v="12597"/>
     <x v="0"/>
@@ -10213,7 +11192,7 @@
     <s v="Rahul Gupta"/>
     <s v="05-05-28"/>
     <s v="08-05-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124878"/>
     <n v="7497"/>
     <x v="0"/>
@@ -10229,7 +11208,7 @@
     <s v="Meera Patel"/>
     <s v="10-05-28"/>
     <s v="12-05-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9901235989"/>
     <n v="7398"/>
     <x v="1"/>
@@ -10245,7 +11224,7 @@
     <s v="Nikhil Kapoor"/>
     <s v="15-05-28"/>
     <s v="18-05-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9012346090"/>
     <n v="17997"/>
     <x v="0"/>
@@ -10261,7 +11240,7 @@
     <s v="Pooja Verma"/>
     <s v="20-05-28"/>
     <s v="23-05-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457101"/>
     <n v="6597"/>
     <x v="0"/>
@@ -10277,7 +11256,7 @@
     <s v="Karthik Jain"/>
     <s v="25-05-28"/>
     <s v="27-05-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568212"/>
     <n v="5798"/>
     <x v="1"/>
@@ -10293,7 +11272,7 @@
     <s v="Aisha Das"/>
     <s v="01-06-28"/>
     <s v="05-06-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679323"/>
     <n v="16796"/>
     <x v="0"/>
@@ -10309,7 +11288,7 @@
     <s v="Varun Sharma"/>
     <s v="05-06-28"/>
     <s v="08-06-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780434"/>
     <n v="7497"/>
     <x v="0"/>
@@ -10325,7 +11304,7 @@
     <s v="Sneha Gupta"/>
     <s v="10-06-28"/>
     <s v="13-06-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9567891545"/>
     <n v="11097"/>
     <x v="1"/>
@@ -10341,7 +11320,7 @@
     <s v="Amit Patel"/>
     <s v="15-06-28"/>
     <s v="20-06-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9678902656"/>
     <n v="29995"/>
     <x v="0"/>
@@ -10357,7 +11336,7 @@
     <s v="Divya Singh"/>
     <s v="20-06-28"/>
     <s v="22-06-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013767"/>
     <n v="4398"/>
     <x v="0"/>
@@ -10373,7 +11352,7 @@
     <s v="Rohan Mehta"/>
     <s v="25-06-28"/>
     <s v="29-06-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124878"/>
     <n v="11596"/>
     <x v="1"/>
@@ -10389,7 +11368,7 @@
     <s v="Ananya Rao"/>
     <s v="01-07-28"/>
     <s v="03-07-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235989"/>
     <n v="8398"/>
     <x v="0"/>
@@ -10405,7 +11384,7 @@
     <s v="Sanjay Kumar"/>
     <s v="05-07-28"/>
     <s v="08-07-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346090"/>
     <n v="7497"/>
     <x v="0"/>
@@ -10421,7 +11400,7 @@
     <s v="Priya Nair"/>
     <s v="10-07-28"/>
     <s v="14-07-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9123457101"/>
     <n v="14796"/>
     <x v="1"/>
@@ -10437,7 +11416,7 @@
     <s v="Aditya Sharma"/>
     <s v="15-07-28"/>
     <s v="18-07-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9234568212"/>
     <n v="17997"/>
     <x v="0"/>
@@ -10453,7 +11432,7 @@
     <s v="Kavya Gupta"/>
     <s v="20-07-28"/>
     <s v="23-07-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679323"/>
     <n v="6597"/>
     <x v="0"/>
@@ -10469,7 +11448,7 @@
     <s v="Neha Patel"/>
     <s v="25-07-28"/>
     <s v="27-07-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780434"/>
     <n v="5798"/>
     <x v="1"/>
@@ -10485,7 +11464,7 @@
     <s v="Rahul Singh"/>
     <s v="01-08-28"/>
     <s v="05-08-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891545"/>
     <n v="16796"/>
     <x v="0"/>
@@ -10501,7 +11480,7 @@
     <s v="Meera Mehta"/>
     <s v="05-08-28"/>
     <s v="09-08-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902656"/>
     <n v="9996"/>
     <x v="0"/>
@@ -10517,7 +11496,7 @@
     <s v="Nikhil Rao"/>
     <s v="10-08-28"/>
     <s v="12-08-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9789013767"/>
     <n v="7398"/>
     <x v="1"/>
@@ -10533,7 +11512,7 @@
     <s v="Pooja Kumar"/>
     <s v="15-08-28"/>
     <s v="18-08-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9890124878"/>
     <n v="17997"/>
     <x v="0"/>
@@ -10549,7 +11528,7 @@
     <s v="Karthik Nair"/>
     <s v="20-08-28"/>
     <s v="22-08-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901235989"/>
     <n v="4398"/>
     <x v="0"/>
@@ -10565,7 +11544,7 @@
     <s v="Aisha Sharma"/>
     <s v="25-08-28"/>
     <s v="29-08-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012346090"/>
     <n v="11596"/>
     <x v="1"/>
@@ -10581,7 +11560,7 @@
     <s v="Varun Gupta"/>
     <s v="01-09-28"/>
     <s v="04-09-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457101"/>
     <n v="12597"/>
     <x v="0"/>
@@ -10597,7 +11576,7 @@
     <s v="Sneha Patel"/>
     <s v="05-09-28"/>
     <s v="08-09-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568212"/>
     <n v="7497"/>
     <x v="0"/>
@@ -10613,7 +11592,7 @@
     <s v="Amit Singh"/>
     <s v="10-09-28"/>
     <s v="13-09-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9345679323"/>
     <n v="11097"/>
     <x v="1"/>
@@ -10629,7 +11608,7 @@
     <s v="Divya Mehta"/>
     <s v="15-09-28"/>
     <s v="18-09-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9456780434"/>
     <n v="17997"/>
     <x v="0"/>
@@ -10645,7 +11624,7 @@
     <s v="Rohan Rao"/>
     <s v="20-09-28"/>
     <s v="22-09-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891545"/>
     <n v="4398"/>
     <x v="0"/>
@@ -10661,7 +11640,7 @@
     <s v="Ananya Kumar"/>
     <s v="25-09-28"/>
     <s v="29-09-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902656"/>
     <n v="11596"/>
     <x v="1"/>
@@ -10677,7 +11656,7 @@
     <s v="Sanjay Nair"/>
     <s v="01-10-28"/>
     <s v="05-10-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013767"/>
     <n v="16796"/>
     <x v="0"/>
@@ -10693,7 +11672,7 @@
     <s v="Priya Sharma"/>
     <s v="05-10-28"/>
     <s v="08-10-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124878"/>
     <n v="7497"/>
     <x v="0"/>
@@ -10709,7 +11688,7 @@
     <s v="Aditya Gupta"/>
     <s v="10-10-28"/>
     <s v="14-10-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9901235989"/>
     <n v="14796"/>
     <x v="1"/>
@@ -10725,7 +11704,7 @@
     <s v="Kavya Patel"/>
     <s v="15-10-28"/>
     <s v="18-10-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9012346090"/>
     <n v="17997"/>
     <x v="0"/>
@@ -10741,7 +11720,7 @@
     <s v="Neha Kapoor"/>
     <s v="20-10-28"/>
     <s v="23-10-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457201"/>
     <n v="6597"/>
     <x v="0"/>
@@ -10757,7 +11736,7 @@
     <s v="Rahul Sharma"/>
     <s v="25-10-28"/>
     <s v="27-10-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568312"/>
     <n v="5798"/>
     <x v="1"/>
@@ -10773,7 +11752,7 @@
     <s v="Meera Gupta"/>
     <s v="01-11-28"/>
     <s v="05-11-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679423"/>
     <n v="16796"/>
     <x v="0"/>
@@ -10789,7 +11768,7 @@
     <s v="Nikhil Patel"/>
     <s v="05-11-28"/>
     <s v="08-11-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780534"/>
     <n v="7497"/>
     <x v="0"/>
@@ -10805,7 +11784,7 @@
     <s v="Pooja Singh"/>
     <s v="10-11-28"/>
     <s v="13-11-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9567891645"/>
     <n v="11097"/>
     <x v="1"/>
@@ -10821,7 +11800,7 @@
     <s v="Karthik Mehta"/>
     <s v="15-11-28"/>
     <s v="20-11-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9678902756"/>
     <n v="29995"/>
     <x v="0"/>
@@ -10837,7 +11816,7 @@
     <s v="Aisha Rao"/>
     <s v="20-11-28"/>
     <s v="22-11-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013867"/>
     <n v="4398"/>
     <x v="0"/>
@@ -10853,7 +11832,7 @@
     <s v="Varun Kumar"/>
     <s v="25-11-28"/>
     <s v="29-11-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124978"/>
     <n v="11596"/>
     <x v="1"/>
@@ -10869,7 +11848,7 @@
     <s v="Sneha Nair"/>
     <s v="01-12-28"/>
     <s v="04-12-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901236089"/>
     <n v="12597"/>
     <x v="0"/>
@@ -10885,7 +11864,7 @@
     <s v="Amit Sharma"/>
     <s v="05-12-28"/>
     <s v="08-12-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012347190"/>
     <n v="7497"/>
     <x v="0"/>
@@ -10901,7 +11880,7 @@
     <s v="Divya Gupta"/>
     <s v="10-12-28"/>
     <s v="14-12-28"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9123457201"/>
     <n v="14796"/>
     <x v="1"/>
@@ -10917,7 +11896,7 @@
     <s v="Rohan Patel"/>
     <s v="15-12-28"/>
     <s v="18-12-28"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9234568312"/>
     <n v="17997"/>
     <x v="0"/>
@@ -10933,7 +11912,7 @@
     <s v="Ananya Singh"/>
     <s v="20-12-28"/>
     <s v="23-12-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679423"/>
     <n v="6597"/>
     <x v="0"/>
@@ -10949,7 +11928,7 @@
     <s v="Sanjay Mehta"/>
     <s v="25-12-28"/>
     <s v="27-12-28"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780534"/>
     <n v="5798"/>
     <x v="1"/>
@@ -10965,7 +11944,7 @@
     <s v="Priya Rao"/>
     <s v="01-01-29"/>
     <s v="05-01-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891645"/>
     <n v="16796"/>
     <x v="0"/>
@@ -10981,7 +11960,7 @@
     <s v="Aditya Kumar"/>
     <s v="05-01-29"/>
     <s v="09-01-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902756"/>
     <n v="9996"/>
     <x v="0"/>
@@ -10997,7 +11976,7 @@
     <s v="Kavya Nair"/>
     <s v="10-01-29"/>
     <s v="12-01-29"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9789013867"/>
     <n v="7398"/>
     <x v="1"/>
@@ -11013,7 +11992,7 @@
     <s v="Neha Sharma"/>
     <s v="15-01-29"/>
     <s v="18-01-29"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9890124978"/>
     <n v="17997"/>
     <x v="0"/>
@@ -11029,7 +12008,7 @@
     <s v="Rahul Gupta"/>
     <s v="20-01-29"/>
     <s v="22-01-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901236089"/>
     <n v="4398"/>
     <x v="0"/>
@@ -11045,7 +12024,7 @@
     <s v="Meera Patel"/>
     <s v="25-01-29"/>
     <s v="29-01-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012347190"/>
     <n v="11596"/>
     <x v="1"/>
@@ -11061,7 +12040,7 @@
     <s v="Nikhil Singh"/>
     <s v="01-02-29"/>
     <s v="04-02-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457201"/>
     <n v="12597"/>
     <x v="0"/>
@@ -11077,7 +12056,7 @@
     <s v="Pooja Mehta"/>
     <s v="05-02-29"/>
     <s v="08-02-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568312"/>
     <n v="7497"/>
     <x v="0"/>
@@ -11093,7 +12072,7 @@
     <s v="Karthik Rao"/>
     <s v="10-02-29"/>
     <s v="13-02-29"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9345679423"/>
     <n v="11097"/>
     <x v="1"/>
@@ -11109,7 +12088,7 @@
     <s v="Aisha Kumar"/>
     <s v="15-02-29"/>
     <s v="20-02-29"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9456780534"/>
     <n v="29995"/>
     <x v="0"/>
@@ -11125,7 +12104,7 @@
     <s v="Varun Nair"/>
     <s v="20-02-29"/>
     <s v="22-02-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891645"/>
     <n v="4398"/>
     <x v="0"/>
@@ -11141,7 +12120,7 @@
     <s v="Sneha Sharma"/>
     <s v="25-02-29"/>
     <s v="01-03-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902756"/>
     <n v="11596"/>
     <x v="1"/>
@@ -11157,7 +12136,7 @@
     <s v="Amit Gupta"/>
     <s v="01-03-29"/>
     <s v="05-03-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013867"/>
     <n v="16796"/>
     <x v="0"/>
@@ -11173,7 +12152,7 @@
     <s v="Divya Patel"/>
     <s v="05-03-29"/>
     <s v="08-03-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124978"/>
     <n v="7497"/>
     <x v="0"/>
@@ -11189,7 +12168,7 @@
     <s v="Rohan Singh"/>
     <s v="10-03-29"/>
     <s v="14-03-29"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9901236089"/>
     <n v="14796"/>
     <x v="1"/>
@@ -11205,7 +12184,7 @@
     <s v="Ananya Mehta"/>
     <s v="15-03-29"/>
     <s v="18-03-29"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9012347190"/>
     <n v="17997"/>
     <x v="0"/>
@@ -11221,7 +12200,7 @@
     <s v="Sanjay Rao"/>
     <s v="20-03-29"/>
     <s v="23-03-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9123457201"/>
     <n v="6597"/>
     <x v="0"/>
@@ -11237,7 +12216,7 @@
     <s v="Priya Kumar"/>
     <s v="25-03-29"/>
     <s v="27-03-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9234568312"/>
     <n v="5798"/>
     <x v="1"/>
@@ -11253,7 +12232,7 @@
     <s v="Aditya Nair"/>
     <s v="01-04-29"/>
     <s v="04-04-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679423"/>
     <n v="12597"/>
     <x v="0"/>
@@ -11269,7 +12248,7 @@
     <s v="Kavya Sharma"/>
     <s v="05-04-29"/>
     <s v="09-04-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780534"/>
     <n v="9996"/>
     <x v="0"/>
@@ -11285,7 +12264,7 @@
     <s v="Neha Gupta"/>
     <s v="10-04-29"/>
     <s v="12-04-29"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9567891645"/>
     <n v="7398"/>
     <x v="1"/>
@@ -11301,7 +12280,7 @@
     <s v="Rahul Patel"/>
     <s v="15-04-29"/>
     <s v="18-04-29"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9678902756"/>
     <n v="17997"/>
     <x v="0"/>
@@ -11317,7 +12296,7 @@
     <s v="Meera Singh"/>
     <s v="20-04-29"/>
     <s v="22-04-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9789013867"/>
     <n v="4398"/>
     <x v="0"/>
@@ -11333,7 +12312,7 @@
     <s v="Nikhil Mehta"/>
     <s v="25-04-29"/>
     <s v="29-04-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9890124978"/>
     <n v="11596"/>
     <x v="1"/>
@@ -11349,7 +12328,7 @@
     <s v="Pooja Rao"/>
     <s v="01-05-29"/>
     <s v="05-05-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901236089"/>
     <n v="16796"/>
     <x v="0"/>
@@ -11365,7 +12344,7 @@
     <s v="Karthik Kumar"/>
     <s v="05-05-29"/>
     <s v="08-05-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012347190"/>
     <n v="7497"/>
     <x v="0"/>
@@ -11381,7 +12360,7 @@
     <s v="Aisha Nair"/>
     <s v="10-05-29"/>
     <s v="13-05-29"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9123457201"/>
     <n v="11097"/>
     <x v="1"/>
@@ -11397,7 +12376,7 @@
     <s v="Varun Sharma"/>
     <s v="15-05-29"/>
     <s v="20-05-29"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9234568312"/>
     <n v="29995"/>
     <x v="0"/>
@@ -11413,7 +12392,7 @@
     <s v="Sneha Gupta"/>
     <s v="20-05-29"/>
     <s v="22-05-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9345679423"/>
     <n v="4398"/>
     <x v="0"/>
@@ -11429,7 +12408,7 @@
     <s v="Amit Patel"/>
     <s v="25-05-29"/>
     <s v="29-05-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9456780534"/>
     <n v="11596"/>
     <x v="1"/>
@@ -11445,7 +12424,7 @@
     <s v="Divya Singh"/>
     <s v="01-06-29"/>
     <s v="04-06-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9567891645"/>
     <n v="12597"/>
     <x v="0"/>
@@ -11461,7 +12440,7 @@
     <s v="Rohan Mehta"/>
     <s v="05-06-29"/>
     <s v="08-06-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9678902756"/>
     <n v="7497"/>
     <x v="0"/>
@@ -11477,7 +12456,7 @@
     <s v="Ananya Rao"/>
     <s v="10-06-29"/>
     <s v="14-06-29"/>
-    <n v="4"/>
+    <x v="1"/>
     <n v="9789013867"/>
     <n v="14796"/>
     <x v="1"/>
@@ -11493,7 +12472,7 @@
     <s v="Sanjay Kumar"/>
     <s v="15-06-29"/>
     <s v="18-06-29"/>
-    <n v="3"/>
+    <x v="2"/>
     <n v="9890124978"/>
     <n v="17997"/>
     <x v="0"/>
@@ -11509,7 +12488,7 @@
     <s v="Priya Nair"/>
     <s v="20-06-29"/>
     <s v="23-06-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9901236089"/>
     <n v="6597"/>
     <x v="0"/>
@@ -11525,7 +12504,7 @@
     <s v="Aditya Sharma"/>
     <s v="25-06-29"/>
     <s v="27-06-29"/>
-    <n v="2"/>
+    <x v="0"/>
     <n v="9012347190"/>
     <n v="5798"/>
     <x v="1"/>
@@ -11539,7 +12518,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -11589,8 +12568,80 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2EA8F300-4D84-400E-BF60-44B402492EDE}" name="PivotTable10" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -11652,7 +12703,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A15:A16" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -11697,7 +12748,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -11742,7 +12793,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -11787,7 +12838,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -11895,7 +12946,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -11963,7 +13014,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -12047,7 +13098,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F432DA-19F0-4D22-A63C-E6256DB1F83D}" name="PivotTable9" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F432DA-19F0-4D22-A63C-E6256DB1F83D}" name="PivotTable9" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -12902,6 +13953,61 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F27B429-55FC-42C8-AA6D-0556A87F986E}">
+  <dimension ref="A3:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B7" s="15">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDD515C-FF03-47FA-A66B-60F1EAC984C4}">
   <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20670CC0-A132-42D7-92F6-6019475211F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603EC0D4-02B5-4366-BEE0-710539F026AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="4" activeTab="6" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="6" activeTab="6" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -19,11 +19,12 @@
     <sheet name="Room-wise Revenue" sheetId="6" r:id="rId4"/>
     <sheet name="Room-wise Bookings" sheetId="7" r:id="rId5"/>
     <sheet name="Guest Capacity Analysis" sheetId="9" r:id="rId6"/>
-    <sheet name="Data" sheetId="1" r:id="rId7"/>
+    <sheet name="Revenue by Payment Status" sheetId="11" r:id="rId7"/>
+    <sheet name="Data" sheetId="1" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId8"/>
+    <pivotCache cacheId="13" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="930">
   <si>
     <t>BookingID</t>
   </si>
@@ -2986,7 +2987,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="22">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -5490,6 +5494,332 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Revenue by Payment Status!PivotTable11</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Total Amount</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revenue by Payment Status'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Revenue by Payment Status'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Paid</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pending</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue by Payment Status'!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1950594</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>885332</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AF0C-4D96-90EC-744AFCEC5F1E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -5651,6 +5981,46 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -8223,6 +8593,525 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -8428,6 +9317,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B92D0F88-93C0-AD88-9831-A537531C5217}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46188.716442129633" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="250" xr:uid="{ABC0FC96-CD6A-4AE4-9F1C-C79E4709B301}">
   <cacheSource type="worksheet">
@@ -12518,7 +13448,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -12552,7 +13482,7 @@
     <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12569,7 +13499,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2EA8F300-4D84-400E-BF60-44B402492EDE}" name="PivotTable10" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2EA8F300-4D84-400E-BF60-44B402492EDE}" name="PivotTable10" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -12640,8 +13570,81 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B81D20A-D62B-4D21-8CAE-95429B735D40}" name="PivotTable11" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -12686,7 +13689,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12703,7 +13706,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A15:A16" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -12731,7 +13734,7 @@
     <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12748,7 +13751,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -12776,7 +13779,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12793,7 +13796,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -12821,7 +13824,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12838,7 +13841,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -12946,7 +13949,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -13014,7 +14017,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13098,7 +14101,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F432DA-19F0-4D22-A63C-E6256DB1F83D}" name="PivotTable9" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F432DA-19F0-4D22-A63C-E6256DB1F83D}" name="PivotTable9" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -13182,31 +14185,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="10" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="11" tableBorderDxfId="21">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="10">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="8">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="9">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="7">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="8">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="6">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="7">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="5">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="6">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14008,6 +15011,53 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A643E268-60B3-4A6C-9DAE-AE8118F5E71E}">
+  <dimension ref="A3:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1950594</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="16">
+        <v>885332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B6" s="16">
+        <v>2835926</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDD515C-FF03-47FA-A66B-60F1EAC984C4}">
   <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{603EC0D4-02B5-4366-BEE0-710539F026AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916F8ADD-F872-4206-9B90-AC61FC8FD1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="6" activeTab="6" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="6" activeTab="7" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -20,13 +20,31 @@
     <sheet name="Room-wise Bookings" sheetId="7" r:id="rId5"/>
     <sheet name="Guest Capacity Analysis" sheetId="9" r:id="rId6"/>
     <sheet name="Revenue by Payment Status" sheetId="11" r:id="rId7"/>
-    <sheet name="Data" sheetId="1" r:id="rId8"/>
+    <sheet name="Slicers" sheetId="12" r:id="rId8"/>
+    <sheet name="Data" sheetId="1" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_Guests">#N/A</definedName>
+    <definedName name="Slicer_PaymentStatus">#N/A</definedName>
+    <definedName name="Slicer_RoomNo">#N/A</definedName>
+    <definedName name="Slicer_Year">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId9"/>
+    <pivotCache cacheId="14" r:id="rId10"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId11"/>
+        <x14:slicerCache r:id="rId12"/>
+        <x14:slicerCache r:id="rId13"/>
+        <x14:slicerCache r:id="rId14"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -44,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="930">
   <si>
     <t>BookingID</t>
   </si>
@@ -2987,7 +3005,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="25">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -9358,6 +9385,323 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="RoomNo">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4D72F95-FB5A-D1D0-C471-442CE82E898E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="RoomNo"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2419350" y="774700"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Guests">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AC0D270-B44F-8598-99DE-F8E7D18FBE39}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Guests"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4279900" y="2825750"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1155700</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>155575</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="PaymentStatus">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{765ACECA-53ED-B873-7BE3-595A11EF49E7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="PaymentStatus"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="190500" y="2235200"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Year">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A872EF87-0876-AC20-E54A-740C4F1BB21E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Year"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6172200" y="615950"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46188.716442129633" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="250" xr:uid="{ABC0FC96-CD6A-4AE4-9F1C-C79E4709B301}">
   <cacheSource type="worksheet">
@@ -9409,7 +9753,12 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="5"/>
     </cacheField>
     <cacheField name="Year" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2026" maxValue="2029"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2026" maxValue="2029" count="4">
+        <n v="2026"/>
+        <n v="2027"/>
+        <n v="2028"/>
+        <n v="2029"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Month" numFmtId="0">
       <sharedItems count="12">
@@ -9436,7 +9785,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="1789889497"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -9455,7 +9804,7 @@
     <n v="8697"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -9471,7 +9820,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -9487,7 +9836,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -9503,7 +9852,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -9519,7 +9868,7 @@
     <n v="7497"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -9535,7 +9884,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -9551,7 +9900,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -9567,7 +9916,7 @@
     <n v="14796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -9583,7 +9932,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -9599,7 +9948,7 @@
     <n v="8398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -9615,7 +9964,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -9631,7 +9980,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -9647,7 +9996,7 @@
     <n v="11998"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -9663,7 +10012,7 @@
     <n v="6597"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -9679,7 +10028,7 @@
     <n v="11097"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -9695,7 +10044,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -9711,7 +10060,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -9727,7 +10076,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -9743,7 +10092,7 @@
     <n v="23996"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -9759,7 +10108,7 @@
     <n v="11097"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -9775,7 +10124,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -9791,7 +10140,7 @@
     <n v="12597"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -9807,7 +10156,7 @@
     <n v="8697"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -9823,7 +10172,7 @@
     <n v="4998"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -9839,7 +10188,7 @@
     <n v="17997"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -9855,7 +10204,7 @@
     <n v="14796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -9871,7 +10220,7 @@
     <n v="6597"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -9887,7 +10236,7 @@
     <n v="5798"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -9903,7 +10252,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -9919,7 +10268,7 @@
     <n v="7497"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -9935,7 +10284,7 @@
     <n v="7398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -9951,7 +10300,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -9967,7 +10316,7 @@
     <n v="4398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -9983,7 +10332,7 @@
     <n v="8697"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -9999,7 +10348,7 @@
     <n v="8398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -10015,7 +10364,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -10031,7 +10380,7 @@
     <n v="14796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -10047,7 +10396,7 @@
     <n v="17997"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -10063,7 +10412,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -10079,7 +10428,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -10095,7 +10444,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -10111,7 +10460,7 @@
     <n v="9996"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -10127,7 +10476,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -10143,7 +10492,7 @@
     <n v="11998"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -10159,7 +10508,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -10175,7 +10524,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -10191,7 +10540,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -10207,7 +10556,7 @@
     <n v="7497"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -10223,7 +10572,7 @@
     <n v="7398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -10239,7 +10588,7 @@
     <n v="23996"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -10255,7 +10604,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -10271,7 +10620,7 @@
     <n v="8697"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -10287,7 +10636,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -10303,7 +10652,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -10319,7 +10668,7 @@
     <n v="14796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -10335,7 +10684,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -10351,7 +10700,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -10367,7 +10716,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -10383,7 +10732,7 @@
     <n v="8398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -10399,7 +10748,7 @@
     <n v="9996"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -10415,7 +10764,7 @@
     <n v="11097"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -10431,7 +10780,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -10447,7 +10796,7 @@
     <n v="6597"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -10463,7 +10812,7 @@
     <n v="5798"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -10479,7 +10828,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -10495,7 +10844,7 @@
     <n v="7497"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -10511,7 +10860,7 @@
     <n v="7398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -10527,7 +10876,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -10543,7 +10892,7 @@
     <n v="4398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -10559,7 +10908,7 @@
     <n v="11596"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2026"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -10575,7 +10924,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -10591,7 +10940,7 @@
     <n v="7497"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -10607,7 +10956,7 @@
     <n v="11097"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -10623,7 +10972,7 @@
     <n v="11998"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -10639,7 +10988,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -10655,7 +11004,7 @@
     <n v="5798"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -10671,7 +11020,7 @@
     <n v="16796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -10687,7 +11036,7 @@
     <n v="9996"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -10703,7 +11052,7 @@
     <n v="14796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -10719,7 +11068,7 @@
     <n v="17997"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -10735,7 +11084,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -10751,7 +11100,7 @@
     <n v="8697"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -10767,7 +11116,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -10783,7 +11132,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -10799,7 +11148,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -10815,7 +11164,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -10831,7 +11180,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -10847,7 +11196,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -10863,7 +11212,7 @@
     <n v="8398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -10879,7 +11228,7 @@
     <n v="7497"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -10895,7 +11244,7 @@
     <n v="14796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -10911,7 +11260,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -10927,7 +11276,7 @@
     <n v="6597"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -10943,7 +11292,7 @@
     <n v="5798"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -10959,7 +11308,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -10975,7 +11324,7 @@
     <n v="9996"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -10991,7 +11340,7 @@
     <n v="7398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -11007,7 +11356,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -11023,7 +11372,7 @@
     <n v="4398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -11039,7 +11388,7 @@
     <n v="11596"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -11055,7 +11404,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -11071,7 +11420,7 @@
     <n v="7497"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -11087,7 +11436,7 @@
     <n v="14796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -11103,7 +11452,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -11119,7 +11468,7 @@
     <n v="4398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -11135,7 +11484,7 @@
     <n v="11596"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -11151,7 +11500,7 @@
     <n v="8398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -11167,7 +11516,7 @@
     <n v="9996"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -11183,7 +11532,7 @@
     <n v="11097"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -11199,7 +11548,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -11215,7 +11564,7 @@
     <n v="6597"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -11231,7 +11580,7 @@
     <n v="5798"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -11247,7 +11596,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -11263,7 +11612,7 @@
     <n v="7497"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -11279,7 +11628,7 @@
     <n v="7398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -11295,7 +11644,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -11311,7 +11660,7 @@
     <n v="4398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -11327,7 +11676,7 @@
     <n v="11596"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -11343,7 +11692,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -11359,7 +11708,7 @@
     <n v="7497"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -11375,7 +11724,7 @@
     <n v="11097"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -11391,7 +11740,7 @@
     <n v="11998"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -11407,7 +11756,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -11423,7 +11772,7 @@
     <n v="5798"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -11439,7 +11788,7 @@
     <n v="16796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -11455,7 +11804,7 @@
     <n v="9996"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -11471,7 +11820,7 @@
     <n v="14796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -11487,7 +11836,7 @@
     <n v="17997"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -11503,7 +11852,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -11519,7 +11868,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -11535,7 +11884,7 @@
     <n v="8398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -11551,7 +11900,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -11567,7 +11916,7 @@
     <n v="14796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -11583,7 +11932,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -11599,7 +11948,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -11615,7 +11964,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -11631,7 +11980,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -11647,7 +11996,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -11663,7 +12012,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -11679,7 +12028,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -11695,7 +12044,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -11711,7 +12060,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2027"/>
+    <x v="1"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -11727,7 +12076,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -11743,7 +12092,7 @@
     <n v="9996"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -11759,7 +12108,7 @@
     <n v="7398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -11775,7 +12124,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -11791,7 +12140,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -11807,7 +12156,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -11823,7 +12172,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -11839,7 +12188,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -11855,7 +12204,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -11871,7 +12220,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -11887,7 +12236,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -11903,7 +12252,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -11919,7 +12268,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -11935,7 +12284,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -11951,7 +12300,7 @@
     <n v="14796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -11967,7 +12316,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -11983,7 +12332,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -11999,7 +12348,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -12015,7 +12364,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -12031,7 +12380,7 @@
     <n v="9996"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -12047,7 +12396,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -12063,7 +12412,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -12079,7 +12428,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -12095,7 +12444,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -12111,7 +12460,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -12127,7 +12476,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -12143,7 +12492,7 @@
     <n v="7398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -12159,7 +12508,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -12175,7 +12524,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -12191,7 +12540,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -12207,7 +12556,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -12223,7 +12572,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -12239,7 +12588,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -12255,7 +12604,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -12271,7 +12620,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -12287,7 +12636,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -12303,7 +12652,7 @@
     <n v="8398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -12319,7 +12668,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -12335,7 +12684,7 @@
     <n v="14796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -12351,7 +12700,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -12367,7 +12716,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -12383,7 +12732,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="6"/>
     <n v="7"/>
     <s v="Q3"/>
@@ -12399,7 +12748,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -12415,7 +12764,7 @@
     <n v="9996"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -12431,7 +12780,7 @@
     <n v="7398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -12447,7 +12796,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -12463,7 +12812,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -12479,7 +12828,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="7"/>
     <n v="8"/>
     <s v="Q3"/>
@@ -12495,7 +12844,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -12511,7 +12860,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -12527,7 +12876,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -12543,7 +12892,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -12559,7 +12908,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -12575,7 +12924,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="8"/>
     <n v="9"/>
     <s v="Q3"/>
@@ -12591,7 +12940,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -12607,7 +12956,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -12623,7 +12972,7 @@
     <n v="14796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -12639,7 +12988,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -12655,7 +13004,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -12671,7 +13020,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="9"/>
     <n v="10"/>
     <s v="Q4"/>
@@ -12687,7 +13036,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -12703,7 +13052,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -12719,7 +13068,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -12735,7 +13084,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -12751,7 +13100,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -12767,7 +13116,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="10"/>
     <n v="11"/>
     <s v="Q4"/>
@@ -12783,7 +13132,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -12799,7 +13148,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -12815,7 +13164,7 @@
     <n v="14796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -12831,7 +13180,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -12847,7 +13196,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -12863,7 +13212,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2028"/>
+    <x v="2"/>
     <x v="11"/>
     <n v="12"/>
     <s v="Q4"/>
@@ -12879,7 +13228,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -12895,7 +13244,7 @@
     <n v="9996"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -12911,7 +13260,7 @@
     <n v="7398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -12927,7 +13276,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -12943,7 +13292,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -12959,7 +13308,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="0"/>
     <n v="1"/>
     <s v="Q1"/>
@@ -12975,7 +13324,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -12991,7 +13340,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -13007,7 +13356,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -13023,7 +13372,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -13039,7 +13388,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -13055,7 +13404,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="1"/>
     <n v="2"/>
     <s v="Q1"/>
@@ -13071,7 +13420,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -13087,7 +13436,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -13103,7 +13452,7 @@
     <n v="14796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -13119,7 +13468,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -13135,7 +13484,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -13151,7 +13500,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="3"/>
     <s v="Q1"/>
@@ -13167,7 +13516,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -13183,7 +13532,7 @@
     <n v="9996"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -13199,7 +13548,7 @@
     <n v="7398"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -13215,7 +13564,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -13231,7 +13580,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -13247,7 +13596,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="3"/>
     <n v="4"/>
     <s v="Q2"/>
@@ -13263,7 +13612,7 @@
     <n v="16796"/>
     <x v="0"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -13279,7 +13628,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -13295,7 +13644,7 @@
     <n v="11097"/>
     <x v="1"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -13311,7 +13660,7 @@
     <n v="29995"/>
     <x v="0"/>
     <n v="5"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -13327,7 +13676,7 @@
     <n v="4398"/>
     <x v="0"/>
     <n v="2"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -13343,7 +13692,7 @@
     <n v="11596"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="4"/>
     <n v="5"/>
     <s v="Q2"/>
@@ -13359,7 +13708,7 @@
     <n v="12597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -13375,7 +13724,7 @@
     <n v="7497"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -13391,7 +13740,7 @@
     <n v="14796"/>
     <x v="1"/>
     <n v="4"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -13407,7 +13756,7 @@
     <n v="17997"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -13423,7 +13772,7 @@
     <n v="6597"/>
     <x v="0"/>
     <n v="3"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -13439,7 +13788,7 @@
     <n v="5798"/>
     <x v="1"/>
     <n v="2"/>
-    <n v="2029"/>
+    <x v="3"/>
     <x v="5"/>
     <n v="6"/>
     <s v="Q2"/>
@@ -13448,7 +13797,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13482,7 +13831,7 @@
     <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13499,7 +13848,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2EA8F300-4D84-400E-BF60-44B402492EDE}" name="PivotTable10" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2EA8F300-4D84-400E-BF60-44B402492EDE}" name="PivotTable10" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -13571,7 +13920,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B81D20A-D62B-4D21-8CAE-95429B735D40}" name="PivotTable11" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B81D20A-D62B-4D21-8CAE-95429B735D40}" name="PivotTable11" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13616,7 +13965,105 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4017B918-D920-43F4-B50F-4463C194D434}" name="PivotTable12" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A6:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13644,7 +14091,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -13689,7 +14136,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13706,7 +14153,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A15:A16" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13734,7 +14181,7 @@
     <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13751,7 +14198,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -13779,7 +14226,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13796,7 +14243,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13824,7 +14271,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="5">
+    <format dxfId="8">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13841,7 +14288,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13949,7 +14396,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -14017,7 +14464,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -14101,7 +14548,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F432DA-19F0-4D22-A63C-E6256DB1F83D}" name="PivotTable9" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F432DA-19F0-4D22-A63C-E6256DB1F83D}" name="PivotTable9" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -14184,32 +14631,112 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_RoomNo" xr10:uid="{D7B642E5-D193-46FB-BEA7-2F0DBF91C9AE}" sourceName="RoomNo">
+  <pivotTables>
+    <pivotTable tabId="12" name="PivotTable12"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1789889497">
+      <items count="6">
+        <i x="0" s="1"/>
+        <i x="4" s="1"/>
+        <i x="1" s="1"/>
+        <i x="3" s="1"/>
+        <i x="2" s="1"/>
+        <i x="5" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Guests" xr10:uid="{C4D36F7B-951A-4971-8FF8-4A90AEB83259}" sourceName="Guests">
+  <pivotTables>
+    <pivotTable tabId="12" name="PivotTable12"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1789889497">
+      <items count="3">
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
+        <i x="1" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_PaymentStatus" xr10:uid="{47629A74-15E7-4AD6-9AED-6A3ECFB8DF31}" sourceName="PaymentStatus">
+  <pivotTables>
+    <pivotTable tabId="12" name="PivotTable12"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1789889497">
+      <items count="2">
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Year" xr10:uid="{4D9FE457-1660-4345-97BC-07FDC11E4FCE}" sourceName="Year">
+  <pivotTables>
+    <pivotTable tabId="12" name="PivotTable12"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1789889497">
+      <items count="4">
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="RoomNo" xr10:uid="{5AD7335F-A18E-45FA-A62D-ADAF691F518C}" cache="Slicer_RoomNo" caption="RoomNo" rowHeight="241300"/>
+  <slicer name="Guests" xr10:uid="{C217F2D5-83C6-4AA6-A027-BC0D2D528192}" cache="Slicer_Guests" caption="Guests" rowHeight="241300"/>
+  <slicer name="PaymentStatus" xr10:uid="{E0F73816-370E-495A-811B-A0F3652A90E6}" cache="Slicer_PaymentStatus" caption="PaymentStatus" rowHeight="241300"/>
+  <slicer name="Year" xr10:uid="{53D1C051-6A6C-458C-80A6-D795AE46C44E}" cache="Slicer_Year" caption="Year" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="11" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="14" tableBorderDxfId="24">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="13">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="9">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="12">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="8">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="11">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="7">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="10">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="6">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="9">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -15058,6 +15585,60 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40DB684-C84D-4777-80A5-AA2E00E9A86A}">
+  <dimension ref="A6:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B6" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>1950594</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="16">
+        <v>885332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B9" s="16">
+        <v>2835926</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDD515C-FF03-47FA-A66B-60F1EAC984C4}">
   <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916F8ADD-F872-4206-9B90-AC61FC8FD1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634E1DEF-5DD7-4DF7-A880-548ECB0B28D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="6" activeTab="7" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="6" activeTab="8" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,8 @@
     <sheet name="Guest Capacity Analysis" sheetId="9" r:id="rId6"/>
     <sheet name="Revenue by Payment Status" sheetId="11" r:id="rId7"/>
     <sheet name="Slicers" sheetId="12" r:id="rId8"/>
-    <sheet name="Data" sheetId="1" r:id="rId9"/>
+    <sheet name="Sheet15" sheetId="15" r:id="rId9"/>
+    <sheet name="Data" sheetId="1" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Guests">#N/A</definedName>
@@ -31,15 +32,15 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId10"/>
+    <pivotCache cacheId="15" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId11"/>
         <x14:slicerCache r:id="rId12"/>
         <x14:slicerCache r:id="rId13"/>
         <x14:slicerCache r:id="rId14"/>
+        <x14:slicerCache r:id="rId15"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="931">
   <si>
     <t>BookingID</t>
   </si>
@@ -2852,6 +2853,9 @@
   </si>
   <si>
     <t>Dec</t>
+  </si>
+  <si>
+    <t>HOTEL BOOKING DASHBOARD</t>
   </si>
 </sst>
 </file>
@@ -2861,7 +2865,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2874,6 +2878,14 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2979,7 +2991,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3001,14 +3013,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -3455,6 +3467,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF1F4E78"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3747,6 +3764,1701 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-1ECC-464E-804C-600AFC926066}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1350862143"/>
+        <c:axId val="1350858303"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1350862143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350858303"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1350858303"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350862143"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Room-wise Revenue!PivotTable8</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Revenue by Room</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Room-wise Revenue'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Room-wise Revenue'!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>206</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Room-wise Revenue'!$B$4:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>379769</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>332367</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>484569</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>566865</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>226497</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>845859</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A864-494C-975B-0E36749268E0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1350909663"/>
+        <c:axId val="1350911103"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1350909663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350911103"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1350911103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350909663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Payment Status Chart!PivotTable7</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Paid vs Pending</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Payment Status Chart'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-C72E-4F8D-A737-2BD95EDC0A71}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-C72E-4F8D-A737-2BD95EDC0A71}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Payment Status Chart'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Paid</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pending</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Payment Status Chart'!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C72E-4F8D-A737-2BD95EDC0A71}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Monthly Revenue Trend!PivotTable6</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Monthly Revenue Trend</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Monthly Revenue Trend'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Monthly Revenue Trend'!$A$4:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monthly Revenue Trend'!$B$4:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>232633</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>272827</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>289522</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>262328</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>266327</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>290323</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>194047</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>195545</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>191747</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>213941</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>226341</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>200345</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6E7D-4FD8-B392-89BD987DC2F4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5847,7 +7559,1655 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Revenue by Payment Status!PivotTable11</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Total Amount</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revenue by Payment Status'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D302-49FB-B2A7-9C8310470613}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D302-49FB-B2A7-9C8310470613}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Revenue by Payment Status'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Paid</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pending</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue by Payment Status'!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>_("₹"* #,##0.00_);_("₹"* \(#,##0.00\);_("₹"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1950594</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>885332</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-D302-49FB-B2A7-9C8310470613}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Guest Capacity Analysis!PivotTable10</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Guest Capacity</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Guest Capacity Analysis'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Guest Capacity Analysis'!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Guest Capacity Analysis'!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F900-4FE5-9267-44B15C44771D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1350863103"/>
+        <c:axId val="1350868383"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1350863103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350868383"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1350868383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350863103"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Hotel Booking Dashboard.xlsx]Room-wise Bookings!PivotTable9</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Bookings per Room</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Room-wise Bookings'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Room-wise Bookings'!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>206</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Room-wise Bookings'!$B$4:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>41</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1891-457D-B906-3BD2342B26AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1289281775"/>
+        <c:axId val="1289291855"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1289281775"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1289291855"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1289291855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1289281775"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6087,6 +9447,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -6590,8 +10070,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6648,7 +10128,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -6699,13 +10179,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -6716,19 +10189,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -6766,7 +10232,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -6809,23 +10275,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -6930,8 +10395,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7063,20 +10528,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -7109,8 +10573,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -7167,7 +10631,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -7218,6 +10682,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -7228,12 +10699,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -7271,7 +10749,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -7314,22 +10792,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -7434,8 +10913,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7567,19 +11046,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -7612,8 +11092,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -7817,23 +11297,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -7938,8 +11417,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8071,20 +11550,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -8117,8 +11595,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -8175,7 +11653,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -8226,6 +11704,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -8236,12 +11721,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -8279,7 +11771,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -8322,22 +11814,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -8442,8 +11935,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8575,19 +12068,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -8620,8 +12114,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -8678,7 +12172,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -8729,13 +12223,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -8746,19 +12233,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -8796,7 +12276,3059 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -9702,6 +16234,551 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>553779</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="RoomNo 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD8AE164-9F35-4609-89F1-D50F215ADE38}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="RoomNo 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="612849" y="1875466"/>
+              <a:ext cx="1838546" cy="2017380"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>177801</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>88901</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="PaymentStatus 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C82A663A-762F-4502-B2D3-3A8F708A1D94}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="PaymentStatus 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3212214" y="1868673"/>
+              <a:ext cx="1838547" cy="948807"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>101601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76201</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>31752</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Guests 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9F35855-D98A-48C1-8CAB-06CE02033E4C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Guests 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3199514" y="2900031"/>
+              <a:ext cx="1838547" cy="1222302"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>241299</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Year 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96F63E9B-FEC7-48E6-9819-4591AED38822}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Year 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5203160" y="1862323"/>
+              <a:ext cx="1838546" cy="1566086"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98ACD6B8-09C7-4B4F-974B-595E4BA693F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57830116-1F21-4F7E-B0EA-42A55E1F1097}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6D42EF5-9522-46E7-B465-DA1E948C2AA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81BFBBBE-12A4-4712-ABD4-47EA0DAD95B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31C6DC40-BCA1-4254-B1E3-E6D00C3206E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51450A07-4C40-4C50-A03F-4BFE04C8E4F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46188.716442129633" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="250" xr:uid="{ABC0FC96-CD6A-4AE4-9F1C-C79E4709B301}">
   <cacheSource type="worksheet">
@@ -13797,7 +20874,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13831,7 +20908,7 @@
     <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="5">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13848,11 +20925,21 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2EA8F300-4D84-400E-BF60-44B402492EDE}" name="PivotTable10" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2EA8F300-4D84-400E-BF60-44B402492EDE}" name="PivotTable10" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -13866,9 +20953,23 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -13896,8 +20997,17 @@
   <dataFields count="1">
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -13920,81 +21030,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B81D20A-D62B-4D21-8CAE-95429B735D40}" name="PivotTable11" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B81D20A-D62B-4D21-8CAE-95429B735D40}" name="PivotTable11" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4017B918-D920-43F4-B50F-4463C194D434}" name="PivotTable12" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A6:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -14067,6 +21104,137 @@
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4017B918-D920-43F4-B50F-4463C194D434}" name="PivotTable12" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A6:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
@@ -14090,8 +21258,139 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E2A3F8F-7DD3-419D-BABB-467627FA5562}" name="PivotTable15" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A2:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -14136,7 +21435,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14153,7 +21452,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A15:A16" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -14181,7 +21480,7 @@
     <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="6">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14198,7 +21497,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -14226,7 +21525,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="7">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14243,7 +21542,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -14271,7 +21570,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="8">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14288,20 +21587,51 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C51A41DF-3E26-4279-BEFC-7995FC96DB9B}" name="PivotTable6" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="13">
         <item x="0"/>
@@ -14372,8 +21702,17 @@
   <dataFields count="1">
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14396,15 +21735,32 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283D40FD-8A63-48FD-85F1-210556922C98}" name="PivotTable7" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
@@ -14415,7 +21771,15 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14440,12 +21804,45 @@
   <dataFields count="1">
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="4">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -14464,7 +21861,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0217378-A88C-48CF-AFA7-091290EE5CFC}" name="PivotTable8" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -14482,12 +21879,33 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14524,8 +21942,17 @@
   <dataFields count="1">
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14548,7 +21975,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F432DA-19F0-4D22-A63C-E6256DB1F83D}" name="PivotTable9" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6F432DA-19F0-4D22-A63C-E6256DB1F83D}" name="PivotTable9" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -14566,12 +21993,33 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14608,8 +22056,17 @@
   <dataFields count="1">
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14635,6 +22092,13 @@
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_RoomNo" xr10:uid="{D7B642E5-D193-46FB-BEA7-2F0DBF91C9AE}" sourceName="RoomNo">
   <pivotTables>
     <pivotTable tabId="12" name="PivotTable12"/>
+    <pivotTable tabId="9" name="PivotTable10"/>
+    <pivotTable tabId="11" name="PivotTable11"/>
+    <pivotTable tabId="7" name="PivotTable9"/>
+    <pivotTable tabId="6" name="PivotTable8"/>
+    <pivotTable tabId="5" name="PivotTable7"/>
+    <pivotTable tabId="4" name="PivotTable6"/>
+    <pivotTable tabId="15" name="PivotTable15"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1789889497">
@@ -14655,6 +22119,13 @@
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Guests" xr10:uid="{C4D36F7B-951A-4971-8FF8-4A90AEB83259}" sourceName="Guests">
   <pivotTables>
     <pivotTable tabId="12" name="PivotTable12"/>
+    <pivotTable tabId="9" name="PivotTable10"/>
+    <pivotTable tabId="11" name="PivotTable11"/>
+    <pivotTable tabId="7" name="PivotTable9"/>
+    <pivotTable tabId="6" name="PivotTable8"/>
+    <pivotTable tabId="5" name="PivotTable7"/>
+    <pivotTable tabId="4" name="PivotTable6"/>
+    <pivotTable tabId="15" name="PivotTable15"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1789889497">
@@ -14672,6 +22143,13 @@
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_PaymentStatus" xr10:uid="{47629A74-15E7-4AD6-9AED-6A3ECFB8DF31}" sourceName="PaymentStatus">
   <pivotTables>
     <pivotTable tabId="12" name="PivotTable12"/>
+    <pivotTable tabId="9" name="PivotTable10"/>
+    <pivotTable tabId="11" name="PivotTable11"/>
+    <pivotTable tabId="7" name="PivotTable9"/>
+    <pivotTable tabId="6" name="PivotTable8"/>
+    <pivotTable tabId="5" name="PivotTable7"/>
+    <pivotTable tabId="4" name="PivotTable6"/>
+    <pivotTable tabId="15" name="PivotTable15"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1789889497">
@@ -14688,6 +22166,13 @@
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Year" xr10:uid="{4D9FE457-1660-4345-97BC-07FDC11E4FCE}" sourceName="Year">
   <pivotTables>
     <pivotTable tabId="12" name="PivotTable12"/>
+    <pivotTable tabId="9" name="PivotTable10"/>
+    <pivotTable tabId="11" name="PivotTable11"/>
+    <pivotTable tabId="7" name="PivotTable9"/>
+    <pivotTable tabId="6" name="PivotTable8"/>
+    <pivotTable tabId="5" name="PivotTable7"/>
+    <pivotTable tabId="4" name="PivotTable6"/>
+    <pivotTable tabId="15" name="PivotTable15"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1789889497">
@@ -14711,32 +22196,41 @@
 </slicers>
 </file>
 
+<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="RoomNo 1" xr10:uid="{E35ABD4A-F52B-431A-A9B6-77850ECC613B}" cache="Slicer_RoomNo" caption="RoomNo" rowHeight="241300"/>
+  <slicer name="Guests 1" xr10:uid="{874D0E70-9CC2-4AB4-85CF-06071CD9EE4E}" cache="Slicer_Guests" caption="Guests" rowHeight="241300"/>
+  <slicer name="PaymentStatus 1" xr10:uid="{5C01683D-790B-46C8-95A4-5EDCC7C646EF}" cache="Slicer_PaymentStatus" caption="PaymentStatus" rowHeight="241300"/>
+  <slicer name="Year 1" xr10:uid="{A521D296-65DA-469F-ABBD-0FFB5B05B35A}" cache="Slicer_Year" caption="Year" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="14" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="13" tableBorderDxfId="23">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="12">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="12">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="11">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="11">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="10">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="10">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="9">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="9">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="8">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -15150,495 +22644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{845A94EE-9C2D-4ED1-9459-BE9FCC0CB032}">
-  <dimension ref="A3:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="B3" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>918</v>
-      </c>
-      <c r="B4" s="15">
-        <v>232633</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
-        <v>919</v>
-      </c>
-      <c r="B5" s="15">
-        <v>272827</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>920</v>
-      </c>
-      <c r="B6" s="15">
-        <v>289522</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
-        <v>921</v>
-      </c>
-      <c r="B7" s="15">
-        <v>262328</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
-        <v>922</v>
-      </c>
-      <c r="B8" s="15">
-        <v>266327</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
-        <v>923</v>
-      </c>
-      <c r="B9" s="15">
-        <v>290323</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
-        <v>924</v>
-      </c>
-      <c r="B10" s="15">
-        <v>194047</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
-        <v>925</v>
-      </c>
-      <c r="B11" s="15">
-        <v>195545</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
-        <v>926</v>
-      </c>
-      <c r="B12" s="15">
-        <v>191747</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>927</v>
-      </c>
-      <c r="B13" s="15">
-        <v>213941</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
-        <v>928</v>
-      </c>
-      <c r="B14" s="15">
-        <v>226341</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
-        <v>929</v>
-      </c>
-      <c r="B15" s="15">
-        <v>200345</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="B16" s="15">
-        <v>2835926</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43145B0-5EAA-4625-86B1-2B343EA48E35}">
-  <dimension ref="A3:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="B3" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="15">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="15">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="B6" s="15">
-        <v>250</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E86FBE-A6BE-4C10-8B1A-63ED78EBA71C}">
-  <dimension ref="A3:B10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="B3" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="18">
-        <v>201</v>
-      </c>
-      <c r="B4" s="15">
-        <v>379769</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="18">
-        <v>202</v>
-      </c>
-      <c r="B5" s="15">
-        <v>332367</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="18">
-        <v>203</v>
-      </c>
-      <c r="B6" s="15">
-        <v>484569</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="18">
-        <v>204</v>
-      </c>
-      <c r="B7" s="15">
-        <v>566865</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="18">
-        <v>205</v>
-      </c>
-      <c r="B8" s="15">
-        <v>226497</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="18">
-        <v>206</v>
-      </c>
-      <c r="B9" s="15">
-        <v>845859</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="B10" s="15">
-        <v>2835926</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4501FBA7-B240-4BCD-BB90-9ED916FDB84F}">
-  <dimension ref="A3:B10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="B3" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="18">
-        <v>201</v>
-      </c>
-      <c r="B4" s="15">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="18">
-        <v>202</v>
-      </c>
-      <c r="B5" s="15">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="18">
-        <v>203</v>
-      </c>
-      <c r="B6" s="15">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="18">
-        <v>204</v>
-      </c>
-      <c r="B7" s="15">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="18">
-        <v>205</v>
-      </c>
-      <c r="B8" s="15">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="18">
-        <v>206</v>
-      </c>
-      <c r="B9" s="15">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="B10" s="15">
-        <v>250</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F27B429-55FC-42C8-AA6D-0556A87F986E}">
-  <dimension ref="A3:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="B3" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="18">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="18">
-        <v>3</v>
-      </c>
-      <c r="B5" s="15">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="18">
-        <v>4</v>
-      </c>
-      <c r="B6" s="15">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="B7" s="15">
-        <v>250</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A643E268-60B3-4A6C-9DAE-AE8118F5E71E}">
-  <dimension ref="A3:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="B3" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="16">
-        <v>1950594</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16">
-        <v>885332</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="B6" s="16">
-        <v>2835926</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40DB684-C84D-4777-80A5-AA2E00E9A86A}">
-  <dimension ref="A6:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="B6" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="16">
-        <v>1950594</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="16">
-        <v>885332</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
-        <v>911</v>
-      </c>
-      <c r="B9" s="16">
-        <v>2835926</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
-      <x14:slicerList>
-        <x14:slicer r:id="rId3"/>
-      </x14:slicerList>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDD515C-FF03-47FA-A66B-60F1EAC984C4}">
   <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15669,7 +22675,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -27959,4 +34965,577 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{845A94EE-9C2D-4ED1-9459-BE9FCC0CB032}">
+  <dimension ref="A3:B16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>918</v>
+      </c>
+      <c r="B4" s="15">
+        <v>232633</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>919</v>
+      </c>
+      <c r="B5" s="15">
+        <v>272827</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>920</v>
+      </c>
+      <c r="B6" s="15">
+        <v>289522</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>921</v>
+      </c>
+      <c r="B7" s="15">
+        <v>262328</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>922</v>
+      </c>
+      <c r="B8" s="15">
+        <v>266327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>923</v>
+      </c>
+      <c r="B9" s="15">
+        <v>290323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="B10" s="15">
+        <v>194047</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="B11" s="15">
+        <v>195545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>926</v>
+      </c>
+      <c r="B12" s="15">
+        <v>191747</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>927</v>
+      </c>
+      <c r="B13" s="15">
+        <v>213941</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="18" t="s">
+        <v>928</v>
+      </c>
+      <c r="B14" s="15">
+        <v>226341</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="18" t="s">
+        <v>929</v>
+      </c>
+      <c r="B15" s="15">
+        <v>200345</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B16" s="15">
+        <v>2835926</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43145B0-5EAA-4625-86B1-2B343EA48E35}">
+  <dimension ref="A3:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="15">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="15">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B6" s="15">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E86FBE-A6BE-4C10-8B1A-63ED78EBA71C}">
+  <dimension ref="A3:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18">
+        <v>201</v>
+      </c>
+      <c r="B4" s="15">
+        <v>379769</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18">
+        <v>202</v>
+      </c>
+      <c r="B5" s="15">
+        <v>332367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18">
+        <v>203</v>
+      </c>
+      <c r="B6" s="15">
+        <v>484569</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18">
+        <v>204</v>
+      </c>
+      <c r="B7" s="15">
+        <v>566865</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="18">
+        <v>205</v>
+      </c>
+      <c r="B8" s="15">
+        <v>226497</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="18">
+        <v>206</v>
+      </c>
+      <c r="B9" s="15">
+        <v>845859</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B10" s="15">
+        <v>2835926</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4501FBA7-B240-4BCD-BB90-9ED916FDB84F}">
+  <dimension ref="A3:B10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18">
+        <v>201</v>
+      </c>
+      <c r="B4" s="15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18">
+        <v>202</v>
+      </c>
+      <c r="B5" s="15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18">
+        <v>203</v>
+      </c>
+      <c r="B6" s="15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18">
+        <v>204</v>
+      </c>
+      <c r="B7" s="15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="18">
+        <v>205</v>
+      </c>
+      <c r="B8" s="15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="18">
+        <v>206</v>
+      </c>
+      <c r="B9" s="15">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B10" s="15">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F27B429-55FC-42C8-AA6D-0556A87F986E}">
+  <dimension ref="A3:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B7" s="15">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A643E268-60B3-4A6C-9DAE-AE8118F5E71E}">
+  <dimension ref="A3:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B3" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1950594</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="16">
+        <v>885332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B6" s="16">
+        <v>2835926</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40DB684-C84D-4777-80A5-AA2E00E9A86A}">
+  <dimension ref="A6:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B6" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>1950594</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="16">
+        <v>885332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B9" s="16">
+        <v>2835926</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE0769F-7E87-4C5E-BCED-92C8CCD95EAE}">
+  <dimension ref="A1:Y5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="46" x14ac:dyDescent="1">
+      <c r="A1" s="19" t="s">
+        <v>930</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B2" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="16">
+        <v>1950594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="16">
+        <v>885332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>911</v>
+      </c>
+      <c r="B5" s="16">
+        <v>2835926</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:Y1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA793D11-AB9F-4DAB-A655-A84F0FA3CC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C641F689-F7A3-4657-B8ED-0EDE6F9DDE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="8" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="6" activeTab="8" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -3108,7 +3108,1019 @@
     <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="931">
+  <dxfs count="1085">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -22393,8 +23405,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1095375" y="1345714"/>
-              <a:ext cx="1637365" cy="1924536"/>
+              <a:off x="1092791" y="1337592"/>
+              <a:ext cx="1637365" cy="1955548"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22471,8 +23483,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1108786" y="3454489"/>
-              <a:ext cx="1623955" cy="1043037"/>
+              <a:off x="1106202" y="3479963"/>
+              <a:ext cx="1623955" cy="1058543"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22549,8 +23561,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1110518" y="6240563"/>
-              <a:ext cx="1614503" cy="1221836"/>
+              <a:off x="1107934" y="6307386"/>
+              <a:ext cx="1614503" cy="1239926"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22627,8 +23639,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1124083" y="4670804"/>
-              <a:ext cx="1615872" cy="1396548"/>
+              <a:off x="1121499" y="4711784"/>
+              <a:ext cx="1615872" cy="1419806"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22856,8 +23868,8 @@
       <xdr:rowOff>11751</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>339396</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>221511</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>9072</xdr:rowOff>
     </xdr:to>
@@ -27263,7 +28275,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="926">
+    <format dxfId="1080">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27455,7 +28467,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="908">
+    <format dxfId="1062">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27634,7 +28646,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="909">
+    <format dxfId="1063">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27975,46 +28987,46 @@
     <dataField name="Total No. of Guests" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="827">
+    <format dxfId="981">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="828">
+    <format dxfId="982">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="829">
+    <format dxfId="983">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="830">
+    <format dxfId="984">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="831">
+    <format dxfId="985">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="832">
+    <format dxfId="986">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="833">
+    <format dxfId="987">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="834">
+    <format dxfId="988">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="740">
+    <format dxfId="894">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="735">
+    <format dxfId="889">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="659">
+    <format dxfId="813">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="645">
+    <format dxfId="799">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="635">
+    <format dxfId="789">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="625">
+    <format dxfId="779">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -28344,46 +29356,46 @@
     <dataField name="Paid %" fld="8" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="819">
+    <format dxfId="973">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="820">
+    <format dxfId="974">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="821">
+    <format dxfId="975">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="822">
+    <format dxfId="976">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="823">
+    <format dxfId="977">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="824">
+    <format dxfId="978">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="825">
+    <format dxfId="979">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="826">
+    <format dxfId="980">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="739">
+    <format dxfId="893">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="733">
+    <format dxfId="887">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="656">
+    <format dxfId="810">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="643">
+    <format dxfId="797">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="633">
+    <format dxfId="787">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="623">
+    <format dxfId="777">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -28713,46 +29725,46 @@
     <dataField name="Avg Stay" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="811">
+    <format dxfId="965">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="812">
+    <format dxfId="966">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="813">
+    <format dxfId="967">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="814">
+    <format dxfId="968">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="815">
+    <format dxfId="969">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="816">
+    <format dxfId="970">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="817">
+    <format dxfId="971">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="818">
+    <format dxfId="972">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="738">
+    <format dxfId="892">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="731">
+    <format dxfId="885">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="653">
+    <format dxfId="807">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="641">
+    <format dxfId="795">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="631">
+    <format dxfId="785">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="621">
+    <format dxfId="775">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29082,46 +30094,46 @@
     <dataField name="No. of Booking" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="906">
+    <format dxfId="1060">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="905">
+    <format dxfId="1059">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="903">
+    <format dxfId="1057">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="894">
+    <format dxfId="1048">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="893">
+    <format dxfId="1047">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="892">
+    <format dxfId="1046">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="872">
+    <format dxfId="1026">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="865">
+    <format dxfId="1019">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="737">
+    <format dxfId="891">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="729">
+    <format dxfId="883">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="650">
+    <format dxfId="804">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="639">
+    <format dxfId="793">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="629">
+    <format dxfId="783">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="619">
+    <format dxfId="773">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29197,61 +30209,61 @@
     <dataField name="Revenue" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="19">
-    <format dxfId="907">
+    <format dxfId="1061">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="904">
+    <format dxfId="1058">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="902">
+    <format dxfId="1056">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1044">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1043">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1042">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="1035">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1031">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="1029">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1028">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="1024">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1022">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="990">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="890">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="889">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="888">
+    <format dxfId="881">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="881">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="877">
+    <format dxfId="801">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="875">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="874">
+    <format dxfId="791">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="870">
+    <format dxfId="781">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="868">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="836">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="736">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="727">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="647">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="637">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="627">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="617">
+    <format dxfId="771">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29322,7 +30334,7 @@
     <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="927">
+    <format dxfId="1081">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29384,7 +30396,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="928">
+    <format dxfId="1082">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29429,7 +30441,7 @@
     <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="929">
+    <format dxfId="1083">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29474,7 +30486,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="930">
+    <format dxfId="1084">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -30150,31 +31162,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="925" tableBorderDxfId="924">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="1079" tableBorderDxfId="1078">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="923"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="922"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="921"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="920"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="919"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="918"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="917"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="916"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="915"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="914">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="1077"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="1076"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="1075"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="1074"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="1073"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="1072"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="1071"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="1070"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="1069"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="1068">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="913">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="1067">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="912">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="1066">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="911">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="1065">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="910">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="1064">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -43372,7 +44384,7 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.4140625" customWidth="1"/>
-    <col min="2" max="2" width="22.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.58203125" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" customWidth="1"/>
     <col min="6" max="6" width="20.1640625" bestFit="1" customWidth="1"/>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7504759-6BB3-4913-B131-EB0B0D2B2ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D55E351-5FA4-4BCD-8D8C-FAA201DC3D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="6" activeTab="9" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="10" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Slicers" sheetId="12" r:id="rId8"/>
     <sheet name="Dashboard" sheetId="15" r:id="rId9"/>
     <sheet name="Data" sheetId="1" r:id="rId10"/>
+    <sheet name="Dashboard - UI" sheetId="16" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Guests">#N/A</definedName>
@@ -32,15 +33,15 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId12"/>
         <x14:slicerCache r:id="rId13"/>
         <x14:slicerCache r:id="rId14"/>
         <x14:slicerCache r:id="rId15"/>
+        <x14:slicerCache r:id="rId16"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -3108,426 +3109,512 @@
     <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="329">
+  <dxfs count="406">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <sz val="18"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <sz val="18"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <sz val="18"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <sz val="16"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+        <top style="medium">
+          <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+        <bottom style="medium">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <color theme="7" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -5048,22 +5135,113 @@
       <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="bottom"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
     </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -5390,118 +5568,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
@@ -5567,6 +5633,447 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -19016,6 +19523,605 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{517FB1B1-7CFC-AF5A-DE35-F1AF69499C79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647700" y="114300"/>
+          <a:ext cx="8610600" cy="939800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle: Rounded Corners 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96107BCF-17D8-F8F4-31C2-F6372EA2998B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1346200" y="361950"/>
+          <a:ext cx="1346200" cy="552450"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle: Rounded Corners 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD1731CF-A2EC-466F-9F61-F66A6D563392}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3308350" y="361950"/>
+          <a:ext cx="1346200" cy="552450"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle: Rounded Corners 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43EF3173-EE1B-417E-A787-4B311DD41C66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5295900" y="361950"/>
+          <a:ext cx="1346200" cy="552450"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>654050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle: Rounded Corners 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC97EADD-272A-447B-B5B8-7EAE50F02459}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7258050" y="361950"/>
+          <a:ext cx="1346200" cy="552450"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>32356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>17045</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>89506</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B62DBFF7-F847-1A20-DABC-5DF4AD6C7287}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1416050" y="387956"/>
+          <a:ext cx="1242595" cy="412750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>32356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>121125</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08F0A128-FBA6-EDDF-CBD7-5A7C01995822}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3422650" y="387956"/>
+          <a:ext cx="1136650" cy="444369"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>32356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>158749</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEBBCE23-0AFB-0997-EEB4-BAB5E1DEF0CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5454650" y="387956"/>
+          <a:ext cx="1009650" cy="481993"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>63501</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>32356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>603251</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>89506</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{711852B9-DC87-54AA-5326-94F0287A1EE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7327901" y="387956"/>
+          <a:ext cx="1200150" cy="412750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46188.716442129633" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="250" xr:uid="{ABC0FC96-CD6A-4AE4-9F1C-C79E4709B301}">
   <cacheSource type="worksheet">
@@ -23362,9 +24468,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -23372,31 +24479,41 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowItems count="1">
-    <i/>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="249">
+    <format dxfId="385">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -23588,7 +24705,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="248">
+    <format dxfId="384">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -23767,7 +24884,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="247">
+    <format dxfId="383">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -23795,6 +24912,525 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A97F3CC-C970-4285-A066-8DA46BC23B39}" name="PivotTable19" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="B2:B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Revenue" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="19">
+    <format dxfId="326">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="325">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="324">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="323">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="322">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="321">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="320">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="319">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="318">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="317">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="316">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="315">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="314">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="313">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="312">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="311">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="310">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="309">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="308">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13A31B96-545B-4121-9A93-11441739092C}" name="PivotTable23" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="Q2:Q3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0">
+      <items count="251">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total No. of Guests" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="14">
+    <format dxfId="340">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="339">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="338">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="337">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="336">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="335">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="334">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="333">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="332">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="331">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="330">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="329">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="328">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="327">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96F22A1B-87ED-4292-AB7D-7D2B76BEDF69}" name="PivotTable22" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="M2:M3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
@@ -24108,46 +25744,46 @@
     <dataField name="Paid %" fld="8" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="267">
+    <format dxfId="354">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="266">
+    <format dxfId="353">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="265">
+    <format dxfId="352">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="264">
+    <format dxfId="351">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="263">
+    <format dxfId="350">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="262">
+    <format dxfId="349">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="261">
+    <format dxfId="348">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="260">
+    <format dxfId="347">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="259">
+    <format dxfId="346">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="258">
+    <format dxfId="345">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="257">
+    <format dxfId="344">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="256">
+    <format dxfId="343">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="255">
+    <format dxfId="342">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="254">
+    <format dxfId="341">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24163,7 +25799,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{23113BB3-1651-47B3-B693-E462A53763D0}" name="PivotTable21" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="J2:J3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
@@ -24477,46 +26113,46 @@
     <dataField name="Avg Stay" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="281">
+    <format dxfId="368">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="280">
+    <format dxfId="367">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="279">
+    <format dxfId="366">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="278">
+    <format dxfId="365">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="277">
+    <format dxfId="364">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="276">
+    <format dxfId="363">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="275">
+    <format dxfId="362">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="274">
+    <format dxfId="361">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="273">
+    <format dxfId="360">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="272">
+    <format dxfId="359">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="271">
+    <format dxfId="358">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="270">
+    <format dxfId="357">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="269">
+    <format dxfId="356">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="268">
+    <format dxfId="355">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24532,7 +26168,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2BDD54C-D059-47DD-9A0B-A957026EDDA7}" name="PivotTable20" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="F2:F3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
@@ -24846,565 +26482,46 @@
     <dataField name="No. of Booking" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="295">
+    <format dxfId="382">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="294">
+    <format dxfId="381">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="293">
+    <format dxfId="380">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="292">
+    <format dxfId="379">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="291">
+    <format dxfId="378">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="290">
+    <format dxfId="377">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="289">
+    <format dxfId="376">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="288">
+    <format dxfId="375">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="287">
+    <format dxfId="374">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="286">
+    <format dxfId="373">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="285">
+    <format dxfId="372">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="284">
+    <format dxfId="371">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="283">
+    <format dxfId="370">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="282">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A97F3CC-C970-4285-A066-8DA46BC23B39}" name="PivotTable19" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="B2:B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Revenue" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <formats count="19">
-    <format dxfId="314">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="313">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="312">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="311">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="310">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="309">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="308">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="307">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="306">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="305">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="304">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="303">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="302">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="301">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="300">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="299">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="298">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="297">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="296">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13A31B96-545B-4121-9A93-11441739092C}" name="PivotTable23" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="Q2:Q3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField showAll="0">
-      <items count="251">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total No. of Guests" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="14">
-    <format dxfId="328">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="327">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="326">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="325">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="324">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="323">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="322">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="321">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="320">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="319">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="318">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="317">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="316">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="315">
+    <format dxfId="369">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -25421,68 +26538,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{756BE26C-7118-4534-BF2F-F78A58C30F2F}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A21:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="250">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3AB224-B964-49E5-95E1-DD2B5D795F59}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A15:A16" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
@@ -25511,7 +26566,7 @@
     <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="251">
+    <format dxfId="386">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -25527,7 +26582,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18B3049A-28F7-45E1-B718-B06E9E8F533A}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
@@ -25556,7 +26611,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="252">
+    <format dxfId="387">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -25572,7 +26627,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BF73C174-F712-44C1-A69F-14973AA028DE}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
@@ -25601,7 +26656,58 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="253">
+    <format dxfId="388">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559C9E3A-D81D-440F-AC65-93EBB3B843D7}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A29:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="389">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -26277,31 +27383,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="405" tableBorderDxfId="404">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="403"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="402"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="401"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="400"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="399"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="398"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="397"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="396"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="395"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="394">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="3">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="393">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="2">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="392">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="1">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="391">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="0">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="390">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -38993,6 +40099,16 @@
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1EB7A96-6EC6-4C17-8130-C269FFBDB8D7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D55E351-5FA4-4BCD-8D8C-FAA201DC3D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE69779-E9E8-4F0B-B5DE-5B4D32DB3556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="10" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
@@ -3109,2031 +3109,7 @@
     <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="406">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
+  <dxfs count="98">
     <dxf>
       <font>
         <sz val="18"/>
@@ -20058,15 +18034,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>63501</xdr:colOff>
+      <xdr:colOff>81644</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>32356</xdr:rowOff>
+      <xdr:rowOff>95856</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>603251</xdr:colOff>
+      <xdr:colOff>621394</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>89506</xdr:rowOff>
+      <xdr:rowOff>153006</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -20096,8 +18072,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7327901" y="387956"/>
-          <a:ext cx="1200150" cy="412750"/>
+          <a:off x="7366001" y="458713"/>
+          <a:ext cx="1201964" cy="420007"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -24513,7 +22489,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="385">
+    <format dxfId="77">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24705,7 +22681,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="384">
+    <format dxfId="76">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24884,7 +22860,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="383">
+    <format dxfId="75">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24971,61 +22947,61 @@
     <dataField name="Revenue" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="19">
-    <format dxfId="326">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="325">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="324">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="323">
+    <format dxfId="15">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="322">
+    <format dxfId="14">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="321">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="320">
+    <format dxfId="12">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="319">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="318">
+    <format dxfId="10">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="317">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="316">
+    <format dxfId="8">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="315">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="314">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="313">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="312">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="311">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="310">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="309">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="308">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -25375,46 +23351,46 @@
     <dataField name="Total No. of Guests" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="340">
+    <format dxfId="32">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="339">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="338">
+    <format dxfId="30">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="337">
+    <format dxfId="29">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="336">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="335">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="334">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="333">
+    <format dxfId="25">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="332">
+    <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="331">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="330">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="329">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="328">
+    <format dxfId="20">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="327">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -25744,46 +23720,46 @@
     <dataField name="Paid %" fld="8" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="354">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="353">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="352">
+    <format dxfId="44">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="351">
+    <format dxfId="43">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="350">
+    <format dxfId="42">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="349">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="348">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="347">
+    <format dxfId="39">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="346">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="345">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="344">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="343">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="342">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="341">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -26113,46 +24089,46 @@
     <dataField name="Avg Stay" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="368">
+    <format dxfId="60">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="367">
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="366">
+    <format dxfId="58">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="365">
+    <format dxfId="57">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="364">
+    <format dxfId="56">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="363">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="362">
+    <format dxfId="54">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="361">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="360">
+    <format dxfId="52">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="359">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="358">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="357">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="356">
+    <format dxfId="48">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="355">
+    <format dxfId="47">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -26482,46 +24458,46 @@
     <dataField name="No. of Booking" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="382">
+    <format dxfId="74">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="381">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="380">
+    <format dxfId="72">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="379">
+    <format dxfId="71">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="378">
+    <format dxfId="70">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="377">
+    <format dxfId="69">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="376">
+    <format dxfId="68">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="375">
+    <format dxfId="67">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="374">
+    <format dxfId="66">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="373">
+    <format dxfId="65">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="372">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="371">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="370">
+    <format dxfId="62">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="369">
+    <format dxfId="61">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -26566,7 +24542,7 @@
     <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="386">
+    <format dxfId="78">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -26611,7 +24587,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="387">
+    <format dxfId="79">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -26656,7 +24632,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="388">
+    <format dxfId="80">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -26707,7 +24683,7 @@
     <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="389">
+    <format dxfId="81">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27383,31 +25359,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="405" tableBorderDxfId="404">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="97" tableBorderDxfId="96">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="403"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="402"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="401"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="400"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="399"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="398"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="397"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="396"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="395"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="394">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="94"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="93"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="91"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="90"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="89"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="88"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="87"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="86">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="393">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="85">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="392">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="84">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="391">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="83">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="390">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="82">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE69779-E9E8-4F0B-B5DE-5B4D32DB3556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797FC07D-0A9E-4D21-8FCD-91028E0B8BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="10" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="8" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -3060,7 +3060,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3094,14 +3094,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3110,527 +3109,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="98">
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4050,6 +3528,527 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -17503,16 +17502,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>656772</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>150585</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>21772</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19957</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -17527,8 +17526,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647700" y="114300"/>
-          <a:ext cx="8610600" cy="939800"/>
+          <a:off x="2643415" y="1057728"/>
+          <a:ext cx="8636000" cy="957943"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -17571,16 +17570,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>34473</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>42635</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>59872</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>61685</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -17595,77 +17594,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1346200" y="361950"/>
-          <a:ext cx="1346200" cy="552450"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-IN" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Rectangle: Rounded Corners 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD1731CF-A2EC-466F-9F61-F66A6D563392}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3308350" y="361950"/>
-          <a:ext cx="1346200" cy="552450"/>
+          <a:off x="3345544" y="1312635"/>
+          <a:ext cx="1349828" cy="563336"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -17710,22 +17640,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:colOff>15422</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>42635</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>40822</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>61685</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Rectangle: Rounded Corners 5">
+        <xdr:cNvPr id="5" name="Rectangle: Rounded Corners 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43EF3173-EE1B-417E-A787-4B311DD41C66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD1731CF-A2EC-466F-9F61-F66A6D563392}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17733,8 +17663,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5295900" y="361950"/>
-          <a:ext cx="1346200" cy="552450"/>
+          <a:off x="5313136" y="1312635"/>
+          <a:ext cx="1349829" cy="563336"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -17778,16 +17708,85 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>654050</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>21772</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>42635</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>47172</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>61685</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle: Rounded Corners 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43EF3173-EE1B-417E-A787-4B311DD41C66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7306129" y="1312635"/>
+          <a:ext cx="1349829" cy="563336"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>908</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>42635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>28122</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>61685</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -17802,8 +17801,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7258050" y="361950"/>
-          <a:ext cx="1346200" cy="552450"/>
+          <a:off x="9271908" y="1312635"/>
+          <a:ext cx="1351643" cy="563336"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -17847,16 +17846,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>32356</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>104323</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>68641</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>17045</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>89506</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>26117</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>125791</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -17886,8 +17885,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1416050" y="387956"/>
-          <a:ext cx="1242595" cy="412750"/>
+          <a:off x="3415394" y="1338641"/>
+          <a:ext cx="1246223" cy="420007"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17911,16 +17910,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>32356</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>129722</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>68641</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>121125</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>605972</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>157410</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -17950,8 +17949,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3422650" y="387956"/>
-          <a:ext cx="1136650" cy="444369"/>
+          <a:off x="5427436" y="1338641"/>
+          <a:ext cx="1138465" cy="451626"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17972,16 +17971,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>32356</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>180522</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>68641</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>158749</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>529773</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>13605</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -18011,8 +18010,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5454650" y="387956"/>
-          <a:ext cx="1009650" cy="481993"/>
+          <a:off x="7464879" y="1338641"/>
+          <a:ext cx="1011465" cy="489250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18033,16 +18032,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>81644</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95856</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>90716</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>132141</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>621394</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>153006</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>630466</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>7862</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -18072,7 +18071,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7366001" y="458713"/>
+          <a:off x="9361716" y="1402141"/>
           <a:ext cx="1201964" cy="420007"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -22489,7 +22488,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="77">
+    <format dxfId="93">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -22681,7 +22680,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="76">
+    <format dxfId="92">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -22860,7 +22859,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="75">
+    <format dxfId="91">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -22888,6 +22887,1113 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96F22A1B-87ED-4292-AB7D-7D2B76BEDF69}" name="PivotTable22" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="M2:M3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0">
+      <items count="251">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Paid %" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="14">
+    <format dxfId="29">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{23113BB3-1651-47B3-B693-E462A53763D0}" name="PivotTable21" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="J2:J3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0">
+      <items count="251">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Avg Stay" fld="9" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="14">
+    <format dxfId="43">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="40">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="39">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2BDD54C-D059-47DD-9A0B-A957026EDDA7}" name="PivotTable20" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="F2:F3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0">
+      <items count="251">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="No. of Booking" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="14">
+    <format dxfId="57">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="55">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="54">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="53">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="51">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="49">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="48">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A97F3CC-C970-4285-A066-8DA46BC23B39}" name="PivotTable19" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="B2:B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
@@ -22947,61 +24053,61 @@
     <dataField name="Revenue" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="19">
-    <format dxfId="18">
+    <format dxfId="76">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="74">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="73">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="72">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="71">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="70">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="69">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="68">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="67">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="66">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="65">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="64">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="63">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="61">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="59">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="58">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -23037,7 +24143,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13A31B96-545B-4121-9A93-11441739092C}" name="PivotTable23" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="Q2:Q3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
@@ -23351,1153 +24457,46 @@
     <dataField name="Total No. of Guests" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="32">
+    <format dxfId="90">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="89">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="88">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="87">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="86">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="85">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="84">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="83">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="82">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="81">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="80">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="79">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="78">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96F22A1B-87ED-4292-AB7D-7D2B76BEDF69}" name="PivotTable22" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="M2:M3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField showAll="0">
-      <items count="251">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Paid %" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="14">
-    <format dxfId="46">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="45">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="44">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="43">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="42">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="41">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="40">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="39">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="38">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{23113BB3-1651-47B3-B693-E462A53763D0}" name="PivotTable21" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="J2:J3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField showAll="0">
-      <items count="251">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Avg Stay" fld="9" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="14">
-    <format dxfId="60">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="59">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="58">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="57">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="56">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="55">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="54">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="53">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="52">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="51">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="50">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="49">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="48">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="47">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A2BDD54C-D059-47DD-9A0B-A957026EDDA7}" name="PivotTable20" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="F2:F3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" showAll="0">
-      <items count="251">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="No. of Booking" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="14">
-    <format dxfId="74">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="73">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="72">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="71">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="70">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="69">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="68">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="67">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="66">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="65">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="64">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="63">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="62">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="61">
+    <format dxfId="77">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24542,7 +24541,7 @@
     <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="78">
+    <format dxfId="94">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24587,7 +24586,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="79">
+    <format dxfId="95">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24632,7 +24631,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="80">
+    <format dxfId="96">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -24683,7 +24682,7 @@
     <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="81">
+    <format dxfId="97">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -25359,31 +25358,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="97" tableBorderDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="95"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="94"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="93"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="92"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="91"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="90"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="89"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="88"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="87"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="86">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="4">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="85">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="3">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="84">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="2">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="83">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="1">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="82">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="0">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -38109,7 +38108,7 @@
       <c r="A4" s="17" t="s">
         <v>918</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4">
         <v>232633</v>
       </c>
     </row>
@@ -38117,7 +38116,7 @@
       <c r="A5" s="17" t="s">
         <v>919</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5">
         <v>272827</v>
       </c>
     </row>
@@ -38125,7 +38124,7 @@
       <c r="A6" s="17" t="s">
         <v>920</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6">
         <v>289522</v>
       </c>
     </row>
@@ -38133,7 +38132,7 @@
       <c r="A7" s="17" t="s">
         <v>921</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7">
         <v>262328</v>
       </c>
     </row>
@@ -38141,7 +38140,7 @@
       <c r="A8" s="17" t="s">
         <v>922</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8">
         <v>266327</v>
       </c>
     </row>
@@ -38149,7 +38148,7 @@
       <c r="A9" s="17" t="s">
         <v>923</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9">
         <v>290323</v>
       </c>
     </row>
@@ -38157,7 +38156,7 @@
       <c r="A10" s="17" t="s">
         <v>924</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10">
         <v>194047</v>
       </c>
     </row>
@@ -38165,7 +38164,7 @@
       <c r="A11" s="17" t="s">
         <v>925</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11">
         <v>195545</v>
       </c>
     </row>
@@ -38173,7 +38172,7 @@
       <c r="A12" s="17" t="s">
         <v>926</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12">
         <v>191747</v>
       </c>
     </row>
@@ -38181,7 +38180,7 @@
       <c r="A13" s="17" t="s">
         <v>927</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13">
         <v>213941</v>
       </c>
     </row>
@@ -38189,7 +38188,7 @@
       <c r="A14" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14">
         <v>226341</v>
       </c>
     </row>
@@ -38197,7 +38196,7 @@
       <c r="A15" s="17" t="s">
         <v>929</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15">
         <v>200345</v>
       </c>
     </row>
@@ -38205,7 +38204,7 @@
       <c r="A16" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16">
         <v>2835926</v>
       </c>
     </row>
@@ -38237,7 +38236,7 @@
       <c r="A4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4">
         <v>162</v>
       </c>
     </row>
@@ -38245,7 +38244,7 @@
       <c r="A5" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5">
         <v>88</v>
       </c>
     </row>
@@ -38253,7 +38252,7 @@
       <c r="A6" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6">
         <v>250</v>
       </c>
     </row>
@@ -38285,7 +38284,7 @@
       <c r="A4" s="17">
         <v>201</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4">
         <v>379769</v>
       </c>
     </row>
@@ -38293,7 +38292,7 @@
       <c r="A5" s="17">
         <v>202</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5">
         <v>332367</v>
       </c>
     </row>
@@ -38301,7 +38300,7 @@
       <c r="A6" s="17">
         <v>203</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6">
         <v>484569</v>
       </c>
     </row>
@@ -38309,7 +38308,7 @@
       <c r="A7" s="17">
         <v>204</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7">
         <v>566865</v>
       </c>
     </row>
@@ -38317,7 +38316,7 @@
       <c r="A8" s="17">
         <v>205</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8">
         <v>226497</v>
       </c>
     </row>
@@ -38325,7 +38324,7 @@
       <c r="A9" s="17">
         <v>206</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9">
         <v>845859</v>
       </c>
     </row>
@@ -38333,7 +38332,7 @@
       <c r="A10" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10">
         <v>2835926</v>
       </c>
     </row>
@@ -38365,7 +38364,7 @@
       <c r="A4" s="17">
         <v>201</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4">
         <v>43</v>
       </c>
     </row>
@@ -38373,7 +38372,7 @@
       <c r="A5" s="17">
         <v>202</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5">
         <v>41</v>
       </c>
     </row>
@@ -38381,7 +38380,7 @@
       <c r="A6" s="17">
         <v>203</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6">
         <v>42</v>
       </c>
     </row>
@@ -38389,7 +38388,7 @@
       <c r="A7" s="17">
         <v>204</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7">
         <v>41</v>
       </c>
     </row>
@@ -38397,7 +38396,7 @@
       <c r="A8" s="17">
         <v>205</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8">
         <v>42</v>
       </c>
     </row>
@@ -38405,7 +38404,7 @@
       <c r="A9" s="17">
         <v>206</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9">
         <v>41</v>
       </c>
     </row>
@@ -38413,7 +38412,7 @@
       <c r="A10" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10">
         <v>250</v>
       </c>
     </row>
@@ -38445,7 +38444,7 @@
       <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4">
         <v>171</v>
       </c>
     </row>
@@ -38453,7 +38452,7 @@
       <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5">
         <v>43</v>
       </c>
     </row>
@@ -38461,7 +38460,7 @@
       <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6">
         <v>36</v>
       </c>
     </row>
@@ -38469,7 +38468,7 @@
       <c r="A7" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7">
         <v>250</v>
       </c>
     </row>
@@ -38601,27 +38600,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="45.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>930</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
       <c r="T1" s="18"/>
       <c r="U1" s="18"/>
       <c r="V1" s="18"/>
@@ -38668,24 +38667,24 @@
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="21"/>
-      <c r="F3" s="28">
+      <c r="F3" s="25">
         <v>250</v>
       </c>
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
       <c r="I3" s="21"/>
-      <c r="J3" s="28">
+      <c r="J3" s="25">
         <v>3.0960000000000001</v>
       </c>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
-      <c r="M3" s="28">
+      <c r="M3" s="25">
         <v>250</v>
       </c>
       <c r="N3" s="21"/>
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
-      <c r="Q3" s="28">
+      <c r="Q3" s="25">
         <v>615</v>
       </c>
       <c r="R3" s="19"/>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C11495E-AE8A-4BCC-9216-835E3FAFB7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C801A793-8A8D-47C0-B67A-78133B4821B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="8" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
@@ -34628,7 +34628,7 @@
   <dataFields count="1">
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="3">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -34639,24 +34639,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -34762,7 +34744,7 @@
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="17">
+  <chartFormats count="11">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -34842,72 +34824,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="0" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="13">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -36991,7 +36907,7 @@
   <dataFields count="1">
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="3">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -37002,24 +36918,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -37120,7 +37018,7 @@
   <dataFields count="1">
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="15">
+  <chartFormats count="9">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -37176,72 +37074,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="12">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -37381,7 +37213,7 @@
   <dataFields count="1">
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="3">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -37392,24 +37224,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -37522,7 +37336,7 @@
   <dataFields count="1">
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="3">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -37533,24 +37347,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C801A793-8A8D-47C0-B67A-78133B4821B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEAC120-640F-4770-BED8-E143D78301BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="8" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="10" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -3109,7 +3109,2031 @@
     <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="714">
+  <dxfs count="1022">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -29652,8 +31676,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3613631" y="2789197"/>
-              <a:ext cx="1636007" cy="2027052"/>
+              <a:off x="3660322" y="2719160"/>
+              <a:ext cx="1654684" cy="1985030"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -29730,8 +31754,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3645185" y="5088694"/>
-              <a:ext cx="1617795" cy="1095217"/>
+              <a:off x="3691876" y="4967297"/>
+              <a:ext cx="1645810" cy="1067202"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -29808,8 +31832,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3646916" y="6488845"/>
-              <a:ext cx="1613145" cy="1282713"/>
+              <a:off x="3693607" y="6330095"/>
+              <a:ext cx="1631822" cy="1250029"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -29886,8 +31910,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3596981" y="8004163"/>
-              <a:ext cx="1614514" cy="1468703"/>
+              <a:off x="3643672" y="7808060"/>
+              <a:ext cx="1633191" cy="1431350"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -34539,7 +36563,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="709">
+    <format dxfId="1017">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -34740,7 +36764,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="708">
+    <format dxfId="1016">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -34952,7 +36976,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="707">
+    <format dxfId="1015">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -35293,46 +37317,46 @@
     <dataField name="Paid %" fld="8" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="645">
+    <format dxfId="953">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="644">
+    <format dxfId="952">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="643">
+    <format dxfId="951">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="642">
+    <format dxfId="950">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="641">
+    <format dxfId="949">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="640">
+    <format dxfId="948">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="639">
+    <format dxfId="947">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="638">
+    <format dxfId="946">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="637">
+    <format dxfId="945">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="636">
+    <format dxfId="944">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="635">
+    <format dxfId="943">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="634">
+    <format dxfId="942">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="633">
+    <format dxfId="941">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="632">
+    <format dxfId="940">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -35662,46 +37686,46 @@
     <dataField name="Avg Stay" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="659">
+    <format dxfId="967">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="658">
+    <format dxfId="966">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="657">
+    <format dxfId="965">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="656">
+    <format dxfId="964">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="655">
+    <format dxfId="963">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="654">
+    <format dxfId="962">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="653">
+    <format dxfId="961">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="652">
+    <format dxfId="960">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="651">
+    <format dxfId="959">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="650">
+    <format dxfId="958">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="649">
+    <format dxfId="957">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="648">
+    <format dxfId="956">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="647">
+    <format dxfId="955">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="646">
+    <format dxfId="954">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -36031,46 +38055,46 @@
     <dataField name="No. of Booking" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="673">
+    <format dxfId="981">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="672">
+    <format dxfId="980">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="671">
+    <format dxfId="979">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="670">
+    <format dxfId="978">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="669">
+    <format dxfId="977">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="668">
+    <format dxfId="976">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="667">
+    <format dxfId="975">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="666">
+    <format dxfId="974">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="665">
+    <format dxfId="973">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="664">
+    <format dxfId="972">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="663">
+    <format dxfId="971">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="662">
+    <format dxfId="970">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="661">
+    <format dxfId="969">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="660">
+    <format dxfId="968">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -36146,61 +38170,61 @@
     <dataField name="Revenue" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="19">
-    <format dxfId="692">
+    <format dxfId="1000">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="691">
+    <format dxfId="999">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="690">
+    <format dxfId="998">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="689">
+    <format dxfId="997">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="688">
+    <format dxfId="996">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="687">
+    <format dxfId="995">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="686">
+    <format dxfId="994">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="685">
+    <format dxfId="993">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="684">
+    <format dxfId="992">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="683">
+    <format dxfId="991">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="682">
+    <format dxfId="990">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="681">
+    <format dxfId="989">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="680">
+    <format dxfId="988">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="679">
+    <format dxfId="987">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="678">
+    <format dxfId="986">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="677">
+    <format dxfId="985">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="676">
+    <format dxfId="984">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="675">
+    <format dxfId="983">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="674">
+    <format dxfId="982">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -36550,46 +38574,46 @@
     <dataField name="Total No. of Guests" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="706">
+    <format dxfId="1014">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="705">
+    <format dxfId="1013">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="704">
+    <format dxfId="1012">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="703">
+    <format dxfId="1011">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="702">
+    <format dxfId="1010">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="701">
+    <format dxfId="1009">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="700">
+    <format dxfId="1008">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="699">
+    <format dxfId="1007">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="698">
+    <format dxfId="1006">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="697">
+    <format dxfId="1005">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="696">
+    <format dxfId="1004">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="695">
+    <format dxfId="1003">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="694">
+    <format dxfId="1002">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="693">
+    <format dxfId="1001">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -36634,7 +38658,7 @@
     <dataField name="Average of TotalAmount" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="710">
+    <format dxfId="1018">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -36679,7 +38703,7 @@
     <dataField name="Count of BookingID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="711">
+    <format dxfId="1019">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -36724,7 +38748,7 @@
     <dataField name="Sum of TotalAmount" fld="7" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="712">
+    <format dxfId="1020">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -36775,7 +38799,7 @@
     <dataField name="Average of Stay Duration" fld="9" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="713">
+    <format dxfId="1021">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -37520,31 +39544,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="631" tableBorderDxfId="630">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}" name="tblBookings" displayName="tblBookings" ref="A1:N251" totalsRowShown="0" dataDxfId="939" tableBorderDxfId="938">
   <autoFilter ref="A1:N251" xr:uid="{57524F6E-2822-4050-BDB9-9EEAD5A67F85}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="629"/>
-    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="628"/>
-    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="627"/>
-    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="626"/>
-    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="625"/>
-    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="624"/>
-    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="623"/>
-    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="622"/>
-    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="621"/>
-    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="620">
+    <tableColumn id="1" xr3:uid="{9170F65A-F052-4775-803A-F0FBBFAD0AA0}" name="BookingID" dataDxfId="937"/>
+    <tableColumn id="2" xr3:uid="{1E10062C-A81B-4B63-8045-5648A68D87A7}" name="RoomNo" dataDxfId="936"/>
+    <tableColumn id="3" xr3:uid="{71B329FD-1710-4DCE-A840-35DD546C2F97}" name="GuestName" dataDxfId="935"/>
+    <tableColumn id="4" xr3:uid="{23C75C8D-4109-4335-B2CB-76B286B71BE4}" name="CheckIn" dataDxfId="934"/>
+    <tableColumn id="5" xr3:uid="{DAC0EA6A-509E-4F56-9CCF-DD5AD73F1591}" name="CheckOut" dataDxfId="933"/>
+    <tableColumn id="6" xr3:uid="{BD3692F2-E7F0-4BB0-BF06-0741FF169716}" name="Guests" dataDxfId="932"/>
+    <tableColumn id="7" xr3:uid="{B42BA88D-A5D8-4B15-85E0-EC46F727D6FB}" name="Phone" dataDxfId="931"/>
+    <tableColumn id="8" xr3:uid="{6DCA41DB-C3CB-419A-B20F-B0609A2257FF}" name="TotalAmount" dataDxfId="930"/>
+    <tableColumn id="9" xr3:uid="{C5365293-BEC3-49C1-B36C-9003272469AC}" name="PaymentStatus" dataDxfId="929"/>
+    <tableColumn id="10" xr3:uid="{88565866-34C1-41F2-BB74-E6BDE2763311}" name="Stay Duration" dataDxfId="928">
       <calculatedColumnFormula>tblBookings[[#This Row],[CheckOut]]-tblBookings[[#This Row],[CheckIn]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="619">
+    <tableColumn id="11" xr3:uid="{AC06E631-1137-4297-9C19-CAE06ED64DBA}" name="Year" dataDxfId="927">
       <calculatedColumnFormula>YEAR(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="618">
+    <tableColumn id="12" xr3:uid="{299C0F0F-6331-4F7C-99A1-7A3C94402C60}" name="Month" dataDxfId="926">
       <calculatedColumnFormula>TEXT(tblBookings[[#This Row],[CheckIn]],"MMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="617">
+    <tableColumn id="13" xr3:uid="{479D8A84-0D9D-4539-940F-33BEBB3A43E2}" name="Month Number" dataDxfId="925">
       <calculatedColumnFormula>MONTH(tblBookings[[#This Row],[CheckIn]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="616">
+    <tableColumn id="14" xr3:uid="{3A8D2957-E3E3-4152-8B92-EF91FE9527CD}" name="Quarter" dataDxfId="924">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(tblBookings[[#This Row],[CheckIn]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>

--- a/Project/Hotel Booking Dashboard.xlsx
+++ b/Project/Hotel Booking Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEAC120-640F-4770-BED8-E143D78301BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D65A495-1EFB-4579-AF9C-BF8443A821F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="10" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="7" activeTab="9" xr2:uid="{8E757E6A-6F47-42FD-B295-C8127A08C130}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI CARDS" sheetId="3" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Slicers" sheetId="12" r:id="rId8"/>
     <sheet name="Dashboard" sheetId="15" r:id="rId9"/>
     <sheet name="Data" sheetId="1" r:id="rId10"/>
-    <sheet name="Dashboard - UI" sheetId="16" r:id="rId11"/>
+    <sheet name="Dashboard - UI" sheetId="16" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Guests">#N/A</definedName>
